--- a/Data/Hires/testDataUS.xlsx
+++ b/Data/Hires/testDataUS.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="27328"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A94587DC-7AE8-41B0-9A41-7D8F773C0D0B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9634BB6E-AEA9-49C1-877D-82B7626DAA38}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="98" uniqueCount="86">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="791" uniqueCount="178">
   <si>
     <t>TestCaseID</t>
   </si>
@@ -171,6 +171,12 @@
     <t>Salary</t>
   </si>
   <si>
+    <t>I9ExpirationDate</t>
+  </si>
+  <si>
+    <t>IssuingAuthority</t>
+  </si>
+  <si>
     <t>USEmploymentVerificationStatus</t>
   </si>
   <si>
@@ -180,9 +186,398 @@
     <t>ProposedPayGroupFinal</t>
   </si>
   <si>
-    <t xml:space="preserve">Test failed for 'Ruthe Fritsch-Breitenberg' Employee:{10651637}TimeoutError: locator.click: Timeout 30000ms exceeded.
+    <t>Test_1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Test failed for 'Conor Rippin' Employee:{undefined}TimeoutError: locator.click: Timeout 30000ms exceeded.
 Call log:
-  [2m- waiting for getByRole('button', { name: 'Change/Update My Government IDs', exact: true })[22m
+  [2m- waiting for getByLabel('My Tasks Items')[22m
+[2m  -   locator resolved to &lt;button class="wdappchrome-w" data-automation-id="inbox_…&gt;…&lt;/button&gt;[22m
+[2m  - attempting click action[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is visible, enabled and stable[22m
+[2m  -   scrolling into view if needed[22m
+[2m  -   done scrolling[22m
+[2m  -   &lt;div class="WDKP" data-automation-id="modalOverlay"&gt;…&lt;/div&gt; from &lt;div id="content-container"&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
+[2m  - retrying click action, attempt #1[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is visible, enabled and stable[22m
+[2m  -   scrolling into view if needed[22m
+[2m  -   done scrolling[22m
+[2m  -   &lt;div class="WDKP" data-automation-id="modalOverlay"&gt;…&lt;/div&gt; from &lt;div id="content-container"&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
+[2m  - retrying click action, attempt #2[22m
+[2m  -   waiting 20ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is visible, enabled and stable[22m
+[2m  -   scrolling into view if needed[22m
+[2m  -   done scrolling[22m
+[2m  -   &lt;div class="WDKP" data-automation-id="modalOverlay"&gt;…&lt;/div&gt; from &lt;div id="content-container"&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
+[2m  - retrying click action, attempt #3[22m
+[2m  -   waiting 100ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is visible, enabled and stable[22m
+[2m  -   scrolling into view if needed[22m
+[2m  -   done scrolling[22m
+[2m  -   &lt;div class="WDKP" data-automation-id="modalOverlay"&gt;…&lt;/div&gt; from &lt;div id="content-container"&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
+[2m  - retrying click action, attempt #4[22m
+[2m  -   waiting 100ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is visible, enabled and stable[22m
+[2m  -   scrolling into view if needed[22m
+[2m  -   done scrolling[22m
+[2m  -   &lt;div class="WDKP" data-automation-id="modalOverlay"&gt;…&lt;/div&gt; from &lt;div id="content-container"&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
+[2m  - retrying click action, attempt #5[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is visible, enabled and stable[22m
+[2m  -   scrolling into view if needed[22m
+[2m  -   done scrolling[22m
+[2m  -   &lt;div class="WDKP" data-automation-id="modalOverlay"&gt;…&lt;/div&gt; from &lt;div id="content-container"&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
+[2m  - retrying click action, attempt #6[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is visible, enabled and stable[22m
+[2m  -   scrolling into view if needed[22m
+[2m  -   done scrolling[22m
+[2m  -   &lt;div class="WDKP" data-automation-id="modalOverlay"&gt;…&lt;/div&gt; from &lt;div id="content-container"&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
+[2m  - retrying click action, attempt #7[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is visible, enabled and stable[22m
+[2m  -   scrolling into view if needed[22m
+[2m  -   done scrolling[22m
+[2m  -   &lt;div class="WDKP" data-automation-id="modalOverlay"&gt;…&lt;/div&gt; from &lt;div id="content-container"&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
+[2m  - retrying click action, attempt #8[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is visible, enabled and stable[22m
+[2m  -   scrolling into view if needed[22m
+[2m  -   done scrolling[22m
+[2m  -   &lt;div class="WDKP" data-automation-id="modalOverlay"&gt;…&lt;/div&gt; from &lt;div id="content-container"&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
+[2m  - retrying click action, attempt #9[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is visible, enabled and stable[22m
+[2m  -   scrolling into view if needed[22m
+[2m  -   done scrolling[22m
+[2m  -   &lt;div class="WDKP" data-automation-id="modalOverlay"&gt;…&lt;/div&gt; from &lt;div id="content-container"&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
+[2m  - retrying click action, attempt #10[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is visible, enabled and stable[22m
+[2m  -   scrolling into view if needed[22m
+[2m  -   done scrolling[22m
+[2m  -   &lt;div class="WDKP" data-automation-id="modalOverlay"&gt;…&lt;/div&gt; from &lt;div id="content-container"&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
+[2m  - retrying click action, attempt #11[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is visible, enabled and stable[22m
+[2m  -   scrolling into view if needed[22m
+[2m  -   done scrolling[22m
+[2m  -   &lt;div class="WDKP" data-automation-id="modalOverlay"&gt;…&lt;/div&gt; from &lt;div id="content-container"&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
+[2m  - retrying click action, attempt #12[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is visible, enabled and stable[22m
+[2m  -   scrolling into view if needed[22m
+[2m  -   done scrolling[22m
+[2m  -   &lt;div class="WDKP" data-automation-id="modalOverlay"&gt;…&lt;/div&gt; from &lt;div id="content-container"&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
+[2m  - retrying click action, attempt #13[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is visible, enabled and stable[22m
+[2m  -   scrolling into view if needed[22m
+[2m  -   done scrolling[22m
+[2m  -   &lt;div class="WDKP" data-automation-id="modalOverlay"&gt;…&lt;/div&gt; from &lt;div id="content-container"&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
+[2m  - retrying click action, attempt #14[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is visible, enabled and stable[22m
+[2m  -   scrolling into view if needed[22m
+[2m  -   done scrolling[22m
+[2m  -   &lt;div class="WDKP" data-automation-id="modalOverlay"&gt;…&lt;/div&gt; from &lt;div id="content-container"&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
+[2m  - retrying click action, attempt #15[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is visible, enabled and stable[22m
+[2m  -   scrolling into view if needed[22m
+[2m  -   done scrolling[22m
+[2m  -   &lt;div class="WDKP" data-automation-id="modalOverlay"&gt;…&lt;/div&gt; from &lt;div id="content-container"&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
+[2m  - retrying click action, attempt #16[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is visible, enabled and stable[22m
+[2m  -   scrolling into view if needed[22m
+[2m  -   done scrolling[22m
+[2m  -   &lt;div class="WDKP" data-automation-id="modalOverlay"&gt;…&lt;/div&gt; from &lt;div id="content-container"&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
+[2m  - retrying click action, attempt #17[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is visible, enabled and stable[22m
+[2m  -   scrolling into view if needed[22m
+[2m  -   done scrolling[22m
+[2m  -   &lt;div class="WDKP" data-automation-id="modalOverlay"&gt;…&lt;/div&gt; from &lt;div id="content-container"&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
+[2m  - retrying click action, attempt #18[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is visible, enabled and stable[22m
+[2m  -   scrolling into view if needed[22m
+[2m  -   done scrolling[22m
+[2m  -   &lt;div class="WDKP" data-automation-id="modalOverlay"&gt;…&lt;/div&gt; from &lt;div id="content-container"&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
+[2m  - retrying click action, attempt #19[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is visible, enabled and stable[22m
+[2m  -   scrolling into view if needed[22m
+[2m  -   done scrolling[22m
+[2m  -   &lt;div class="WDKP" data-automation-id="modalOverlay"&gt;…&lt;/div&gt; from &lt;div id="content-container"&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
+[2m  - retrying click action, attempt #20[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is visible, enabled and stable[22m
+[2m  -   scrolling into view if needed[22m
+[2m  -   done scrolling[22m
+[2m  -   &lt;div class="WDKP" data-automation-id="modalOverlay"&gt;…&lt;/div&gt; from &lt;div id="content-container"&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
+[2m  - retrying click action, attempt #21[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is visible, enabled and stable[22m
+[2m  -   scrolling into view if needed[22m
+[2m  -   done scrolling[22m
+[2m  -   &lt;div class="WDKP" data-automation-id="modalOverlay"&gt;…&lt;/div&gt; from &lt;div id="content-container"&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
+[2m  - retrying click action, attempt #22[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is visible, enabled and stable[22m
+[2m  -   scrolling into view if needed[22m
+[2m  -   done scrolling[22m
+[2m  -   &lt;div class="WDKP" data-automation-id="modalOverlay"&gt;…&lt;/div&gt; from &lt;div id="content-container"&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
+[2m  - retrying click action, attempt #23[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is visible, enabled and stable[22m
+[2m  -   scrolling into view if needed[22m
+[2m  -   done scrolling[22m
+[2m  -   &lt;div class="WDKP" data-automation-id="modalOverlay"&gt;…&lt;/div&gt; from &lt;div id="content-container"&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
+[2m  - retrying click action, attempt #24[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is visible, enabled and stable[22m
+[2m  -   scrolling into view if needed[22m
+[2m  -   done scrolling[22m
+[2m  -   &lt;div class="WDKP" data-automation-id="modalOverlay"&gt;…&lt;/div&gt; from &lt;div id="content-container"&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
+[2m  - retrying click action, attempt #25[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is visible, enabled and stable[22m
+[2m  -   scrolling into view if needed[22m
+[2m  -   done scrolling[22m
+[2m  -   &lt;div class="WDKP" data-automation-id="modalOverlay"&gt;…&lt;/div&gt; from &lt;div id="content-container"&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
+[2m  - retrying click action, attempt #26[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is visible, enabled and stable[22m
+[2m  -   scrolling into view if needed[22m
+[2m  -   done scrolling[22m
+[2m  -   &lt;div class="WDKP" data-automation-id="modalOverlay"&gt;…&lt;/div&gt; from &lt;div id="content-container"&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
+[2m  - retrying click action, attempt #27[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is visible, enabled and stable[22m
+[2m  -   scrolling into view if needed[22m
+[2m  -   done scrolling[22m
+[2m  -   &lt;div class="WDKP" data-automation-id="modalOverlay"&gt;…&lt;/div&gt; from &lt;div id="content-container"&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
+[2m  - retrying click action, attempt #28[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is visible, enabled and stable[22m
+[2m  -   scrolling into view if needed[22m
+[2m  -   done scrolling[22m
+[2m  -   &lt;div class="WDKP" data-automation-id="modalOverlay"&gt;…&lt;/div&gt; from &lt;div id="content-container"&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
+[2m  - retrying click action, attempt #29[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is visible, enabled and stable[22m
+[2m  -   scrolling into view if needed[22m
+[2m  -   done scrolling[22m
+[2m  -   &lt;div class="WDKP" data-automation-id="modalOverlay"&gt;…&lt;/div&gt; from &lt;div id="content-container"&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
+[2m  - retrying click action, attempt #30[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is visible, enabled and stable[22m
+[2m  -   scrolling into view if needed[22m
+[2m  -   done scrolling[22m
+[2m  -   &lt;div class="WDKP" data-automation-id="modalOverlay"&gt;…&lt;/div&gt; from &lt;div id="content-container"&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
+[2m  - retrying click action, attempt #31[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is visible, enabled and stable[22m
+[2m  -   scrolling into view if needed[22m
+[2m  -   done scrolling[22m
+[2m  -   &lt;div class="WDKP" data-automation-id="modalOverlay"&gt;…&lt;/div&gt; from &lt;div id="content-container"&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
+[2m  - retrying click action, attempt #32[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is visible, enabled and stable[22m
+[2m  -   scrolling into view if needed[22m
+[2m  -   done scrolling[22m
+[2m  -   &lt;div class="WDKP" data-automation-id="modalOverlay"&gt;…&lt;/div&gt; from &lt;div id="content-container"&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
+[2m  - retrying click action, attempt #33[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is visible, enabled and stable[22m
+[2m  -   scrolling into view if needed[22m
+[2m  -   done scrolling[22m
+[2m  -   &lt;div class="WDKP" data-automation-id="modalOverlay"&gt;…&lt;/div&gt; from &lt;div id="content-container"&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
+[2m  - retrying click action, attempt #34[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is visible, enabled and stable[22m
+[2m  -   scrolling into view if needed[22m
+[2m  -   done scrolling[22m
+[2m  -   &lt;div class="WDKP" data-automation-id="modalOverlay"&gt;…&lt;/div&gt; from &lt;div id="content-container"&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
+[2m  - retrying click action, attempt #35[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is visible, enabled and stable[22m
+[2m  -   scrolling into view if needed[22m
+[2m  -   done scrolling[22m
+[2m  -   &lt;div class="WDKP" data-automation-id="modalOverlay"&gt;…&lt;/div&gt; from &lt;div id="content-container"&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
+[2m  - retrying click action, attempt #36[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is visible, enabled and stable[22m
+[2m  -   scrolling into view if needed[22m
+[2m  -   done scrolling[22m
+[2m  -   &lt;div class="WDKP" data-automation-id="modalOverlay"&gt;…&lt;/div&gt; from &lt;div id="content-container"&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
+[2m  - retrying click action, attempt #37[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is visible, enabled and stable[22m
+[2m  -   scrolling into view if needed[22m
+[2m  -   done scrolling[22m
+[2m  -   &lt;div class="WDKP" data-automation-id="modalOverlay"&gt;…&lt;/div&gt; from &lt;div id="content-container"&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
+[2m  - retrying click action, attempt #38[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is visible, enabled and stable[22m
+[2m  -   scrolling into view if needed[22m
+[2m  -   done scrolling[22m
+[2m  -   &lt;div class="WDKP" data-automation-id="modalOverlay"&gt;…&lt;/div&gt; from &lt;div id="content-container"&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
+[2m  - retrying click action, attempt #39[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is visible, enabled and stable[22m
+[2m  -   scrolling into view if needed[22m
+[2m  -   done scrolling[22m
+[2m  -   &lt;div class="WDKP" data-automation-id="modalOverlay"&gt;…&lt;/div&gt; from &lt;div id="content-container"&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
+[2m  - retrying click action, attempt #40[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is visible, enabled and stable[22m
+[2m  -   scrolling into view if needed[22m
+[2m  -   done scrolling[22m
+[2m  -   &lt;div class="WDKP" data-automation-id="modalOverlay"&gt;…&lt;/div&gt; from &lt;div id="content-container"&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
+[2m  - retrying click action, attempt #41[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is visible, enabled and stable[22m
+[2m  -   scrolling into view if needed[22m
+[2m  -   done scrolling[22m
+[2m  -   &lt;div class="WDKP" data-automation-id="modalOverlay"&gt;…&lt;/div&gt; from &lt;div id="content-container"&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
+[2m  - retrying click action, attempt #42[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is visible, enabled and stable[22m
+[2m  -   scrolling into view if needed[22m
+[2m  -   done scrolling[22m
+[2m  -   &lt;div class="WDKP" data-automation-id="modalOverlay"&gt;…&lt;/div&gt; from &lt;div id="content-container"&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
+[2m  - retrying click action, attempt #43[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is visible, enabled and stable[22m
+[2m  -   scrolling into view if needed[22m
+[2m  -   done scrolling[22m
+[2m  -   &lt;div class="WDKP" data-automation-id="modalOverlay"&gt;…&lt;/div&gt; from &lt;div id="content-container"&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
+[2m  - retrying click action, attempt #44[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is visible, enabled and stable[22m
+[2m  -   scrolling into view if needed[22m
+[2m  -   done scrolling[22m
+[2m  -   &lt;div class="WDKP" data-automation-id="modalOverlay"&gt;…&lt;/div&gt; from &lt;div id="content-container"&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
+[2m  - retrying click action, attempt #45[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is visible, enabled and stable[22m
+[2m  -   scrolling into view if needed[22m
+[2m  -   done scrolling[22m
+[2m  -   &lt;div class="WDKP" data-automation-id="modalOverlay"&gt;…&lt;/div&gt; from &lt;div id="content-container"&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
+[2m  - retrying click action, attempt #46[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is visible, enabled and stable[22m
+[2m  -   scrolling into view if needed[22m
+[2m  -   done scrolling[22m
+[2m  -   &lt;div class="WDKP" data-automation-id="modalOverlay"&gt;…&lt;/div&gt; from &lt;div id="content-container"&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
+[2m  - retrying click action, attempt #47[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is visible, enabled and stable[22m
+[2m  -   scrolling into view if needed[22m
+[2m  -   done scrolling[22m
+[2m  -   &lt;div class="WDKP" data-automation-id="modalOverlay"&gt;…&lt;/div&gt; from &lt;div id="content-container"&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
+[2m  - retrying click action, attempt #48[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is visible, enabled and stable[22m
+[2m  -   scrolling into view if needed[22m
+[2m  -   done scrolling[22m
+[2m  -   &lt;div class="WDKP" data-automation-id="modalOverlay"&gt;…&lt;/div&gt; from &lt;div id="content-container"&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
+[2m  - retrying click action, attempt #49[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is visible, enabled and stable[22m
+[2m  -   scrolling into view if needed[22m
+[2m  -   done scrolling[22m
+[2m  -   &lt;div class="WDKP" data-automation-id="modalOverlay"&gt;…&lt;/div&gt; from &lt;div id="content-container"&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
+[2m  - retrying click action, attempt #50[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is visible, enabled and stable[22m
+[2m  -   scrolling into view if needed[22m
+[2m  -   done scrolling[22m
+[2m  -   &lt;div class="WDKP" data-automation-id="modalOverlay"&gt;…&lt;/div&gt; from &lt;div id="content-container"&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
+[2m  - retrying click action, attempt #51[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is visible, enabled and stable[22m
+[2m  -   scrolling into view if needed[22m
+[2m  -   done scrolling[22m
+[2m  -   &lt;div class="WDKP" data-automation-id="modalOverlay"&gt;…&lt;/div&gt; from &lt;div id="content-container"&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
+[2m  - retrying click action, attempt #52[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is visible, enabled and stable[22m
+[2m  -   scrolling into view if needed[22m
+[2m  -   done scrolling[22m
+[2m  -   &lt;div class="WDKP" data-automation-id="modalOverlay"&gt;…&lt;/div&gt; from &lt;div id="content-container"&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
+[2m  - retrying click action, attempt #53[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is visible, enabled and stable[22m
+[2m  -   scrolling into view if needed[22m
+[2m  -   done scrolling[22m
+[2m  -   &lt;div class="WDKP" data-automation-id="modalOverlay"&gt;…&lt;/div&gt; from &lt;div id="content-container"&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
+[2m  - retrying click action, attempt #54[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is visible, enabled and stable[22m
+[2m  -   scrolling into view if needed[22m
+[2m  -   done scrolling[22m
+[2m  -   &lt;div class="WDKP" data-automation-id="modalOverlay"&gt;…&lt;/div&gt; from &lt;div id="content-container"&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
+[2m  - retrying click action, attempt #55[22m
+[2m  -   waiting 500ms[22m
 </t>
   </si>
   <si>
@@ -198,10 +593,10 @@
     <t>Mr</t>
   </si>
   <si>
-    <t>Ruthe</t>
-  </si>
-  <si>
-    <t>Fritsch-Breitenberg</t>
+    <t>Conor</t>
+  </si>
+  <si>
+    <t>Rippin</t>
   </si>
   <si>
     <t>(202) 555-0147</t>
@@ -288,17 +683,2151 @@
     <t>USA Pay Group</t>
   </si>
   <si>
-    <t>Test_1</t>
+    <t>Test_2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Test failed for 'Francesco Heaney' Employee:{}TimeoutError: locator.click: Timeout 30000ms exceeded.
+Call log:
+  [2m- waiting for locator('text=Hire Employee').nth(1)[22m
+</t>
+  </si>
+  <si>
+    <t>121 Recruitment (Depez Wicypy (10498025))</t>
+  </si>
+  <si>
+    <t>Francesco</t>
+  </si>
+  <si>
+    <t>Heaney</t>
+  </si>
+  <si>
+    <t>Regular</t>
+  </si>
+  <si>
+    <t>Full time</t>
+  </si>
+  <si>
+    <t>06</t>
+  </si>
+  <si>
+    <t>Test_3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Test failed for 'Ward Aufderhar' Employee:{}TimeoutError: locator.click: Timeout 30000ms exceeded.
+Call log:
+  [2m- waiting for locator('[aria-label="Save Other"]')[22m
+[2m  -   locator resolved to &lt;button title="Save" aria-pressed="false" aria-label="Sa…&gt;…&lt;/button&gt;[22m
+[2m  - attempting click action[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is not stable[22m
+[2m  - retrying click action, attempt #1[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is not stable[22m
+[2m  - retrying click action, attempt #2[22m
+[2m  -   waiting 20ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is not stable[22m
+[2m  - retrying click action, attempt #3[22m
+[2m  -   waiting 100ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is not stable[22m
+[2m  - retrying click action, attempt #4[22m
+[2m  -   waiting 100ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is not stable[22m
+[2m  - retrying click action, attempt #5[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is not stable[22m
+[2m  - retrying click action, attempt #6[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is not stable[22m
+[2m  - retrying click action, attempt #7[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is not stable[22m
+[2m  - retrying click action, attempt #8[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is not stable[22m
+[2m  - retrying click action, attempt #9[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is not stable[22m
+[2m  - retrying click action, attempt #10[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is not stable[22m
+[2m  - retrying click action, attempt #11[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is not stable[22m
+[2m  - retrying click action, attempt #12[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is not stable[22m
+[2m  - retrying click action, attempt #13[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is not stable[22m
+[2m  - retrying click action, attempt #14[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is not stable[22m
+[2m  - retrying click action, attempt #15[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is not stable[22m
+[2m  - retrying click action, attempt #16[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is not stable[22m
+[2m  - retrying click action, attempt #17[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is not stable[22m
+[2m  - retrying click action, attempt #18[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is not stable[22m
+[2m  - retrying click action, attempt #19[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is not stable[22m
+[2m  - retrying click action, attempt #20[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is not stable[22m
+[2m  - retrying click action, attempt #21[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is not stable[22m
+[2m  - retrying click action, attempt #22[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is not stable[22m
+[2m  - retrying click action, attempt #23[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is not stable[22m
+[2m  - retrying click action, attempt #24[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is not stable[22m
+[2m  - retrying click action, attempt #25[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is not stable[22m
+[2m  - retrying click action, attempt #26[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is not stable[22m
+[2m  - retrying click action, attempt #27[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is not stable[22m
+[2m  - retrying click action, attempt #28[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is not stable[22m
+[2m  - retrying click action, attempt #29[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is not stable[22m
+[2m  - retrying click action, attempt #30[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is not stable[22m
+[2m  - retrying click action, attempt #31[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is not stable[22m
+[2m  - retrying click action, attempt #32[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is not stable[22m
+[2m  - retrying click action, attempt #33[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is not stable[22m
+[2m  - retrying click action, attempt #34[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is not stable[22m
+[2m  - retrying click action, attempt #35[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is not stable[22m
+[2m  - retrying click action, attempt #36[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is not stable[22m
+[2m  - retrying click action, attempt #37[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is not stable[22m
+[2m  - retrying click action, attempt #38[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is not stable[22m
+[2m  - retrying click action, attempt #39[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is not stable[22m
+[2m  - retrying click action, attempt #40[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is not stable[22m
+[2m  - retrying click action, attempt #41[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is not stable[22m
+[2m  - retrying click action, attempt #42[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is not stable[22m
+[2m  - retrying click action, attempt #43[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is not stable[22m
+[2m  - retrying click action, attempt #44[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is not stable[22m
+[2m  - retrying click action, attempt #45[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is not stable[22m
+[2m  - retrying click action, attempt #46[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is not stable[22m
+[2m  - retrying click action, attempt #47[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is not stable[22m
+[2m  - retrying click action, attempt #48[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is not stable[22m
+[2m  - retrying click action, attempt #49[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is not stable[22m
+[2m  - retrying click action, attempt #50[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is not stable[22m
+[2m  - retrying click action, attempt #51[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is not stable[22m
+[2m  - retrying click action, attempt #52[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is not stable[22m
+[2m  - retrying click action, attempt #53[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is not stable[22m
+[2m  - retrying click action, attempt #54[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is not stable[22m
+[2m  - retrying click action, attempt #55[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is not stable[22m
+[2m  - retrying click action, attempt #56[22m
+[2m  -   waiting 500ms[22m
+</t>
+  </si>
+  <si>
+    <t>124 Store Management (Setap Pijura Vucylu (10181574))</t>
+  </si>
+  <si>
+    <t>Ward</t>
+  </si>
+  <si>
+    <t>Aufderhar</t>
+  </si>
+  <si>
+    <t>Auto 21405142</t>
+  </si>
+  <si>
+    <t>Department Manager_NEW</t>
+  </si>
+  <si>
+    <t xml:space="preserve">92 Retail Management </t>
+  </si>
+  <si>
+    <t xml:space="preserve">251 Management Retail </t>
+  </si>
+  <si>
+    <t>Test_4</t>
+  </si>
+  <si>
+    <t>10651893</t>
+  </si>
+  <si>
+    <t>Passed</t>
+  </si>
+  <si>
+    <t>Syble</t>
+  </si>
+  <si>
+    <t>Runolfsson</t>
+  </si>
+  <si>
+    <t>Test_5</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Test failed for 'Marcelino Harber' Employee:{}TimeoutError: locator.click: Timeout 30000ms exceeded.
+Call log:
+  [2m- waiting for locator('[aria-label="Save Other"]')[22m
+[2m  -   locator resolved to &lt;button title="Save" aria-pressed="false" aria-label="Sa…&gt;…&lt;/button&gt;[22m
+[2m  - attempting click action[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is not stable[22m
+[2m  - retrying click action, attempt #1[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is not stable[22m
+[2m  - retrying click action, attempt #2[22m
+[2m  -   waiting 20ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is not stable[22m
+[2m  - retrying click action, attempt #3[22m
+[2m  -   waiting 100ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is not stable[22m
+[2m  - retrying click action, attempt #4[22m
+[2m  -   waiting 100ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is not stable[22m
+[2m  - retrying click action, attempt #5[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is not stable[22m
+[2m  - retrying click action, attempt #6[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is not stable[22m
+[2m  - retrying click action, attempt #7[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is not stable[22m
+[2m  - retrying click action, attempt #8[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is not stable[22m
+[2m  - retrying click action, attempt #9[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is not stable[22m
+[2m  - retrying click action, attempt #10[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is not stable[22m
+[2m  - retrying click action, attempt #11[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is not stable[22m
+[2m  - retrying click action, attempt #12[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is not stable[22m
+[2m  - retrying click action, attempt #13[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is not stable[22m
+[2m  - retrying click action, attempt #14[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is not stable[22m
+[2m  - retrying click action, attempt #15[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is not stable[22m
+[2m  - retrying click action, attempt #16[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is not stable[22m
+[2m  - retrying click action, attempt #17[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is not stable[22m
+[2m  - retrying click action, attempt #18[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is not stable[22m
+[2m  - retrying click action, attempt #19[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is not stable[22m
+[2m  - retrying click action, attempt #20[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is not stable[22m
+[2m  - retrying click action, attempt #21[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is not stable[22m
+[2m  - retrying click action, attempt #22[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is not stable[22m
+[2m  - retrying click action, attempt #23[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is not stable[22m
+[2m  - retrying click action, attempt #24[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is not stable[22m
+[2m  - retrying click action, attempt #25[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is not stable[22m
+[2m  - retrying click action, attempt #26[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is not stable[22m
+[2m  - retrying click action, attempt #27[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is not stable[22m
+[2m  - retrying click action, attempt #28[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is not stable[22m
+[2m  - retrying click action, attempt #29[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is not stable[22m
+[2m  - retrying click action, attempt #30[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is not stable[22m
+[2m  - retrying click action, attempt #31[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is not stable[22m
+[2m  - retrying click action, attempt #32[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is not stable[22m
+[2m  - retrying click action, attempt #33[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is not stable[22m
+[2m  - retrying click action, attempt #34[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is not stable[22m
+[2m  - retrying click action, attempt #35[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is not stable[22m
+[2m  - retrying click action, attempt #36[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is not stable[22m
+[2m  - retrying click action, attempt #37[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is not stable[22m
+[2m  - retrying click action, attempt #38[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is not stable[22m
+[2m  - retrying click action, attempt #39[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is not stable[22m
+[2m  - retrying click action, attempt #40[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is not stable[22m
+[2m  - retrying click action, attempt #41[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is not stable[22m
+[2m  - retrying click action, attempt #42[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is not stable[22m
+[2m  - retrying click action, attempt #43[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is not stable[22m
+[2m  - retrying click action, attempt #44[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is not stable[22m
+[2m  - retrying click action, attempt #45[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is not stable[22m
+[2m  - retrying click action, attempt #46[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is not stable[22m
+[2m  - retrying click action, attempt #47[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is not stable[22m
+[2m  - retrying click action, attempt #48[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is not stable[22m
+[2m  - retrying click action, attempt #49[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is not stable[22m
+[2m  - retrying click action, attempt #50[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is not stable[22m
+[2m  - retrying click action, attempt #51[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is not stable[22m
+[2m  - retrying click action, attempt #52[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is not stable[22m
+[2m  - retrying click action, attempt #53[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is not stable[22m
+[2m  - retrying click action, attempt #54[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is not stable[22m
+[2m  - retrying click action, attempt #55[22m
+[2m  -   waiting 500ms[22m
+</t>
+  </si>
+  <si>
+    <t>Marcelino</t>
+  </si>
+  <si>
+    <t>Harber</t>
+  </si>
+  <si>
+    <t>Auto 33976609</t>
+  </si>
+  <si>
+    <t>Store Manager_NEW</t>
+  </si>
+  <si>
+    <t>Test_6</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Test failed for 'Mose Bradtke' Employee:{}TimeoutError: locator.click: Timeout 30000ms exceeded.
+Call log:
+  [2m- waiting for locator('[aria-label="Save Other"]')[22m
+[2m  -   locator resolved to &lt;button title="Save" aria-pressed="false" aria-label="Sa…&gt;…&lt;/button&gt;[22m
+[2m  - attempting click action[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is not stable[22m
+[2m  - retrying click action, attempt #1[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is not stable[22m
+[2m  - retrying click action, attempt #2[22m
+[2m  -   waiting 20ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is not stable[22m
+[2m  - retrying click action, attempt #3[22m
+[2m  -   waiting 100ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is not stable[22m
+[2m  - retrying click action, attempt #4[22m
+[2m  -   waiting 100ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is not stable[22m
+[2m  - retrying click action, attempt #5[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is not stable[22m
+[2m  - retrying click action, attempt #6[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is not stable[22m
+[2m  - retrying click action, attempt #7[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is not stable[22m
+[2m  - retrying click action, attempt #8[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is not stable[22m
+[2m  - retrying click action, attempt #9[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is not stable[22m
+[2m  - retrying click action, attempt #10[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is not stable[22m
+[2m  - retrying click action, attempt #11[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is not stable[22m
+[2m  - retrying click action, attempt #12[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is not stable[22m
+[2m  - retrying click action, attempt #13[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is not stable[22m
+[2m  - retrying click action, attempt #14[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is not stable[22m
+[2m  - retrying click action, attempt #15[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is not stable[22m
+[2m  - retrying click action, attempt #16[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is not stable[22m
+[2m  - retrying click action, attempt #17[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is not stable[22m
+[2m  - retrying click action, attempt #18[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is not stable[22m
+[2m  - retrying click action, attempt #19[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is not stable[22m
+[2m  - retrying click action, attempt #20[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is not stable[22m
+[2m  - retrying click action, attempt #21[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is not stable[22m
+[2m  - retrying click action, attempt #22[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is not stable[22m
+[2m  - retrying click action, attempt #23[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is not stable[22m
+[2m  - retrying click action, attempt #24[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is not stable[22m
+[2m  - retrying click action, attempt #25[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is not stable[22m
+[2m  - retrying click action, attempt #26[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is not stable[22m
+[2m  - retrying click action, attempt #27[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is not stable[22m
+[2m  - retrying click action, attempt #28[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is not stable[22m
+[2m  - retrying click action, attempt #29[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is not stable[22m
+[2m  - retrying click action, attempt #30[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is not stable[22m
+[2m  - retrying click action, attempt #31[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is not stable[22m
+[2m  - retrying click action, attempt #32[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is not stable[22m
+[2m  - retrying click action, attempt #33[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is not stable[22m
+[2m  - retrying click action, attempt #34[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is not stable[22m
+[2m  - retrying click action, attempt #35[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is not stable[22m
+[2m  - retrying click action, attempt #36[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is not stable[22m
+[2m  - retrying click action, attempt #37[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is not stable[22m
+[2m  - retrying click action, attempt #38[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is not stable[22m
+[2m  - retrying click action, attempt #39[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is not stable[22m
+[2m  - retrying click action, attempt #40[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is not stable[22m
+[2m  - retrying click action, attempt #41[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is not stable[22m
+[2m  - retrying click action, attempt #42[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is not stable[22m
+[2m  - retrying click action, attempt #43[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is not stable[22m
+[2m  - retrying click action, attempt #44[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is not stable[22m
+[2m  - retrying click action, attempt #45[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is not stable[22m
+[2m  - retrying click action, attempt #46[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is not stable[22m
+[2m  - retrying click action, attempt #47[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is not stable[22m
+[2m  - retrying click action, attempt #48[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is not stable[22m
+[2m  - retrying click action, attempt #49[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is not stable[22m
+[2m  - retrying click action, attempt #50[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is not stable[22m
+[2m  - retrying click action, attempt #51[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is not stable[22m
+[2m  - retrying click action, attempt #52[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is not stable[22m
+[2m  - retrying click action, attempt #53[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is not stable[22m
+[2m  - retrying click action, attempt #54[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is not stable[22m
+[2m  - retrying click action, attempt #55[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is not stable[22m
+[2m  - retrying click action, attempt #56[22m
+[2m  -   waiting 500ms[22m
+</t>
+  </si>
+  <si>
+    <t>Mose</t>
+  </si>
+  <si>
+    <t>Bradtke</t>
+  </si>
+  <si>
+    <t>Auto 76485729</t>
+  </si>
+  <si>
+    <t>Assistant Store Manager_NEW</t>
+  </si>
+  <si>
+    <t>Test_7</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Test failed for 'Hosea Hickle' Employee:{}TimeoutError: locator.click: Timeout 30000ms exceeded.
+Call log:
+  [2m- waiting for locator('[aria-label="Save Other"]')[22m
+[2m  -   locator resolved to &lt;button title="Save" aria-pressed="false" aria-label="Sa…&gt;…&lt;/button&gt;[22m
+[2m  - attempting click action[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is not stable[22m
+[2m  - retrying click action, attempt #1[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is not stable[22m
+[2m  - retrying click action, attempt #2[22m
+[2m  -   waiting 20ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is not stable[22m
+[2m  - retrying click action, attempt #3[22m
+[2m  -   waiting 100ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is not stable[22m
+[2m  - retrying click action, attempt #4[22m
+[2m  -   waiting 100ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is not stable[22m
+[2m  - retrying click action, attempt #5[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is not stable[22m
+[2m  - retrying click action, attempt #6[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is not stable[22m
+[2m  - retrying click action, attempt #7[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is not stable[22m
+[2m  - retrying click action, attempt #8[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is not stable[22m
+[2m  - retrying click action, attempt #9[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is not stable[22m
+[2m  - retrying click action, attempt #10[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is not stable[22m
+[2m  - retrying click action, attempt #11[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is not stable[22m
+[2m  - retrying click action, attempt #12[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is not stable[22m
+[2m  - retrying click action, attempt #13[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is not stable[22m
+[2m  - retrying click action, attempt #14[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is not stable[22m
+[2m  - retrying click action, attempt #15[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is not stable[22m
+[2m  - retrying click action, attempt #16[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is not stable[22m
+[2m  - retrying click action, attempt #17[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is not stable[22m
+[2m  - retrying click action, attempt #18[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is not stable[22m
+[2m  - retrying click action, attempt #19[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is not stable[22m
+[2m  - retrying click action, attempt #20[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is not stable[22m
+[2m  - retrying click action, attempt #21[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is not stable[22m
+[2m  - retrying click action, attempt #22[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is not stable[22m
+[2m  - retrying click action, attempt #23[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is not stable[22m
+[2m  - retrying click action, attempt #24[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is not stable[22m
+[2m  - retrying click action, attempt #25[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is not stable[22m
+[2m  - retrying click action, attempt #26[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is not stable[22m
+[2m  - retrying click action, attempt #27[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is not stable[22m
+[2m  - retrying click action, attempt #28[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is not stable[22m
+[2m  - retrying click action, attempt #29[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is not stable[22m
+[2m  - retrying click action, attempt #30[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is not stable[22m
+[2m  - retrying click action, attempt #31[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is not stable[22m
+[2m  - retrying click action, attempt #32[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is not stable[22m
+[2m  - retrying click action, attempt #33[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is not stable[22m
+[2m  - retrying click action, attempt #34[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is not stable[22m
+[2m  - retrying click action, attempt #35[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is not stable[22m
+[2m  - retrying click action, attempt #36[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is not stable[22m
+[2m  - retrying click action, attempt #37[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is not stable[22m
+[2m  - retrying click action, attempt #38[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is not stable[22m
+[2m  - retrying click action, attempt #39[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is not stable[22m
+[2m  - retrying click action, attempt #40[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is not stable[22m
+[2m  - retrying click action, attempt #41[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is not stable[22m
+[2m  - retrying click action, attempt #42[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is not stable[22m
+[2m  - retrying click action, attempt #43[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is not stable[22m
+[2m  - retrying click action, attempt #44[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is not stable[22m
+[2m  - retrying click action, attempt #45[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is not stable[22m
+[2m  - retrying click action, attempt #46[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is not stable[22m
+[2m  - retrying click action, attempt #47[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is not stable[22m
+[2m  - retrying click action, attempt #48[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is not stable[22m
+[2m  - retrying click action, attempt #49[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is not stable[22m
+[2m  - retrying click action, attempt #50[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is not stable[22m
+[2m  - retrying click action, attempt #51[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is not stable[22m
+[2m  - retrying click action, attempt #52[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is not stable[22m
+[2m  - retrying click action, attempt #53[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is not stable[22m
+[2m  - retrying click action, attempt #54[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is not stable[22m
+[2m  - retrying click action, attempt #55[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is not stable[22m
+[2m  - retrying click action, attempt #56[22m
+[2m  -   waiting 500ms[22m
+</t>
+  </si>
+  <si>
+    <t>Hosea</t>
+  </si>
+  <si>
+    <t>Hickle</t>
+  </si>
+  <si>
+    <t>Auto 82482604</t>
+  </si>
+  <si>
+    <t>In-Store P&amp;C Manager_NEW</t>
+  </si>
+  <si>
+    <t>Test_8</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Test failed for 'Cheyenne Weber' Employee:{}TimeoutError: locator.click: Timeout 30000ms exceeded.
+Call log:
+  [2m- waiting for getByLabel('My Tasks Items')[22m
+[2m  -   locator resolved to &lt;button class="wdappchrome-w" data-automation-id="inbox_…&gt;…&lt;/button&gt;[22m
+[2m  - attempting click action[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is not visible[22m
+[2m  - retrying click action, attempt #1[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is not visible[22m
+[2m  - retrying click action, attempt #2[22m
+[2m  -   waiting 20ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is not visible[22m
+[2m  - retrying click action, attempt #3[22m
+[2m  -   waiting 100ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is not visible[22m
+[2m  - retrying click action, attempt #4[22m
+[2m  -   waiting 100ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is not visible[22m
+[2m  - retrying click action, attempt #5[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is not visible[22m
+[2m  - retrying click action, attempt #6[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is not visible[22m
+[2m  - retrying click action, attempt #7[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is not visible[22m
+[2m  - retrying click action, attempt #8[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is not visible[22m
+[2m  - retrying click action, attempt #9[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is not visible[22m
+[2m  - retrying click action, attempt #10[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is not visible[22m
+[2m  - retrying click action, attempt #11[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is not visible[22m
+[2m  - retrying click action, attempt #12[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is not visible[22m
+[2m  - retrying click action, attempt #13[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is not visible[22m
+[2m  - retrying click action, attempt #14[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is not visible[22m
+[2m  - retrying click action, attempt #15[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is not visible[22m
+[2m  - retrying click action, attempt #16[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is not visible[22m
+[2m  - retrying click action, attempt #17[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is not visible[22m
+[2m  - retrying click action, attempt #18[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is not visible[22m
+[2m  - retrying click action, attempt #19[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is not visible[22m
+[2m  - retrying click action, attempt #20[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is not visible[22m
+[2m  - retrying click action, attempt #21[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is not visible[22m
+[2m  - retrying click action, attempt #22[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is not visible[22m
+[2m  - retrying click action, attempt #23[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is not visible[22m
+[2m  - retrying click action, attempt #24[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is not visible[22m
+[2m  - retrying click action, attempt #25[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is not visible[22m
+[2m  - retrying click action, attempt #26[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is not visible[22m
+[2m  - retrying click action, attempt #27[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is not visible[22m
+[2m  - retrying click action, attempt #28[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is not visible[22m
+[2m  - retrying click action, attempt #29[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is not visible[22m
+[2m  - retrying click action, attempt #30[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is not visible[22m
+[2m  - retrying click action, attempt #31[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is not visible[22m
+[2m  - retrying click action, attempt #32[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is not visible[22m
+[2m  - retrying click action, attempt #33[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is not visible[22m
+[2m  - retrying click action, attempt #34[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is not visible[22m
+[2m  - retrying click action, attempt #35[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is not visible[22m
+[2m  - retrying click action, attempt #36[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is not visible[22m
+[2m  - retrying click action, attempt #37[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is not visible[22m
+[2m  - retrying click action, attempt #38[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is not visible[22m
+[2m  - retrying click action, attempt #39[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is not visible[22m
+[2m  - retrying click action, attempt #40[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is not visible[22m
+[2m  - retrying click action, attempt #41[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is not visible[22m
+[2m  - retrying click action, attempt #42[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is not visible[22m
+[2m  - retrying click action, attempt #43[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is not visible[22m
+[2m  - retrying click action, attempt #44[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is not visible[22m
+[2m  - retrying click action, attempt #45[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is not visible[22m
+[2m  - retrying click action, attempt #46[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is not visible[22m
+[2m  - retrying click action, attempt #47[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is not visible[22m
+[2m  - retrying click action, attempt #48[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is not visible[22m
+[2m  - retrying click action, attempt #49[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is not visible[22m
+[2m  - retrying click action, attempt #50[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is not visible[22m
+[2m  - retrying click action, attempt #51[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is not visible[22m
+[2m  - retrying click action, attempt #52[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is not visible[22m
+[2m  - retrying click action, attempt #53[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is not visible[22m
+[2m  - retrying click action, attempt #54[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is not visible[22m
+[2m  - retrying click action, attempt #55[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is not visible[22m
+[2m  - retrying click action, attempt #56[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is not visible[22m
+[2m  - retrying click action, attempt #57[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is not visible[22m
+[2m  - retrying click action, attempt #58[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is not visible[22m
+[2m  - retrying click action, attempt #59[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is not visible[22m
+[2m  - retrying click action, attempt #60[22m
+[2m  -   waiting 500ms[22m
+</t>
+  </si>
+  <si>
+    <t>Cheyenne</t>
+  </si>
+  <si>
+    <t>Weber</t>
+  </si>
+  <si>
+    <t>Auto 66233751</t>
+  </si>
+  <si>
+    <t>Visual Merchandising Manager_NEW</t>
+  </si>
+  <si>
+    <t>Test_9</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Test failed for 'Euna Schulist' Employee:{}TimeoutError: locator.click: Timeout 30000ms exceeded.
+Call log:
+  [2m- waiting for locator('[aria-label="Save Other"]')[22m
+[2m  -   locator resolved to &lt;button title="Save" aria-pressed="false" aria-label="Sa…&gt;…&lt;/button&gt;[22m
+[2m  - attempting click action[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is not stable[22m
+[2m  - retrying click action, attempt #1[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is not stable[22m
+[2m  - retrying click action, attempt #2[22m
+[2m  -   waiting 20ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is not stable[22m
+[2m  - retrying click action, attempt #3[22m
+[2m  -   waiting 100ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is not stable[22m
+[2m  - retrying click action, attempt #4[22m
+[2m  -   waiting 100ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is not stable[22m
+[2m  - retrying click action, attempt #5[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is not stable[22m
+[2m  - retrying click action, attempt #6[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is not stable[22m
+[2m  - retrying click action, attempt #7[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is not stable[22m
+[2m  - retrying click action, attempt #8[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is not stable[22m
+[2m  - retrying click action, attempt #9[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is not stable[22m
+[2m  - retrying click action, attempt #10[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is not stable[22m
+[2m  - retrying click action, attempt #11[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is not stable[22m
+[2m  - retrying click action, attempt #12[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is not stable[22m
+[2m  - retrying click action, attempt #13[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is not stable[22m
+[2m  - retrying click action, attempt #14[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is not stable[22m
+[2m  - retrying click action, attempt #15[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is not stable[22m
+[2m  - retrying click action, attempt #16[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is not stable[22m
+[2m  - retrying click action, attempt #17[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is not stable[22m
+[2m  - retrying click action, attempt #18[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is not stable[22m
+[2m  - retrying click action, attempt #19[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is not stable[22m
+[2m  - retrying click action, attempt #20[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is not stable[22m
+[2m  - retrying click action, attempt #21[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is not stable[22m
+[2m  - retrying click action, attempt #22[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is not stable[22m
+[2m  - retrying click action, attempt #23[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is not stable[22m
+[2m  - retrying click action, attempt #24[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is not stable[22m
+[2m  - retrying click action, attempt #25[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is not stable[22m
+[2m  - retrying click action, attempt #26[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is not stable[22m
+[2m  - retrying click action, attempt #27[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is not stable[22m
+[2m  - retrying click action, attempt #28[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is not stable[22m
+[2m  - retrying click action, attempt #29[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is not stable[22m
+[2m  - retrying click action, attempt #30[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is not stable[22m
+[2m  - retrying click action, attempt #31[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is not stable[22m
+[2m  - retrying click action, attempt #32[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is not stable[22m
+[2m  - retrying click action, attempt #33[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is not stable[22m
+[2m  - retrying click action, attempt #34[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is not stable[22m
+[2m  - retrying click action, attempt #35[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is not stable[22m
+[2m  - retrying click action, attempt #36[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is not stable[22m
+[2m  - retrying click action, attempt #37[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is not stable[22m
+[2m  - retrying click action, attempt #38[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is not stable[22m
+[2m  - retrying click action, attempt #39[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is not stable[22m
+[2m  - retrying click action, attempt #40[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is not stable[22m
+[2m  - retrying click action, attempt #41[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is not stable[22m
+[2m  - retrying click action, attempt #42[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is not stable[22m
+[2m  - retrying click action, attempt #43[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is not stable[22m
+[2m  - retrying click action, attempt #44[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is not stable[22m
+[2m  - retrying click action, attempt #45[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is not stable[22m
+[2m  - retrying click action, attempt #46[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is not stable[22m
+[2m  - retrying click action, attempt #47[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is not stable[22m
+[2m  - retrying click action, attempt #48[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is not stable[22m
+[2m  - retrying click action, attempt #49[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is not stable[22m
+[2m  - retrying click action, attempt #50[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is not stable[22m
+[2m  - retrying click action, attempt #51[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is not stable[22m
+[2m  - retrying click action, attempt #52[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is not stable[22m
+[2m  - retrying click action, attempt #53[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is not stable[22m
+[2m  - retrying click action, attempt #54[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is not stable[22m
+[2m  - retrying click action, attempt #55[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is not stable[22m
+[2m  - retrying click action, attempt #56[22m
+[2m  -   waiting 500ms[22m
+</t>
+  </si>
+  <si>
+    <t>Euna</t>
+  </si>
+  <si>
+    <t>Schulist</t>
+  </si>
+  <si>
+    <t>Auto 74632106</t>
+  </si>
+  <si>
+    <t>Team Manager - Retail_NEW</t>
+  </si>
+  <si>
+    <t>Test_10</t>
+  </si>
+  <si>
+    <t>Test failed for 'Matt Runte' Employee:{}TypeError: Cannot read properties of undefined (reading 'toString')</t>
+  </si>
+  <si>
+    <t>Matt</t>
+  </si>
+  <si>
+    <t>Runte</t>
+  </si>
+  <si>
+    <t>In-Store P&amp;C Assistant_NEW</t>
+  </si>
+  <si>
+    <t>Part</t>
+  </si>
+  <si>
+    <t>250 Human Resources Retail</t>
+  </si>
+  <si>
+    <t>Test_11</t>
+  </si>
+  <si>
+    <t>Test failed for 'Rachael Parker' Employee:{}TypeError: Cannot read properties of undefined (reading 'toString')</t>
+  </si>
+  <si>
+    <t>Rachael</t>
+  </si>
+  <si>
+    <t>Parker</t>
+  </si>
+  <si>
+    <t>In-Store Visual Merchandising Supervisor_NEW</t>
+  </si>
+  <si>
+    <t>256 Visual Merchandising</t>
+  </si>
+  <si>
+    <t>Test_12</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Test failed for 'Jaylen Schmitt' Employee:{10651895}TimeoutError: locator.click: Timeout 30000ms exceeded.
+Call log:
+  [2m- waiting for getByRole('button', { name: 'USA Employee Handbook: Retail' })[22m
+</t>
+  </si>
+  <si>
+    <t>Jaylen</t>
+  </si>
+  <si>
+    <t>Schmitt</t>
+  </si>
+  <si>
+    <t>Supervisor_NEW</t>
+  </si>
+  <si>
+    <t>253 Supervisors</t>
+  </si>
+  <si>
+    <t>Test_13</t>
+  </si>
+  <si>
+    <t>Test failed for 'Israel Will' Employee:{}TypeError: Cannot read properties of undefined (reading 'toString')</t>
+  </si>
+  <si>
+    <t>Israel</t>
+  </si>
+  <si>
+    <t>Will</t>
+  </si>
+  <si>
+    <t>In-Store Visual Merchandising Assistant_NEW</t>
+  </si>
+  <si>
+    <t>Test_14</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Test failed for 'Archibald Hahn' Employee:{}TimeoutError: locator.click: Timeout 30000ms exceeded.
+Call log:
+  [2m- waiting for getByLabel('My Tasks Items')[22m
+[2m  -   locator resolved to &lt;button class="wdappchrome-w" data-automation-id="inbox_…&gt;…&lt;/button&gt;[22m
+[2m  - attempting click action[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is not visible[22m
+[2m  - retrying click action, attempt #1[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is not visible[22m
+[2m  - retrying click action, attempt #2[22m
+[2m  -   waiting 20ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is not visible[22m
+[2m  - retrying click action, attempt #3[22m
+[2m  -   waiting 100ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is not visible[22m
+[2m  - retrying click action, attempt #4[22m
+[2m  -   waiting 100ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is not visible[22m
+[2m  - retrying click action, attempt #5[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is not visible[22m
+[2m  - retrying click action, attempt #6[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is not visible[22m
+[2m  - retrying click action, attempt #7[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is not visible[22m
+[2m  - retrying click action, attempt #8[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is not visible[22m
+[2m  - retrying click action, attempt #9[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is not visible[22m
+[2m  - retrying click action, attempt #10[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is not visible[22m
+[2m  - retrying click action, attempt #11[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is not visible[22m
+[2m  - retrying click action, attempt #12[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is not visible[22m
+[2m  - retrying click action, attempt #13[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is not visible[22m
+[2m  - retrying click action, attempt #14[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is not visible[22m
+[2m  - retrying click action, attempt #15[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is not visible[22m
+[2m  - retrying click action, attempt #16[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is not visible[22m
+[2m  - retrying click action, attempt #17[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is not visible[22m
+[2m  - retrying click action, attempt #18[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is not visible[22m
+[2m  - retrying click action, attempt #19[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is not visible[22m
+[2m  - retrying click action, attempt #20[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is not visible[22m
+[2m  - retrying click action, attempt #21[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is not visible[22m
+[2m  - retrying click action, attempt #22[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is not visible[22m
+[2m  - retrying click action, attempt #23[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is not visible[22m
+[2m  - retrying click action, attempt #24[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is not visible[22m
+[2m  - retrying click action, attempt #25[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is not visible[22m
+[2m  - retrying click action, attempt #26[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is not visible[22m
+[2m  - retrying click action, attempt #27[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is not visible[22m
+[2m  - retrying click action, attempt #28[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is not visible[22m
+[2m  - retrying click action, attempt #29[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is not visible[22m
+[2m  - retrying click action, attempt #30[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is not visible[22m
+[2m  - retrying click action, attempt #31[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is not visible[22m
+[2m  - retrying click action, attempt #32[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is not visible[22m
+[2m  - retrying click action, attempt #33[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is not visible[22m
+[2m  - retrying click action, attempt #34[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is not visible[22m
+[2m  - retrying click action, attempt #35[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is not visible[22m
+[2m  - retrying click action, attempt #36[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is not visible[22m
+[2m  - retrying click action, attempt #37[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is not visible[22m
+[2m  - retrying click action, attempt #38[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is not visible[22m
+[2m  - retrying click action, attempt #39[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is not visible[22m
+[2m  - retrying click action, attempt #40[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is not visible[22m
+[2m  - retrying click action, attempt #41[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is not visible[22m
+[2m  - retrying click action, attempt #42[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is not visible[22m
+[2m  - retrying click action, attempt #43[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is not visible[22m
+[2m  - retrying click action, attempt #44[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is not visible[22m
+[2m  - retrying click action, attempt #45[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is not visible[22m
+[2m  - retrying click action, attempt #46[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is not visible[22m
+[2m  - retrying click action, attempt #47[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is not visible[22m
+[2m  - retrying click action, attempt #48[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is not visible[22m
+[2m  - retrying click action, attempt #49[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is not visible[22m
+[2m  - retrying click action, attempt #50[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is not visible[22m
+[2m  - retrying click action, attempt #51[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is not visible[22m
+[2m  - retrying click action, attempt #52[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is not visible[22m
+[2m  - retrying click action, attempt #53[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is not visible[22m
+[2m  - retrying click action, attempt #54[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is not visible[22m
+[2m  - retrying click action, attempt #55[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is not visible[22m
+[2m  - retrying click action, attempt #56[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is not visible[22m
+[2m  - retrying click action, attempt #57[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is not visible[22m
+[2m  - retrying click action, attempt #58[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is not visible[22m
+[2m  - retrying click action, attempt #59[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is not visible[22m
+[2m  - retrying click action, attempt #60[22m
+[2m  -   waiting 500ms[22m
+</t>
+  </si>
+  <si>
+    <t>Archibald</t>
+  </si>
+  <si>
+    <t>Hahn</t>
+  </si>
+  <si>
+    <t>Cash Office Operative_NEW</t>
+  </si>
+  <si>
+    <t>258 Cash Office</t>
+  </si>
+  <si>
+    <t>Test_15</t>
+  </si>
+  <si>
+    <t>10651897</t>
+  </si>
+  <si>
+    <t>Juliet</t>
+  </si>
+  <si>
+    <t>Pfannerstill</t>
+  </si>
+  <si>
+    <t>Test_16</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Test failed for 'Reggie Altenwerth' Employee:{}TimeoutError: locator.click: Timeout 30000ms exceeded.
+Call log:
+  [2m- waiting for getByLabel('My Tasks Items')[22m
+[2m  -   locator resolved to &lt;button class="wdappchrome-w" data-automation-id="inbox_…&gt;…&lt;/button&gt;[22m
+[2m  - attempting click action[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is not visible[22m
+[2m  - retrying click action, attempt #1[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is not visible[22m
+[2m  - retrying click action, attempt #2[22m
+[2m  -   waiting 20ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is not visible[22m
+[2m  - retrying click action, attempt #3[22m
+[2m  -   waiting 100ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is not visible[22m
+[2m  - retrying click action, attempt #4[22m
+[2m  -   waiting 100ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is not visible[22m
+[2m  - retrying click action, attempt #5[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is not visible[22m
+[2m  - retrying click action, attempt #6[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is not visible[22m
+[2m  - retrying click action, attempt #7[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is not visible[22m
+[2m  - retrying click action, attempt #8[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is not visible[22m
+[2m  - retrying click action, attempt #9[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is not visible[22m
+[2m  - retrying click action, attempt #10[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is not visible[22m
+[2m  - retrying click action, attempt #11[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is not visible[22m
+[2m  - retrying click action, attempt #12[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is not visible[22m
+[2m  - retrying click action, attempt #13[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is not visible[22m
+[2m  - retrying click action, attempt #14[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is not visible[22m
+[2m  - retrying click action, attempt #15[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is not visible[22m
+[2m  - retrying click action, attempt #16[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is not visible[22m
+[2m  - retrying click action, attempt #17[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is not visible[22m
+[2m  - retrying click action, attempt #18[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is not visible[22m
+[2m  - retrying click action, attempt #19[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is not visible[22m
+[2m  - retrying click action, attempt #20[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is not visible[22m
+[2m  - retrying click action, attempt #21[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is not visible[22m
+[2m  - retrying click action, attempt #22[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is not visible[22m
+[2m  - retrying click action, attempt #23[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is not visible[22m
+[2m  - retrying click action, attempt #24[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is not visible[22m
+[2m  - retrying click action, attempt #25[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is not visible[22m
+[2m  - retrying click action, attempt #26[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is not visible[22m
+[2m  - retrying click action, attempt #27[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is not visible[22m
+[2m  - retrying click action, attempt #28[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is not visible[22m
+[2m  - retrying click action, attempt #29[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is not visible[22m
+[2m  - retrying click action, attempt #30[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is not visible[22m
+[2m  - retrying click action, attempt #31[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is not visible[22m
+[2m  - retrying click action, attempt #32[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is not visible[22m
+[2m  - retrying click action, attempt #33[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is not visible[22m
+[2m  - retrying click action, attempt #34[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is not visible[22m
+[2m  - retrying click action, attempt #35[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is not visible[22m
+[2m  - retrying click action, attempt #36[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is not visible[22m
+[2m  - retrying click action, attempt #37[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is not visible[22m
+[2m  - retrying click action, attempt #38[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is not visible[22m
+[2m  - retrying click action, attempt #39[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is not visible[22m
+[2m  - retrying click action, attempt #40[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is not visible[22m
+[2m  - retrying click action, attempt #41[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is not visible[22m
+[2m  - retrying click action, attempt #42[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is not visible[22m
+[2m  - retrying click action, attempt #43[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is not visible[22m
+[2m  - retrying click action, attempt #44[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is not visible[22m
+[2m  - retrying click action, attempt #45[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is not visible[22m
+[2m  - retrying click action, attempt #46[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is not visible[22m
+[2m  - retrying click action, attempt #47[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is not visible[22m
+[2m  - retrying click action, attempt #48[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is not visible[22m
+[2m  - retrying click action, attempt #49[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is not visible[22m
+[2m  - retrying click action, attempt #50[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is not visible[22m
+[2m  - retrying click action, attempt #51[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is not visible[22m
+[2m  - retrying click action, attempt #52[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is not visible[22m
+[2m  - retrying click action, attempt #53[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is not visible[22m
+[2m  - retrying click action, attempt #54[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is not visible[22m
+[2m  - retrying click action, attempt #55[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is not visible[22m
+[2m  - retrying click action, attempt #56[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is not visible[22m
+[2m  - retrying click action, attempt #57[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is not visible[22m
+[2m  - retrying click action, attempt #58[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is not visible[22m
+[2m  - retrying click action, attempt #59[22m
+[2m  -   waiting 500ms[22m
+</t>
+  </si>
+  <si>
+    <t>Reggie</t>
+  </si>
+  <si>
+    <t>Altenwerth</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="1">
-    <numFmt numFmtId="164" formatCode="mm/dd/yyyy"/>
-  </numFmts>
-  <fonts count="7" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -318,33 +2847,8 @@
       <name val="Arial"/>
       <family val="2"/>
     </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF040C28"/>
-      <name val="Arial"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color theme="10"/>
-      <name val="Arial"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF4A4A4A"/>
-      <name val="Arial"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color indexed="8"/>
-      <name val="Arial"/>
-      <family val="2"/>
-    </font>
   </fonts>
-  <fills count="5">
+  <fills count="6">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -364,12 +2868,17 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FF00FF00"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="5" tint="0.79998168889431442"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
   </fills>
-  <borders count="7">
+  <borders count="5">
     <border>
       <left/>
       <right/>
@@ -433,35 +2942,11 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left style="medium">
-        <color indexed="64"/>
-      </left>
-      <right style="medium">
-        <color indexed="64"/>
-      </right>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color auto="1"/>
-      </left>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="31">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -479,72 +2964,10 @@
     <xf numFmtId="0" fontId="2" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="14" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyProtection="1">
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="14" fontId="2" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyProtection="1">
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="14" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="164" fontId="2" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="164" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left"/>
-      <protection locked="0"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -826,65 +3249,66 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:BA2"/>
+  <dimension ref="A1:BC18"/>
   <sheetFormatPr defaultRowHeight="14.5" customHeight="1" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="10" customWidth="1"/>
+    <col min="1" max="1" width="7.26953125" customWidth="1"/>
     <col min="2" max="2" width="10.81640625" customWidth="1"/>
     <col min="3" max="3" width="9.36328125" customWidth="1"/>
-    <col min="4" max="4" width="22.6328125" customWidth="1"/>
-    <col min="5" max="5" width="7.6328125" customWidth="1"/>
-    <col min="6" max="6" width="5.90625" customWidth="1"/>
-    <col min="7" max="7" width="11.1796875" customWidth="1"/>
-    <col min="8" max="8" width="11.81640625" customWidth="1"/>
-    <col min="9" max="9" width="13.453125" customWidth="1"/>
-    <col min="10" max="10" width="12.54296875" customWidth="1"/>
-    <col min="11" max="11" width="5.26953125" customWidth="1"/>
-    <col min="12" max="12" width="12.90625" customWidth="1"/>
-    <col min="13" max="13" width="7.6328125" customWidth="1"/>
-    <col min="14" max="14" width="7" customWidth="1"/>
-    <col min="15" max="16" width="11.7265625" customWidth="1"/>
-    <col min="17" max="17" width="11.1796875" customWidth="1"/>
-    <col min="18" max="18" width="4.26953125" customWidth="1"/>
-    <col min="19" max="19" width="5.453125" customWidth="1"/>
-    <col min="20" max="20" width="5.26953125" customWidth="1"/>
-    <col min="21" max="21" width="7.36328125" customWidth="1"/>
-    <col min="22" max="22" width="13.08984375" customWidth="1"/>
-    <col min="23" max="23" width="5.26953125" customWidth="1"/>
-    <col min="24" max="24" width="8.6328125" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="17.1796875" customWidth="1"/>
-    <col min="26" max="26" width="7.6328125" customWidth="1"/>
-    <col min="27" max="27" width="8" customWidth="1"/>
-    <col min="28" max="28" width="14.1796875" customWidth="1"/>
-    <col min="29" max="29" width="9.81640625" customWidth="1"/>
-    <col min="30" max="30" width="9.7265625" customWidth="1"/>
-    <col min="31" max="31" width="8.36328125" customWidth="1"/>
-    <col min="32" max="32" width="13" customWidth="1"/>
-    <col min="33" max="33" width="21.81640625" customWidth="1"/>
-    <col min="34" max="34" width="25.81640625" customWidth="1"/>
-    <col min="35" max="35" width="9.453125" customWidth="1"/>
-    <col min="36" max="36" width="19.54296875" customWidth="1"/>
-    <col min="37" max="37" width="10.36328125" customWidth="1"/>
-    <col min="38" max="38" width="10.81640625" customWidth="1"/>
-    <col min="39" max="39" width="17.81640625" customWidth="1"/>
-    <col min="40" max="40" width="12" customWidth="1"/>
-    <col min="41" max="41" width="4.90625" customWidth="1"/>
-    <col min="42" max="42" width="8.7265625" customWidth="1"/>
-    <col min="43" max="43" width="15.6328125" customWidth="1"/>
-    <col min="44" max="44" width="10.90625" customWidth="1"/>
-    <col min="45" max="45" width="7.26953125" customWidth="1"/>
-    <col min="46" max="46" width="11.1796875" customWidth="1"/>
-    <col min="47" max="47" width="13.90625" customWidth="1"/>
-    <col min="48" max="48" width="14" customWidth="1"/>
-    <col min="49" max="49" width="17" customWidth="1"/>
-    <col min="50" max="50" width="6.36328125" customWidth="1"/>
-    <col min="51" max="51" width="30.453125" customWidth="1"/>
-    <col min="52" max="52" width="15.1796875" customWidth="1"/>
-    <col min="53" max="53" width="22.7265625" customWidth="1"/>
-    <col min="54" max="54" width="8.7265625" customWidth="1"/>
+    <col min="4" max="4" width="22.26953125" customWidth="1"/>
+    <col min="5" max="5" width="29.453125" customWidth="1"/>
+    <col min="6" max="6" width="3.90625" customWidth="1"/>
+    <col min="7" max="7" width="11.7265625" customWidth="1"/>
+    <col min="8" max="8" width="26.1796875" customWidth="1"/>
+    <col min="9" max="9" width="18.90625" customWidth="1"/>
+    <col min="10" max="10" width="10.6328125" customWidth="1"/>
+    <col min="11" max="11" width="7.7265625" customWidth="1"/>
+    <col min="12" max="12" width="14.1796875" customWidth="1"/>
+    <col min="13" max="13" width="29.453125" customWidth="1"/>
+    <col min="14" max="14" width="11.26953125" customWidth="1"/>
+    <col min="15" max="15" width="29.1796875" customWidth="1"/>
+    <col min="16" max="16" width="11.26953125" customWidth="1"/>
+    <col min="17" max="17" width="8.26953125" customWidth="1"/>
+    <col min="18" max="19" width="12" customWidth="1"/>
+    <col min="20" max="20" width="7.7265625" customWidth="1"/>
+    <col min="21" max="21" width="18" customWidth="1"/>
+    <col min="22" max="22" width="31.1796875" customWidth="1"/>
+    <col min="23" max="23" width="7.7265625" customWidth="1"/>
+    <col min="24" max="25" width="14.1796875" customWidth="1"/>
+    <col min="26" max="26" width="11.1796875" customWidth="1"/>
+    <col min="27" max="27" width="28.453125" customWidth="1"/>
+    <col min="28" max="28" width="11.453125" customWidth="1"/>
+    <col min="29" max="29" width="40.54296875" customWidth="1"/>
+    <col min="30" max="30" width="11.1796875" customWidth="1"/>
+    <col min="31" max="31" width="5.36328125" customWidth="1"/>
+    <col min="32" max="32" width="8.1796875" customWidth="1"/>
+    <col min="33" max="33" width="6.08984375" customWidth="1"/>
+    <col min="34" max="34" width="83.26953125" customWidth="1"/>
+    <col min="35" max="35" width="52.7265625" customWidth="1"/>
+    <col min="36" max="36" width="5.26953125" customWidth="1"/>
+    <col min="37" max="37" width="36.54296875" customWidth="1"/>
+    <col min="38" max="38" width="27.6328125" customWidth="1"/>
+    <col min="39" max="39" width="29.08984375" customWidth="1"/>
+    <col min="40" max="40" width="24.36328125" customWidth="1"/>
+    <col min="41" max="41" width="21.36328125" customWidth="1"/>
+    <col min="42" max="42" width="29.453125" customWidth="1"/>
+    <col min="43" max="43" width="35.6328125" customWidth="1"/>
+    <col min="44" max="44" width="10.6328125" customWidth="1"/>
+    <col min="45" max="45" width="6.36328125" customWidth="1"/>
+    <col min="46" max="46" width="14.1796875" customWidth="1"/>
+    <col min="47" max="47" width="29.453125" customWidth="1"/>
+    <col min="48" max="48" width="66.54296875" customWidth="1"/>
+    <col min="49" max="49" width="29.453125" customWidth="1"/>
+    <col min="50" max="50" width="11.7265625" customWidth="1"/>
+    <col min="51" max="51" width="10.6328125" customWidth="1"/>
+    <col min="52" max="52" width="8.81640625" customWidth="1"/>
+    <col min="53" max="53" width="28.453125" customWidth="1"/>
+    <col min="54" max="54" width="50.90625" customWidth="1"/>
+    <col min="55" max="55" width="19.26953125" customWidth="1"/>
+    <col min="56" max="56" width="8.7265625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:53" s="1" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:55" s="1" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1044,182 +3468,2783 @@
       <c r="BA1" s="3" t="s">
         <v>49</v>
       </c>
+      <c r="BB1" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="BC1" s="3" t="s">
+        <v>51</v>
+      </c>
     </row>
-    <row r="2" spans="1:53" ht="36" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:55" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
+        <v>52</v>
+      </c>
+      <c r="B2" t="s">
+        <v>53</v>
+      </c>
+      <c r="C2" s="7" t="s">
+        <v>54</v>
+      </c>
+      <c r="D2" t="s">
+        <v>55</v>
+      </c>
+      <c r="E2" t="s">
+        <v>56</v>
+      </c>
+      <c r="F2" t="s">
+        <v>57</v>
+      </c>
+      <c r="G2" t="s">
+        <v>58</v>
+      </c>
+      <c r="H2" t="s">
+        <v>59</v>
+      </c>
+      <c r="I2" t="s">
+        <v>60</v>
+      </c>
+      <c r="J2" t="s">
+        <v>61</v>
+      </c>
+      <c r="K2" t="s">
+        <v>62</v>
+      </c>
+      <c r="L2">
+        <f t="shared" ref="L2:L17" ca="1" si="0">TODAY()-31</f>
+        <v>45563</v>
+      </c>
+      <c r="M2" t="s">
+        <v>56</v>
+      </c>
+      <c r="N2" t="s">
+        <v>63</v>
+      </c>
+      <c r="O2" t="s">
+        <v>64</v>
+      </c>
+      <c r="P2" t="s">
+        <v>63</v>
+      </c>
+      <c r="Q2">
+        <v>21201</v>
+      </c>
+      <c r="R2" t="s">
+        <v>65</v>
+      </c>
+      <c r="S2" t="s">
+        <v>65</v>
+      </c>
+      <c r="T2" t="s">
+        <v>62</v>
+      </c>
+      <c r="U2" t="s">
+        <v>66</v>
+      </c>
+      <c r="V2" t="s">
+        <v>67</v>
+      </c>
+      <c r="W2" t="s">
+        <v>62</v>
+      </c>
+      <c r="X2">
+        <f t="shared" ref="X2:X17" ca="1" si="1">L2</f>
+        <v>45563</v>
+      </c>
+      <c r="Y2">
+        <f t="shared" ref="Y2:Y17" ca="1" si="2">TODAY()+20</f>
+        <v>45614</v>
+      </c>
+      <c r="Z2" t="s">
+        <v>68</v>
+      </c>
+      <c r="AA2" t="s">
+        <v>69</v>
+      </c>
+      <c r="AB2" t="s">
+        <v>70</v>
+      </c>
+      <c r="AC2" t="s">
+        <v>71</v>
+      </c>
+      <c r="AD2" t="s">
+        <v>72</v>
+      </c>
+      <c r="AE2">
+        <v>121</v>
+      </c>
+      <c r="AF2" t="s">
+        <v>73</v>
+      </c>
+      <c r="AG2">
+        <v>10</v>
+      </c>
+      <c r="AH2" t="s">
+        <v>74</v>
+      </c>
+      <c r="AI2" t="s">
+        <v>75</v>
+      </c>
+      <c r="AJ2" t="s">
+        <v>76</v>
+      </c>
+      <c r="AK2" t="s">
+        <v>77</v>
+      </c>
+      <c r="AL2" t="s">
+        <v>78</v>
+      </c>
+      <c r="AM2" t="s">
+        <v>79</v>
+      </c>
+      <c r="AN2" t="s">
+        <v>80</v>
+      </c>
+      <c r="AO2" t="s">
+        <v>76</v>
+      </c>
+      <c r="AP2" t="s">
+        <v>56</v>
+      </c>
+      <c r="AQ2" t="s">
+        <v>81</v>
+      </c>
+      <c r="AR2">
+        <f t="array" aca="1" ref="AR2:AR17" ca="1">_xlfn.RANDARRAY(16,1,123456789,999999999,FALSE)</f>
+        <v>844100754.75221956</v>
+      </c>
+      <c r="AS2" t="s">
+        <v>82</v>
+      </c>
+      <c r="AT2">
+        <v>35226</v>
+      </c>
+      <c r="AU2" t="s">
+        <v>56</v>
+      </c>
+      <c r="AV2" t="s">
+        <v>83</v>
+      </c>
+      <c r="AW2" t="s">
+        <v>56</v>
+      </c>
+      <c r="AX2" t="s">
+        <v>84</v>
+      </c>
+      <c r="AY2">
+        <v>54057</v>
+      </c>
+      <c r="AZ2" t="s">
+        <v>63</v>
+      </c>
+      <c r="BA2" t="s">
         <v>85</v>
       </c>
-      <c r="B2" s="7" t="s">
-        <v>50</v>
-      </c>
-      <c r="C2" s="8" t="s">
-        <v>51</v>
-      </c>
-      <c r="D2" s="9" t="s">
-        <v>52</v>
-      </c>
-      <c r="E2" s="10" t="s">
-        <v>53</v>
-      </c>
-      <c r="F2" s="11" t="s">
+      <c r="BB2" t="s">
+        <v>86</v>
+      </c>
+      <c r="BC2" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="3" spans="1:55" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A3" t="s">
+        <v>88</v>
+      </c>
+      <c r="B3" t="s">
+        <v>89</v>
+      </c>
+      <c r="C3" s="7" t="s">
         <v>54</v>
       </c>
-      <c r="G2" s="12" t="s">
-        <v>55</v>
-      </c>
-      <c r="H2" s="13" t="s">
-        <v>56</v>
-      </c>
-      <c r="I2" s="14" t="s">
+      <c r="D3" t="s">
+        <v>90</v>
+      </c>
+      <c r="E3" t="s">
+        <v>56</v>
+      </c>
+      <c r="F3" t="s">
         <v>57</v>
       </c>
-      <c r="J2" s="14" t="s">
-        <v>58</v>
-      </c>
-      <c r="K2" s="14" t="s">
-        <v>59</v>
-      </c>
-      <c r="L2" s="15">
-        <f ca="1">TODAY()-31</f>
-        <v>45562</v>
-      </c>
-      <c r="M2" s="10" t="s">
-        <v>53</v>
-      </c>
-      <c r="N2" s="16" t="s">
+      <c r="G3" t="s">
+        <v>91</v>
+      </c>
+      <c r="H3" t="s">
+        <v>92</v>
+      </c>
+      <c r="I3" t="s">
         <v>60</v>
       </c>
-      <c r="O2" s="16" t="s">
+      <c r="J3" t="s">
         <v>61</v>
       </c>
-      <c r="P2" s="16" t="s">
+      <c r="K3" t="s">
+        <v>62</v>
+      </c>
+      <c r="L3">
+        <f t="shared" ca="1" si="0"/>
+        <v>45563</v>
+      </c>
+      <c r="M3" t="s">
+        <v>56</v>
+      </c>
+      <c r="N3" t="s">
+        <v>63</v>
+      </c>
+      <c r="O3" t="s">
+        <v>64</v>
+      </c>
+      <c r="P3" t="s">
+        <v>63</v>
+      </c>
+      <c r="Q3">
+        <v>21201</v>
+      </c>
+      <c r="R3" t="s">
+        <v>65</v>
+      </c>
+      <c r="S3" t="s">
+        <v>65</v>
+      </c>
+      <c r="T3" t="s">
+        <v>62</v>
+      </c>
+      <c r="U3" t="s">
+        <v>66</v>
+      </c>
+      <c r="V3" t="s">
+        <v>67</v>
+      </c>
+      <c r="W3" t="s">
+        <v>62</v>
+      </c>
+      <c r="X3">
+        <f t="shared" ca="1" si="1"/>
+        <v>45563</v>
+      </c>
+      <c r="Y3">
+        <f t="shared" ca="1" si="2"/>
+        <v>45614</v>
+      </c>
+      <c r="Z3" t="s">
+        <v>68</v>
+      </c>
+      <c r="AA3" t="s">
+        <v>69</v>
+      </c>
+      <c r="AB3" t="s">
+        <v>93</v>
+      </c>
+      <c r="AC3" t="s">
+        <v>71</v>
+      </c>
+      <c r="AD3" t="s">
+        <v>94</v>
+      </c>
+      <c r="AE3">
+        <v>121</v>
+      </c>
+      <c r="AF3" t="s">
+        <v>73</v>
+      </c>
+      <c r="AG3">
+        <v>37.5</v>
+      </c>
+      <c r="AH3" t="s">
+        <v>74</v>
+      </c>
+      <c r="AI3" t="s">
+        <v>75</v>
+      </c>
+      <c r="AJ3" t="s">
+        <v>76</v>
+      </c>
+      <c r="AK3" t="s">
+        <v>77</v>
+      </c>
+      <c r="AL3" t="s">
+        <v>78</v>
+      </c>
+      <c r="AM3" t="s">
+        <v>95</v>
+      </c>
+      <c r="AN3" t="s">
+        <v>80</v>
+      </c>
+      <c r="AO3" t="s">
+        <v>76</v>
+      </c>
+      <c r="AP3" t="s">
+        <v>56</v>
+      </c>
+      <c r="AQ3" t="s">
+        <v>81</v>
+      </c>
+      <c r="AR3">
+        <f ca="1"/>
+        <v>978941583.73973286</v>
+      </c>
+      <c r="AS3" t="s">
+        <v>82</v>
+      </c>
+      <c r="AT3">
+        <v>35591</v>
+      </c>
+      <c r="AU3" t="s">
+        <v>56</v>
+      </c>
+      <c r="AV3" t="s">
+        <v>83</v>
+      </c>
+      <c r="AW3" t="s">
+        <v>56</v>
+      </c>
+      <c r="AX3" t="s">
+        <v>84</v>
+      </c>
+      <c r="AY3">
+        <v>54057</v>
+      </c>
+      <c r="AZ3" t="s">
+        <v>63</v>
+      </c>
+      <c r="BA3" t="s">
+        <v>85</v>
+      </c>
+      <c r="BB3" t="s">
+        <v>86</v>
+      </c>
+      <c r="BC3" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="4" spans="1:55" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A4" t="s">
+        <v>96</v>
+      </c>
+      <c r="B4" t="s">
+        <v>97</v>
+      </c>
+      <c r="C4" s="7" t="s">
+        <v>54</v>
+      </c>
+      <c r="D4" t="s">
+        <v>98</v>
+      </c>
+      <c r="E4" t="s">
+        <v>56</v>
+      </c>
+      <c r="F4" t="s">
+        <v>57</v>
+      </c>
+      <c r="G4" t="s">
+        <v>99</v>
+      </c>
+      <c r="H4" t="s">
+        <v>100</v>
+      </c>
+      <c r="I4" t="s">
         <v>60</v>
       </c>
-      <c r="Q2" s="17">
+      <c r="J4" t="s">
+        <v>61</v>
+      </c>
+      <c r="K4" t="s">
+        <v>62</v>
+      </c>
+      <c r="L4">
+        <f t="shared" ca="1" si="0"/>
+        <v>45563</v>
+      </c>
+      <c r="M4" t="s">
+        <v>56</v>
+      </c>
+      <c r="N4" t="s">
+        <v>63</v>
+      </c>
+      <c r="O4" t="s">
+        <v>64</v>
+      </c>
+      <c r="P4" t="s">
+        <v>63</v>
+      </c>
+      <c r="Q4">
         <v>21201</v>
       </c>
-      <c r="R2" s="14" t="s">
+      <c r="R4" t="s">
+        <v>65</v>
+      </c>
+      <c r="S4" t="s">
+        <v>65</v>
+      </c>
+      <c r="T4" t="s">
         <v>62</v>
       </c>
-      <c r="S2" s="14" t="s">
+      <c r="U4" t="s">
+        <v>66</v>
+      </c>
+      <c r="V4" t="s">
+        <v>67</v>
+      </c>
+      <c r="W4" t="s">
         <v>62</v>
       </c>
-      <c r="T2" s="14" t="s">
-        <v>59</v>
-      </c>
-      <c r="U2" s="18" t="s">
+      <c r="X4">
+        <f t="shared" ca="1" si="1"/>
+        <v>45563</v>
+      </c>
+      <c r="Y4">
+        <f t="shared" ca="1" si="2"/>
+        <v>45614</v>
+      </c>
+      <c r="Z4" t="s">
+        <v>68</v>
+      </c>
+      <c r="AA4" t="s">
+        <v>101</v>
+      </c>
+      <c r="AB4" t="s">
+        <v>93</v>
+      </c>
+      <c r="AC4" t="s">
+        <v>102</v>
+      </c>
+      <c r="AD4" t="s">
+        <v>94</v>
+      </c>
+      <c r="AE4">
+        <v>124</v>
+      </c>
+      <c r="AF4" t="s">
+        <v>46</v>
+      </c>
+      <c r="AG4">
+        <v>40</v>
+      </c>
+      <c r="AH4" t="s">
+        <v>74</v>
+      </c>
+      <c r="AI4" t="s">
+        <v>75</v>
+      </c>
+      <c r="AJ4" t="s">
+        <v>76</v>
+      </c>
+      <c r="AK4" t="s">
+        <v>77</v>
+      </c>
+      <c r="AL4" t="s">
+        <v>103</v>
+      </c>
+      <c r="AM4" t="s">
+        <v>104</v>
+      </c>
+      <c r="AN4" t="s">
+        <v>76</v>
+      </c>
+      <c r="AO4" t="s">
+        <v>76</v>
+      </c>
+      <c r="AP4" t="s">
+        <v>56</v>
+      </c>
+      <c r="AQ4" t="s">
+        <v>81</v>
+      </c>
+      <c r="AR4">
+        <f ca="1"/>
+        <v>617992452.72788286</v>
+      </c>
+      <c r="AS4" t="s">
+        <v>82</v>
+      </c>
+      <c r="AT4">
+        <v>35591</v>
+      </c>
+      <c r="AU4" t="s">
+        <v>56</v>
+      </c>
+      <c r="AV4" t="s">
+        <v>83</v>
+      </c>
+      <c r="AW4" t="s">
+        <v>56</v>
+      </c>
+      <c r="AX4" t="s">
+        <v>84</v>
+      </c>
+      <c r="AY4">
+        <v>54057</v>
+      </c>
+      <c r="AZ4" t="s">
         <v>63</v>
       </c>
-      <c r="V2" s="19" t="s">
+      <c r="BA4" t="s">
+        <v>85</v>
+      </c>
+      <c r="BB4" t="s">
+        <v>86</v>
+      </c>
+      <c r="BC4" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="5" spans="1:55" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A5" t="s">
+        <v>105</v>
+      </c>
+      <c r="B5" t="s">
+        <v>106</v>
+      </c>
+      <c r="C5" s="8" t="s">
+        <v>107</v>
+      </c>
+      <c r="D5" t="s">
+        <v>90</v>
+      </c>
+      <c r="E5" t="s">
+        <v>56</v>
+      </c>
+      <c r="F5" t="s">
+        <v>57</v>
+      </c>
+      <c r="G5" t="s">
+        <v>108</v>
+      </c>
+      <c r="H5" t="s">
+        <v>109</v>
+      </c>
+      <c r="I5" t="s">
+        <v>60</v>
+      </c>
+      <c r="J5" t="s">
+        <v>61</v>
+      </c>
+      <c r="K5" t="s">
+        <v>62</v>
+      </c>
+      <c r="L5">
+        <f t="shared" ca="1" si="0"/>
+        <v>45563</v>
+      </c>
+      <c r="M5" t="s">
+        <v>56</v>
+      </c>
+      <c r="N5" t="s">
+        <v>63</v>
+      </c>
+      <c r="O5" t="s">
         <v>64</v>
       </c>
-      <c r="W2" s="14" t="s">
-        <v>59</v>
-      </c>
-      <c r="X2" s="20">
-        <f ca="1">L2</f>
-        <v>45562</v>
-      </c>
-      <c r="Y2" s="15">
-        <f ca="1">TODAY()+20</f>
-        <v>45613</v>
-      </c>
-      <c r="Z2" s="21" t="s">
+      <c r="P5" t="s">
+        <v>63</v>
+      </c>
+      <c r="Q5">
+        <v>21201</v>
+      </c>
+      <c r="R5" t="s">
         <v>65</v>
       </c>
-      <c r="AA2" s="22" t="s">
+      <c r="S5" t="s">
+        <v>65</v>
+      </c>
+      <c r="T5" t="s">
+        <v>62</v>
+      </c>
+      <c r="U5" t="s">
         <v>66</v>
       </c>
-      <c r="AB2" s="23" t="s">
+      <c r="V5" t="s">
         <v>67</v>
       </c>
-      <c r="AC2" s="24" t="s">
+      <c r="W5" t="s">
+        <v>62</v>
+      </c>
+      <c r="X5">
+        <f t="shared" ca="1" si="1"/>
+        <v>45563</v>
+      </c>
+      <c r="Y5">
+        <f t="shared" ca="1" si="2"/>
+        <v>45614</v>
+      </c>
+      <c r="Z5" t="s">
         <v>68</v>
       </c>
-      <c r="AD2" s="23" t="s">
+      <c r="AA5" t="s">
         <v>69</v>
       </c>
-      <c r="AE2" s="25">
+      <c r="AB5" t="s">
+        <v>93</v>
+      </c>
+      <c r="AC5" t="s">
+        <v>71</v>
+      </c>
+      <c r="AD5" t="s">
+        <v>72</v>
+      </c>
+      <c r="AE5">
         <v>121</v>
       </c>
-      <c r="AF2" s="25" t="s">
+      <c r="AF5" t="s">
+        <v>73</v>
+      </c>
+      <c r="AG5">
+        <v>25</v>
+      </c>
+      <c r="AH5" t="s">
+        <v>74</v>
+      </c>
+      <c r="AI5" t="s">
+        <v>75</v>
+      </c>
+      <c r="AJ5" t="s">
+        <v>76</v>
+      </c>
+      <c r="AK5" t="s">
+        <v>77</v>
+      </c>
+      <c r="AL5" t="s">
+        <v>78</v>
+      </c>
+      <c r="AM5" t="s">
+        <v>79</v>
+      </c>
+      <c r="AN5" t="s">
+        <v>80</v>
+      </c>
+      <c r="AO5" t="s">
+        <v>76</v>
+      </c>
+      <c r="AP5" t="s">
+        <v>56</v>
+      </c>
+      <c r="AQ5" t="s">
+        <v>81</v>
+      </c>
+      <c r="AR5">
+        <f ca="1"/>
+        <v>341904021.5753274</v>
+      </c>
+      <c r="AS5" t="s">
+        <v>82</v>
+      </c>
+      <c r="AT5">
+        <v>35591</v>
+      </c>
+      <c r="AU5" t="s">
+        <v>56</v>
+      </c>
+      <c r="AV5" t="s">
+        <v>83</v>
+      </c>
+      <c r="AW5" t="s">
+        <v>56</v>
+      </c>
+      <c r="AX5" t="s">
+        <v>84</v>
+      </c>
+      <c r="AY5">
+        <v>54057</v>
+      </c>
+      <c r="AZ5" t="s">
+        <v>63</v>
+      </c>
+      <c r="BA5" t="s">
+        <v>85</v>
+      </c>
+      <c r="BB5" t="s">
+        <v>86</v>
+      </c>
+      <c r="BC5" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="6" spans="1:55" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A6" t="s">
+        <v>110</v>
+      </c>
+      <c r="B6" t="s">
+        <v>111</v>
+      </c>
+      <c r="C6" s="7" t="s">
+        <v>54</v>
+      </c>
+      <c r="D6" t="s">
+        <v>98</v>
+      </c>
+      <c r="E6" t="s">
+        <v>56</v>
+      </c>
+      <c r="F6" t="s">
+        <v>57</v>
+      </c>
+      <c r="G6" t="s">
+        <v>112</v>
+      </c>
+      <c r="H6" t="s">
+        <v>113</v>
+      </c>
+      <c r="I6" t="s">
+        <v>60</v>
+      </c>
+      <c r="J6" t="s">
+        <v>61</v>
+      </c>
+      <c r="K6" t="s">
+        <v>62</v>
+      </c>
+      <c r="L6">
+        <f t="shared" ca="1" si="0"/>
+        <v>45563</v>
+      </c>
+      <c r="M6" t="s">
+        <v>56</v>
+      </c>
+      <c r="N6" t="s">
+        <v>63</v>
+      </c>
+      <c r="O6" t="s">
+        <v>64</v>
+      </c>
+      <c r="P6" t="s">
+        <v>63</v>
+      </c>
+      <c r="Q6">
+        <v>21201</v>
+      </c>
+      <c r="R6" t="s">
+        <v>65</v>
+      </c>
+      <c r="S6" t="s">
+        <v>65</v>
+      </c>
+      <c r="T6" t="s">
+        <v>62</v>
+      </c>
+      <c r="U6" t="s">
+        <v>66</v>
+      </c>
+      <c r="V6" t="s">
+        <v>67</v>
+      </c>
+      <c r="W6" t="s">
+        <v>62</v>
+      </c>
+      <c r="X6">
+        <f t="shared" ca="1" si="1"/>
+        <v>45563</v>
+      </c>
+      <c r="Y6">
+        <f t="shared" ca="1" si="2"/>
+        <v>45614</v>
+      </c>
+      <c r="Z6" t="s">
+        <v>68</v>
+      </c>
+      <c r="AA6" t="s">
+        <v>114</v>
+      </c>
+      <c r="AB6" t="s">
+        <v>93</v>
+      </c>
+      <c r="AC6" t="s">
+        <v>115</v>
+      </c>
+      <c r="AD6" t="s">
+        <v>94</v>
+      </c>
+      <c r="AE6">
+        <v>124</v>
+      </c>
+      <c r="AF6" t="s">
+        <v>46</v>
+      </c>
+      <c r="AG6">
+        <v>40</v>
+      </c>
+      <c r="AH6" t="s">
+        <v>74</v>
+      </c>
+      <c r="AI6" t="s">
+        <v>75</v>
+      </c>
+      <c r="AJ6" t="s">
+        <v>76</v>
+      </c>
+      <c r="AK6" t="s">
+        <v>77</v>
+      </c>
+      <c r="AL6" t="s">
+        <v>103</v>
+      </c>
+      <c r="AM6" t="s">
+        <v>104</v>
+      </c>
+      <c r="AN6" t="s">
+        <v>76</v>
+      </c>
+      <c r="AO6" t="s">
+        <v>76</v>
+      </c>
+      <c r="AP6" t="s">
+        <v>56</v>
+      </c>
+      <c r="AQ6" t="s">
+        <v>81</v>
+      </c>
+      <c r="AR6">
+        <f ca="1"/>
+        <v>549430002.93627071</v>
+      </c>
+      <c r="AS6" t="s">
+        <v>82</v>
+      </c>
+      <c r="AT6">
+        <v>35591</v>
+      </c>
+      <c r="AU6" t="s">
+        <v>56</v>
+      </c>
+      <c r="AV6" t="s">
+        <v>83</v>
+      </c>
+      <c r="AW6" t="s">
+        <v>56</v>
+      </c>
+      <c r="AX6" t="s">
+        <v>84</v>
+      </c>
+      <c r="AY6">
+        <v>54057</v>
+      </c>
+      <c r="AZ6" t="s">
+        <v>63</v>
+      </c>
+      <c r="BA6" t="s">
+        <v>85</v>
+      </c>
+      <c r="BB6" t="s">
+        <v>86</v>
+      </c>
+      <c r="BC6" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="7" spans="1:55" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A7" t="s">
+        <v>116</v>
+      </c>
+      <c r="B7" t="s">
+        <v>117</v>
+      </c>
+      <c r="C7" s="7" t="s">
+        <v>54</v>
+      </c>
+      <c r="D7" t="s">
+        <v>98</v>
+      </c>
+      <c r="E7" t="s">
+        <v>56</v>
+      </c>
+      <c r="F7" t="s">
+        <v>57</v>
+      </c>
+      <c r="G7" t="s">
+        <v>118</v>
+      </c>
+      <c r="H7" t="s">
+        <v>119</v>
+      </c>
+      <c r="I7" t="s">
+        <v>60</v>
+      </c>
+      <c r="J7" t="s">
+        <v>61</v>
+      </c>
+      <c r="K7" t="s">
+        <v>62</v>
+      </c>
+      <c r="L7">
+        <f t="shared" ca="1" si="0"/>
+        <v>45563</v>
+      </c>
+      <c r="M7" t="s">
+        <v>56</v>
+      </c>
+      <c r="N7" t="s">
+        <v>63</v>
+      </c>
+      <c r="O7" t="s">
+        <v>64</v>
+      </c>
+      <c r="P7" t="s">
+        <v>63</v>
+      </c>
+      <c r="Q7">
+        <v>21201</v>
+      </c>
+      <c r="R7" t="s">
+        <v>65</v>
+      </c>
+      <c r="S7" t="s">
+        <v>65</v>
+      </c>
+      <c r="T7" t="s">
+        <v>62</v>
+      </c>
+      <c r="U7" t="s">
+        <v>66</v>
+      </c>
+      <c r="V7" t="s">
+        <v>67</v>
+      </c>
+      <c r="W7" t="s">
+        <v>62</v>
+      </c>
+      <c r="X7">
+        <f t="shared" ca="1" si="1"/>
+        <v>45563</v>
+      </c>
+      <c r="Y7">
+        <f t="shared" ca="1" si="2"/>
+        <v>45614</v>
+      </c>
+      <c r="Z7" t="s">
+        <v>68</v>
+      </c>
+      <c r="AA7" t="s">
+        <v>120</v>
+      </c>
+      <c r="AB7" t="s">
+        <v>93</v>
+      </c>
+      <c r="AC7" t="s">
+        <v>121</v>
+      </c>
+      <c r="AD7" t="s">
+        <v>72</v>
+      </c>
+      <c r="AE7">
+        <v>124</v>
+      </c>
+      <c r="AF7" t="s">
+        <v>46</v>
+      </c>
+      <c r="AG7">
+        <v>25</v>
+      </c>
+      <c r="AH7" t="s">
+        <v>74</v>
+      </c>
+      <c r="AI7" t="s">
+        <v>75</v>
+      </c>
+      <c r="AJ7" t="s">
+        <v>76</v>
+      </c>
+      <c r="AK7" t="s">
+        <v>77</v>
+      </c>
+      <c r="AL7" t="s">
+        <v>103</v>
+      </c>
+      <c r="AM7" t="s">
+        <v>104</v>
+      </c>
+      <c r="AN7" t="s">
+        <v>76</v>
+      </c>
+      <c r="AO7" t="s">
+        <v>76</v>
+      </c>
+      <c r="AP7" t="s">
+        <v>56</v>
+      </c>
+      <c r="AQ7" t="s">
+        <v>81</v>
+      </c>
+      <c r="AR7">
+        <f ca="1"/>
+        <v>729117931.47737575</v>
+      </c>
+      <c r="AS7" t="s">
+        <v>82</v>
+      </c>
+      <c r="AT7">
+        <v>35591</v>
+      </c>
+      <c r="AU7" t="s">
+        <v>56</v>
+      </c>
+      <c r="AV7" t="s">
+        <v>83</v>
+      </c>
+      <c r="AW7" t="s">
+        <v>56</v>
+      </c>
+      <c r="AX7" t="s">
+        <v>84</v>
+      </c>
+      <c r="AY7">
+        <v>54057</v>
+      </c>
+      <c r="AZ7" t="s">
+        <v>63</v>
+      </c>
+      <c r="BA7" t="s">
+        <v>85</v>
+      </c>
+      <c r="BB7" t="s">
+        <v>86</v>
+      </c>
+      <c r="BC7" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="8" spans="1:55" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A8" t="s">
+        <v>122</v>
+      </c>
+      <c r="B8" t="s">
+        <v>123</v>
+      </c>
+      <c r="C8" s="7" t="s">
+        <v>54</v>
+      </c>
+      <c r="D8" t="s">
+        <v>98</v>
+      </c>
+      <c r="E8" t="s">
+        <v>56</v>
+      </c>
+      <c r="F8" t="s">
+        <v>57</v>
+      </c>
+      <c r="G8" t="s">
+        <v>124</v>
+      </c>
+      <c r="H8" t="s">
+        <v>125</v>
+      </c>
+      <c r="I8" t="s">
+        <v>60</v>
+      </c>
+      <c r="J8" t="s">
+        <v>61</v>
+      </c>
+      <c r="K8" t="s">
+        <v>62</v>
+      </c>
+      <c r="L8">
+        <f t="shared" ca="1" si="0"/>
+        <v>45563</v>
+      </c>
+      <c r="M8" t="s">
+        <v>56</v>
+      </c>
+      <c r="N8" t="s">
+        <v>63</v>
+      </c>
+      <c r="O8" t="s">
+        <v>64</v>
+      </c>
+      <c r="P8" t="s">
+        <v>63</v>
+      </c>
+      <c r="Q8">
+        <v>21201</v>
+      </c>
+      <c r="R8" t="s">
+        <v>65</v>
+      </c>
+      <c r="S8" t="s">
+        <v>65</v>
+      </c>
+      <c r="T8" t="s">
+        <v>62</v>
+      </c>
+      <c r="U8" t="s">
+        <v>66</v>
+      </c>
+      <c r="V8" t="s">
+        <v>67</v>
+      </c>
+      <c r="W8" t="s">
+        <v>62</v>
+      </c>
+      <c r="X8">
+        <f t="shared" ca="1" si="1"/>
+        <v>45563</v>
+      </c>
+      <c r="Y8">
+        <f t="shared" ca="1" si="2"/>
+        <v>45614</v>
+      </c>
+      <c r="Z8" t="s">
+        <v>68</v>
+      </c>
+      <c r="AA8" t="s">
+        <v>126</v>
+      </c>
+      <c r="AB8" t="s">
+        <v>93</v>
+      </c>
+      <c r="AC8" t="s">
+        <v>127</v>
+      </c>
+      <c r="AD8" t="s">
+        <v>94</v>
+      </c>
+      <c r="AE8">
+        <v>124</v>
+      </c>
+      <c r="AF8" t="s">
+        <v>46</v>
+      </c>
+      <c r="AG8">
+        <v>40</v>
+      </c>
+      <c r="AH8" t="s">
+        <v>74</v>
+      </c>
+      <c r="AI8" t="s">
+        <v>75</v>
+      </c>
+      <c r="AJ8" t="s">
+        <v>76</v>
+      </c>
+      <c r="AK8" t="s">
+        <v>77</v>
+      </c>
+      <c r="AL8" t="s">
+        <v>103</v>
+      </c>
+      <c r="AM8" t="s">
+        <v>104</v>
+      </c>
+      <c r="AN8" t="s">
+        <v>76</v>
+      </c>
+      <c r="AO8" t="s">
+        <v>76</v>
+      </c>
+      <c r="AP8" t="s">
+        <v>56</v>
+      </c>
+      <c r="AQ8" t="s">
+        <v>81</v>
+      </c>
+      <c r="AR8">
+        <f ca="1"/>
+        <v>134367581.14492083</v>
+      </c>
+      <c r="AS8" t="s">
+        <v>82</v>
+      </c>
+      <c r="AT8">
+        <v>35591</v>
+      </c>
+      <c r="AU8" t="s">
+        <v>56</v>
+      </c>
+      <c r="AV8" t="s">
+        <v>83</v>
+      </c>
+      <c r="AW8" t="s">
+        <v>56</v>
+      </c>
+      <c r="AX8" t="s">
+        <v>84</v>
+      </c>
+      <c r="AY8">
+        <v>54057</v>
+      </c>
+      <c r="AZ8" t="s">
+        <v>63</v>
+      </c>
+      <c r="BA8" t="s">
+        <v>85</v>
+      </c>
+      <c r="BB8" t="s">
+        <v>86</v>
+      </c>
+      <c r="BC8" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="9" spans="1:55" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A9" t="s">
+        <v>128</v>
+      </c>
+      <c r="B9" t="s">
+        <v>129</v>
+      </c>
+      <c r="C9" s="7" t="s">
+        <v>54</v>
+      </c>
+      <c r="D9" t="s">
+        <v>98</v>
+      </c>
+      <c r="E9" t="s">
+        <v>56</v>
+      </c>
+      <c r="F9" t="s">
+        <v>57</v>
+      </c>
+      <c r="G9" t="s">
+        <v>130</v>
+      </c>
+      <c r="H9" t="s">
+        <v>131</v>
+      </c>
+      <c r="I9" t="s">
+        <v>60</v>
+      </c>
+      <c r="J9" t="s">
+        <v>61</v>
+      </c>
+      <c r="K9" t="s">
+        <v>62</v>
+      </c>
+      <c r="L9">
+        <f t="shared" ca="1" si="0"/>
+        <v>45563</v>
+      </c>
+      <c r="M9" t="s">
+        <v>56</v>
+      </c>
+      <c r="N9" t="s">
+        <v>63</v>
+      </c>
+      <c r="O9" t="s">
+        <v>64</v>
+      </c>
+      <c r="P9" t="s">
+        <v>63</v>
+      </c>
+      <c r="Q9">
+        <v>21201</v>
+      </c>
+      <c r="R9" t="s">
+        <v>65</v>
+      </c>
+      <c r="S9" t="s">
+        <v>65</v>
+      </c>
+      <c r="T9" t="s">
+        <v>62</v>
+      </c>
+      <c r="U9" t="s">
+        <v>66</v>
+      </c>
+      <c r="V9" t="s">
+        <v>67</v>
+      </c>
+      <c r="W9" t="s">
+        <v>62</v>
+      </c>
+      <c r="X9">
+        <f t="shared" ca="1" si="1"/>
+        <v>45563</v>
+      </c>
+      <c r="Y9">
+        <f t="shared" ca="1" si="2"/>
+        <v>45614</v>
+      </c>
+      <c r="Z9" t="s">
+        <v>68</v>
+      </c>
+      <c r="AA9" t="s">
+        <v>132</v>
+      </c>
+      <c r="AB9" t="s">
+        <v>93</v>
+      </c>
+      <c r="AC9" t="s">
+        <v>133</v>
+      </c>
+      <c r="AD9" t="s">
+        <v>94</v>
+      </c>
+      <c r="AE9">
+        <v>124</v>
+      </c>
+      <c r="AF9" t="s">
+        <v>46</v>
+      </c>
+      <c r="AG9">
+        <v>40</v>
+      </c>
+      <c r="AH9" t="s">
+        <v>74</v>
+      </c>
+      <c r="AI9" t="s">
+        <v>75</v>
+      </c>
+      <c r="AJ9" t="s">
+        <v>76</v>
+      </c>
+      <c r="AK9" t="s">
+        <v>77</v>
+      </c>
+      <c r="AL9" t="s">
+        <v>103</v>
+      </c>
+      <c r="AM9" t="s">
+        <v>104</v>
+      </c>
+      <c r="AN9" t="s">
+        <v>76</v>
+      </c>
+      <c r="AO9" t="s">
+        <v>76</v>
+      </c>
+      <c r="AP9" t="s">
+        <v>56</v>
+      </c>
+      <c r="AQ9" t="s">
+        <v>81</v>
+      </c>
+      <c r="AR9">
+        <f ca="1"/>
+        <v>605135441.84431624</v>
+      </c>
+      <c r="AS9" t="s">
+        <v>82</v>
+      </c>
+      <c r="AT9">
+        <v>35591</v>
+      </c>
+      <c r="AU9" t="s">
+        <v>56</v>
+      </c>
+      <c r="AV9" t="s">
+        <v>83</v>
+      </c>
+      <c r="AW9" t="s">
+        <v>56</v>
+      </c>
+      <c r="AX9" t="s">
+        <v>84</v>
+      </c>
+      <c r="AY9">
+        <v>54057</v>
+      </c>
+      <c r="AZ9" t="s">
+        <v>63</v>
+      </c>
+      <c r="BA9" t="s">
+        <v>85</v>
+      </c>
+      <c r="BB9" t="s">
+        <v>86</v>
+      </c>
+      <c r="BC9" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="10" spans="1:55" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A10" t="s">
+        <v>134</v>
+      </c>
+      <c r="B10" t="s">
+        <v>135</v>
+      </c>
+      <c r="C10" s="7" t="s">
+        <v>54</v>
+      </c>
+      <c r="D10" t="s">
+        <v>98</v>
+      </c>
+      <c r="E10" t="s">
+        <v>56</v>
+      </c>
+      <c r="F10" t="s">
+        <v>57</v>
+      </c>
+      <c r="G10" t="s">
+        <v>136</v>
+      </c>
+      <c r="H10" t="s">
+        <v>137</v>
+      </c>
+      <c r="I10" t="s">
+        <v>60</v>
+      </c>
+      <c r="J10" t="s">
+        <v>61</v>
+      </c>
+      <c r="K10" t="s">
+        <v>62</v>
+      </c>
+      <c r="L10">
+        <f t="shared" ca="1" si="0"/>
+        <v>45563</v>
+      </c>
+      <c r="M10" t="s">
+        <v>56</v>
+      </c>
+      <c r="N10" t="s">
+        <v>63</v>
+      </c>
+      <c r="O10" t="s">
+        <v>64</v>
+      </c>
+      <c r="P10" t="s">
+        <v>63</v>
+      </c>
+      <c r="Q10">
+        <v>21201</v>
+      </c>
+      <c r="R10" t="s">
+        <v>65</v>
+      </c>
+      <c r="S10" t="s">
+        <v>65</v>
+      </c>
+      <c r="T10" t="s">
+        <v>62</v>
+      </c>
+      <c r="U10" t="s">
+        <v>66</v>
+      </c>
+      <c r="V10" t="s">
+        <v>67</v>
+      </c>
+      <c r="W10" t="s">
+        <v>62</v>
+      </c>
+      <c r="X10">
+        <f t="shared" ca="1" si="1"/>
+        <v>45563</v>
+      </c>
+      <c r="Y10">
+        <f t="shared" ca="1" si="2"/>
+        <v>45614</v>
+      </c>
+      <c r="Z10" t="s">
+        <v>68</v>
+      </c>
+      <c r="AA10" t="s">
+        <v>138</v>
+      </c>
+      <c r="AB10" t="s">
+        <v>93</v>
+      </c>
+      <c r="AC10" t="s">
+        <v>139</v>
+      </c>
+      <c r="AD10" t="s">
+        <v>72</v>
+      </c>
+      <c r="AE10">
+        <v>124</v>
+      </c>
+      <c r="AF10" t="s">
+        <v>73</v>
+      </c>
+      <c r="AG10">
+        <v>20</v>
+      </c>
+      <c r="AH10" t="s">
+        <v>74</v>
+      </c>
+      <c r="AI10" t="s">
+        <v>75</v>
+      </c>
+      <c r="AJ10" t="s">
+        <v>76</v>
+      </c>
+      <c r="AK10" t="s">
+        <v>77</v>
+      </c>
+      <c r="AL10" t="s">
+        <v>103</v>
+      </c>
+      <c r="AM10" t="s">
+        <v>104</v>
+      </c>
+      <c r="AN10" t="s">
+        <v>76</v>
+      </c>
+      <c r="AO10" t="s">
+        <v>76</v>
+      </c>
+      <c r="AP10" t="s">
+        <v>56</v>
+      </c>
+      <c r="AQ10" t="s">
+        <v>81</v>
+      </c>
+      <c r="AR10">
+        <f ca="1"/>
+        <v>511097241.76941502</v>
+      </c>
+      <c r="AS10" t="s">
+        <v>82</v>
+      </c>
+      <c r="AT10">
+        <v>35591</v>
+      </c>
+      <c r="AU10" t="s">
+        <v>56</v>
+      </c>
+      <c r="AV10" t="s">
+        <v>83</v>
+      </c>
+      <c r="AW10" t="s">
+        <v>56</v>
+      </c>
+      <c r="AX10" t="s">
+        <v>84</v>
+      </c>
+      <c r="AY10">
+        <v>54057</v>
+      </c>
+      <c r="AZ10" t="s">
+        <v>63</v>
+      </c>
+      <c r="BA10" t="s">
+        <v>85</v>
+      </c>
+      <c r="BB10" t="s">
+        <v>86</v>
+      </c>
+      <c r="BC10" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="11" spans="1:55" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A11" t="s">
+        <v>140</v>
+      </c>
+      <c r="B11" t="s">
+        <v>141</v>
+      </c>
+      <c r="C11" s="7" t="s">
+        <v>54</v>
+      </c>
+      <c r="D11" t="s">
+        <v>90</v>
+      </c>
+      <c r="E11" t="s">
+        <v>56</v>
+      </c>
+      <c r="F11" t="s">
+        <v>57</v>
+      </c>
+      <c r="G11" t="s">
+        <v>142</v>
+      </c>
+      <c r="H11" t="s">
+        <v>143</v>
+      </c>
+      <c r="I11" t="s">
+        <v>60</v>
+      </c>
+      <c r="J11" t="s">
+        <v>61</v>
+      </c>
+      <c r="K11" t="s">
+        <v>62</v>
+      </c>
+      <c r="L11">
+        <f t="shared" ca="1" si="0"/>
+        <v>45563</v>
+      </c>
+      <c r="M11" t="s">
+        <v>56</v>
+      </c>
+      <c r="N11" t="s">
+        <v>63</v>
+      </c>
+      <c r="O11" t="s">
+        <v>64</v>
+      </c>
+      <c r="P11" t="s">
+        <v>63</v>
+      </c>
+      <c r="Q11">
+        <v>21201</v>
+      </c>
+      <c r="R11" t="s">
+        <v>65</v>
+      </c>
+      <c r="S11" t="s">
+        <v>65</v>
+      </c>
+      <c r="T11" t="s">
+        <v>62</v>
+      </c>
+      <c r="U11" t="s">
+        <v>66</v>
+      </c>
+      <c r="V11" t="s">
+        <v>67</v>
+      </c>
+      <c r="W11" t="s">
+        <v>62</v>
+      </c>
+      <c r="X11">
+        <f t="shared" ca="1" si="1"/>
+        <v>45563</v>
+      </c>
+      <c r="Y11">
+        <f t="shared" ca="1" si="2"/>
+        <v>45614</v>
+      </c>
+      <c r="Z11" t="s">
+        <v>68</v>
+      </c>
+      <c r="AA11" t="s">
+        <v>69</v>
+      </c>
+      <c r="AB11" t="s">
+        <v>93</v>
+      </c>
+      <c r="AC11" t="s">
+        <v>144</v>
+      </c>
+      <c r="AD11" t="s">
+        <v>145</v>
+      </c>
+      <c r="AE11">
+        <v>121</v>
+      </c>
+      <c r="AF11" t="s">
+        <v>73</v>
+      </c>
+      <c r="AG11">
+        <v>15</v>
+      </c>
+      <c r="AH11" t="s">
+        <v>74</v>
+      </c>
+      <c r="AI11" t="s">
+        <v>75</v>
+      </c>
+      <c r="AJ11" t="s">
+        <v>76</v>
+      </c>
+      <c r="AK11" t="s">
+        <v>77</v>
+      </c>
+      <c r="AL11" t="s">
+        <v>78</v>
+      </c>
+      <c r="AM11" t="s">
+        <v>146</v>
+      </c>
+      <c r="AN11" t="s">
+        <v>80</v>
+      </c>
+      <c r="AO11" t="s">
+        <v>76</v>
+      </c>
+      <c r="AP11" t="s">
+        <v>56</v>
+      </c>
+      <c r="AQ11" t="s">
+        <v>81</v>
+      </c>
+      <c r="AR11">
+        <f ca="1"/>
+        <v>948406794.54615104</v>
+      </c>
+      <c r="AS11" t="s">
+        <v>82</v>
+      </c>
+      <c r="AT11">
+        <v>35591</v>
+      </c>
+      <c r="AU11" t="s">
+        <v>56</v>
+      </c>
+      <c r="AV11" t="s">
+        <v>83</v>
+      </c>
+      <c r="AW11" t="s">
+        <v>56</v>
+      </c>
+      <c r="AX11" t="s">
+        <v>84</v>
+      </c>
+      <c r="AY11">
+        <v>54057</v>
+      </c>
+      <c r="AZ11" t="s">
+        <v>63</v>
+      </c>
+      <c r="BA11" t="s">
+        <v>85</v>
+      </c>
+      <c r="BB11" t="s">
+        <v>86</v>
+      </c>
+      <c r="BC11" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="12" spans="1:55" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A12" t="s">
+        <v>147</v>
+      </c>
+      <c r="B12" t="s">
+        <v>148</v>
+      </c>
+      <c r="C12" s="7" t="s">
+        <v>54</v>
+      </c>
+      <c r="D12" t="s">
+        <v>90</v>
+      </c>
+      <c r="E12" t="s">
+        <v>56</v>
+      </c>
+      <c r="F12" t="s">
+        <v>57</v>
+      </c>
+      <c r="G12" t="s">
+        <v>149</v>
+      </c>
+      <c r="H12" t="s">
+        <v>150</v>
+      </c>
+      <c r="I12" t="s">
+        <v>60</v>
+      </c>
+      <c r="J12" t="s">
+        <v>61</v>
+      </c>
+      <c r="K12" t="s">
+        <v>62</v>
+      </c>
+      <c r="L12">
+        <f t="shared" ca="1" si="0"/>
+        <v>45563</v>
+      </c>
+      <c r="M12" t="s">
+        <v>56</v>
+      </c>
+      <c r="N12" t="s">
+        <v>63</v>
+      </c>
+      <c r="O12" t="s">
+        <v>64</v>
+      </c>
+      <c r="P12" t="s">
+        <v>63</v>
+      </c>
+      <c r="Q12">
+        <v>21201</v>
+      </c>
+      <c r="R12" t="s">
+        <v>65</v>
+      </c>
+      <c r="S12" t="s">
+        <v>65</v>
+      </c>
+      <c r="T12" t="s">
+        <v>62</v>
+      </c>
+      <c r="U12" t="s">
+        <v>66</v>
+      </c>
+      <c r="V12" t="s">
+        <v>67</v>
+      </c>
+      <c r="W12" t="s">
+        <v>62</v>
+      </c>
+      <c r="X12">
+        <f t="shared" ca="1" si="1"/>
+        <v>45563</v>
+      </c>
+      <c r="Y12">
+        <f t="shared" ca="1" si="2"/>
+        <v>45614</v>
+      </c>
+      <c r="Z12" t="s">
+        <v>68</v>
+      </c>
+      <c r="AA12" t="s">
+        <v>69</v>
+      </c>
+      <c r="AB12" t="s">
+        <v>93</v>
+      </c>
+      <c r="AC12" t="s">
+        <v>151</v>
+      </c>
+      <c r="AD12" t="s">
+        <v>94</v>
+      </c>
+      <c r="AE12">
+        <v>121</v>
+      </c>
+      <c r="AF12" t="s">
+        <v>73</v>
+      </c>
+      <c r="AG12">
+        <v>37.5</v>
+      </c>
+      <c r="AH12" t="s">
+        <v>74</v>
+      </c>
+      <c r="AI12" t="s">
+        <v>75</v>
+      </c>
+      <c r="AJ12" t="s">
+        <v>76</v>
+      </c>
+      <c r="AK12" t="s">
+        <v>77</v>
+      </c>
+      <c r="AL12" t="s">
+        <v>78</v>
+      </c>
+      <c r="AM12" t="s">
+        <v>152</v>
+      </c>
+      <c r="AN12" t="s">
+        <v>80</v>
+      </c>
+      <c r="AO12" t="s">
+        <v>76</v>
+      </c>
+      <c r="AP12" t="s">
+        <v>56</v>
+      </c>
+      <c r="AQ12" t="s">
+        <v>81</v>
+      </c>
+      <c r="AR12">
+        <f ca="1"/>
+        <v>348597166.78207755</v>
+      </c>
+      <c r="AS12" t="s">
+        <v>82</v>
+      </c>
+      <c r="AT12">
+        <v>35591</v>
+      </c>
+      <c r="AU12" t="s">
+        <v>56</v>
+      </c>
+      <c r="AV12" t="s">
+        <v>83</v>
+      </c>
+      <c r="AW12" t="s">
+        <v>56</v>
+      </c>
+      <c r="AX12" t="s">
+        <v>84</v>
+      </c>
+      <c r="AY12">
+        <v>54057</v>
+      </c>
+      <c r="AZ12" t="s">
+        <v>63</v>
+      </c>
+      <c r="BA12" t="s">
+        <v>85</v>
+      </c>
+      <c r="BB12" t="s">
+        <v>86</v>
+      </c>
+      <c r="BC12" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="13" spans="1:55" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A13" t="s">
+        <v>153</v>
+      </c>
+      <c r="B13" t="s">
+        <v>154</v>
+      </c>
+      <c r="C13" s="7" t="s">
+        <v>54</v>
+      </c>
+      <c r="D13" t="s">
+        <v>90</v>
+      </c>
+      <c r="E13" t="s">
+        <v>56</v>
+      </c>
+      <c r="F13" t="s">
+        <v>57</v>
+      </c>
+      <c r="G13" t="s">
+        <v>155</v>
+      </c>
+      <c r="H13" t="s">
+        <v>156</v>
+      </c>
+      <c r="I13" t="s">
+        <v>60</v>
+      </c>
+      <c r="J13" t="s">
+        <v>61</v>
+      </c>
+      <c r="K13" t="s">
+        <v>62</v>
+      </c>
+      <c r="L13">
+        <f t="shared" ca="1" si="0"/>
+        <v>45563</v>
+      </c>
+      <c r="M13" t="s">
+        <v>56</v>
+      </c>
+      <c r="N13" t="s">
+        <v>63</v>
+      </c>
+      <c r="O13" t="s">
+        <v>64</v>
+      </c>
+      <c r="P13" t="s">
+        <v>63</v>
+      </c>
+      <c r="Q13">
+        <v>21201</v>
+      </c>
+      <c r="R13" t="s">
+        <v>65</v>
+      </c>
+      <c r="S13" t="s">
+        <v>65</v>
+      </c>
+      <c r="T13" t="s">
+        <v>62</v>
+      </c>
+      <c r="U13" t="s">
+        <v>66</v>
+      </c>
+      <c r="V13" t="s">
+        <v>67</v>
+      </c>
+      <c r="W13" t="s">
+        <v>62</v>
+      </c>
+      <c r="X13">
+        <f t="shared" ca="1" si="1"/>
+        <v>45563</v>
+      </c>
+      <c r="Y13">
+        <f t="shared" ca="1" si="2"/>
+        <v>45614</v>
+      </c>
+      <c r="Z13" t="s">
+        <v>68</v>
+      </c>
+      <c r="AA13" t="s">
+        <v>69</v>
+      </c>
+      <c r="AB13" t="s">
+        <v>93</v>
+      </c>
+      <c r="AC13" t="s">
+        <v>157</v>
+      </c>
+      <c r="AD13" t="s">
+        <v>72</v>
+      </c>
+      <c r="AE13">
+        <v>121</v>
+      </c>
+      <c r="AF13" t="s">
+        <v>73</v>
+      </c>
+      <c r="AG13">
+        <v>12</v>
+      </c>
+      <c r="AH13" t="s">
+        <v>74</v>
+      </c>
+      <c r="AI13" t="s">
+        <v>75</v>
+      </c>
+      <c r="AJ13" t="s">
+        <v>76</v>
+      </c>
+      <c r="AK13" t="s">
+        <v>77</v>
+      </c>
+      <c r="AL13" t="s">
+        <v>78</v>
+      </c>
+      <c r="AM13" t="s">
+        <v>158</v>
+      </c>
+      <c r="AN13" t="s">
+        <v>80</v>
+      </c>
+      <c r="AO13" t="s">
+        <v>76</v>
+      </c>
+      <c r="AP13" t="s">
+        <v>56</v>
+      </c>
+      <c r="AQ13" t="s">
+        <v>81</v>
+      </c>
+      <c r="AR13">
+        <f ca="1"/>
+        <v>996765621.22767663</v>
+      </c>
+      <c r="AS13" t="s">
+        <v>82</v>
+      </c>
+      <c r="AT13">
+        <v>35591</v>
+      </c>
+      <c r="AU13" t="s">
+        <v>56</v>
+      </c>
+      <c r="AV13" t="s">
+        <v>83</v>
+      </c>
+      <c r="AW13" t="s">
+        <v>56</v>
+      </c>
+      <c r="AX13" t="s">
+        <v>84</v>
+      </c>
+      <c r="AY13">
+        <v>54057</v>
+      </c>
+      <c r="AZ13" t="s">
+        <v>63</v>
+      </c>
+      <c r="BA13" t="s">
+        <v>85</v>
+      </c>
+      <c r="BB13" t="s">
+        <v>86</v>
+      </c>
+      <c r="BC13" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="14" spans="1:55" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A14" t="s">
+        <v>159</v>
+      </c>
+      <c r="B14" t="s">
+        <v>160</v>
+      </c>
+      <c r="C14" s="7" t="s">
+        <v>54</v>
+      </c>
+      <c r="D14" t="s">
+        <v>90</v>
+      </c>
+      <c r="E14" t="s">
+        <v>56</v>
+      </c>
+      <c r="F14" t="s">
+        <v>57</v>
+      </c>
+      <c r="G14" t="s">
+        <v>161</v>
+      </c>
+      <c r="H14" t="s">
+        <v>162</v>
+      </c>
+      <c r="I14" t="s">
+        <v>60</v>
+      </c>
+      <c r="J14" t="s">
+        <v>61</v>
+      </c>
+      <c r="K14" t="s">
+        <v>62</v>
+      </c>
+      <c r="L14">
+        <f t="shared" ca="1" si="0"/>
+        <v>45563</v>
+      </c>
+      <c r="M14" t="s">
+        <v>56</v>
+      </c>
+      <c r="N14" t="s">
+        <v>63</v>
+      </c>
+      <c r="O14" t="s">
+        <v>64</v>
+      </c>
+      <c r="P14" t="s">
+        <v>63</v>
+      </c>
+      <c r="Q14">
+        <v>21201</v>
+      </c>
+      <c r="R14" t="s">
+        <v>65</v>
+      </c>
+      <c r="S14" t="s">
+        <v>65</v>
+      </c>
+      <c r="T14" t="s">
+        <v>62</v>
+      </c>
+      <c r="U14" t="s">
+        <v>66</v>
+      </c>
+      <c r="V14" t="s">
+        <v>67</v>
+      </c>
+      <c r="W14" t="s">
+        <v>62</v>
+      </c>
+      <c r="X14">
+        <f t="shared" ca="1" si="1"/>
+        <v>45563</v>
+      </c>
+      <c r="Y14">
+        <f t="shared" ca="1" si="2"/>
+        <v>45614</v>
+      </c>
+      <c r="Z14" t="s">
+        <v>68</v>
+      </c>
+      <c r="AA14" t="s">
+        <v>69</v>
+      </c>
+      <c r="AB14" t="s">
+        <v>93</v>
+      </c>
+      <c r="AC14" t="s">
+        <v>163</v>
+      </c>
+      <c r="AD14" t="s">
+        <v>94</v>
+      </c>
+      <c r="AE14">
+        <v>121</v>
+      </c>
+      <c r="AF14" t="s">
+        <v>73</v>
+      </c>
+      <c r="AG14">
+        <v>37.5</v>
+      </c>
+      <c r="AH14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AI14" t="s">
+        <v>75</v>
+      </c>
+      <c r="AJ14" t="s">
+        <v>76</v>
+      </c>
+      <c r="AK14" t="s">
+        <v>77</v>
+      </c>
+      <c r="AL14" t="s">
+        <v>78</v>
+      </c>
+      <c r="AM14" t="s">
+        <v>152</v>
+      </c>
+      <c r="AN14" t="s">
+        <v>80</v>
+      </c>
+      <c r="AO14" t="s">
+        <v>76</v>
+      </c>
+      <c r="AP14" t="s">
+        <v>56</v>
+      </c>
+      <c r="AQ14" t="s">
+        <v>81</v>
+      </c>
+      <c r="AR14">
+        <f ca="1"/>
+        <v>324906807.98325133</v>
+      </c>
+      <c r="AS14" t="s">
+        <v>82</v>
+      </c>
+      <c r="AT14">
+        <v>35591</v>
+      </c>
+      <c r="AU14" t="s">
+        <v>56</v>
+      </c>
+      <c r="AV14" t="s">
+        <v>83</v>
+      </c>
+      <c r="AW14" t="s">
+        <v>56</v>
+      </c>
+      <c r="AX14" t="s">
+        <v>84</v>
+      </c>
+      <c r="AY14">
+        <v>54057</v>
+      </c>
+      <c r="AZ14" t="s">
+        <v>63</v>
+      </c>
+      <c r="BA14" t="s">
+        <v>85</v>
+      </c>
+      <c r="BB14" t="s">
+        <v>86</v>
+      </c>
+      <c r="BC14" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="15" spans="1:55" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A15" t="s">
+        <v>164</v>
+      </c>
+      <c r="B15" t="s">
+        <v>165</v>
+      </c>
+      <c r="C15" s="7" t="s">
+        <v>54</v>
+      </c>
+      <c r="D15" t="s">
+        <v>90</v>
+      </c>
+      <c r="E15" t="s">
+        <v>56</v>
+      </c>
+      <c r="F15" t="s">
+        <v>57</v>
+      </c>
+      <c r="G15" t="s">
+        <v>166</v>
+      </c>
+      <c r="H15" t="s">
+        <v>167</v>
+      </c>
+      <c r="I15" t="s">
+        <v>60</v>
+      </c>
+      <c r="J15" t="s">
+        <v>61</v>
+      </c>
+      <c r="K15" t="s">
+        <v>62</v>
+      </c>
+      <c r="L15">
+        <f t="shared" ca="1" si="0"/>
+        <v>45563</v>
+      </c>
+      <c r="M15" t="s">
+        <v>56</v>
+      </c>
+      <c r="N15" t="s">
+        <v>63</v>
+      </c>
+      <c r="O15" t="s">
+        <v>64</v>
+      </c>
+      <c r="P15" t="s">
+        <v>63</v>
+      </c>
+      <c r="Q15">
+        <v>21201</v>
+      </c>
+      <c r="R15" t="s">
+        <v>65</v>
+      </c>
+      <c r="S15" t="s">
+        <v>65</v>
+      </c>
+      <c r="T15" t="s">
+        <v>62</v>
+      </c>
+      <c r="U15" t="s">
+        <v>66</v>
+      </c>
+      <c r="V15" t="s">
+        <v>67</v>
+      </c>
+      <c r="W15" t="s">
+        <v>62</v>
+      </c>
+      <c r="X15">
+        <f t="shared" ca="1" si="1"/>
+        <v>45563</v>
+      </c>
+      <c r="Y15">
+        <f t="shared" ca="1" si="2"/>
+        <v>45614</v>
+      </c>
+      <c r="Z15" t="s">
+        <v>68</v>
+      </c>
+      <c r="AA15" t="s">
+        <v>69</v>
+      </c>
+      <c r="AB15" t="s">
+        <v>93</v>
+      </c>
+      <c r="AC15" t="s">
+        <v>168</v>
+      </c>
+      <c r="AD15" t="s">
+        <v>94</v>
+      </c>
+      <c r="AE15">
+        <v>121</v>
+      </c>
+      <c r="AF15" t="s">
+        <v>73</v>
+      </c>
+      <c r="AG15">
+        <v>37.5</v>
+      </c>
+      <c r="AH15" t="s">
+        <v>74</v>
+      </c>
+      <c r="AI15" t="s">
+        <v>75</v>
+      </c>
+      <c r="AJ15" t="s">
+        <v>76</v>
+      </c>
+      <c r="AK15" t="s">
+        <v>77</v>
+      </c>
+      <c r="AL15" t="s">
+        <v>78</v>
+      </c>
+      <c r="AM15" t="s">
+        <v>169</v>
+      </c>
+      <c r="AN15" t="s">
+        <v>80</v>
+      </c>
+      <c r="AO15" t="s">
+        <v>76</v>
+      </c>
+      <c r="AP15" t="s">
+        <v>56</v>
+      </c>
+      <c r="AQ15" t="s">
+        <v>81</v>
+      </c>
+      <c r="AR15">
+        <f ca="1"/>
+        <v>686344253.4275887</v>
+      </c>
+      <c r="AS15" t="s">
+        <v>82</v>
+      </c>
+      <c r="AT15">
+        <v>35591</v>
+      </c>
+      <c r="AU15" t="s">
+        <v>56</v>
+      </c>
+      <c r="AV15" t="s">
+        <v>83</v>
+      </c>
+      <c r="AW15" t="s">
+        <v>56</v>
+      </c>
+      <c r="AX15" t="s">
+        <v>84</v>
+      </c>
+      <c r="AY15">
+        <v>54057</v>
+      </c>
+      <c r="AZ15" t="s">
+        <v>63</v>
+      </c>
+      <c r="BA15" t="s">
+        <v>85</v>
+      </c>
+      <c r="BB15" t="s">
+        <v>86</v>
+      </c>
+      <c r="BC15" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="16" spans="1:55" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A16" t="s">
+        <v>170</v>
+      </c>
+      <c r="B16" t="s">
+        <v>171</v>
+      </c>
+      <c r="C16" s="8" t="s">
+        <v>107</v>
+      </c>
+      <c r="D16" t="s">
+        <v>90</v>
+      </c>
+      <c r="E16" t="s">
+        <v>56</v>
+      </c>
+      <c r="F16" t="s">
+        <v>57</v>
+      </c>
+      <c r="G16" t="s">
+        <v>172</v>
+      </c>
+      <c r="H16" t="s">
+        <v>173</v>
+      </c>
+      <c r="I16" t="s">
+        <v>60</v>
+      </c>
+      <c r="J16" t="s">
+        <v>61</v>
+      </c>
+      <c r="K16" t="s">
+        <v>62</v>
+      </c>
+      <c r="L16">
+        <f t="shared" ca="1" si="0"/>
+        <v>45563</v>
+      </c>
+      <c r="M16" t="s">
+        <v>56</v>
+      </c>
+      <c r="N16" t="s">
+        <v>63</v>
+      </c>
+      <c r="O16" t="s">
+        <v>64</v>
+      </c>
+      <c r="P16" t="s">
+        <v>63</v>
+      </c>
+      <c r="Q16">
+        <v>21201</v>
+      </c>
+      <c r="R16" t="s">
+        <v>65</v>
+      </c>
+      <c r="S16" t="s">
+        <v>65</v>
+      </c>
+      <c r="T16" t="s">
+        <v>62</v>
+      </c>
+      <c r="U16" t="s">
+        <v>66</v>
+      </c>
+      <c r="V16" t="s">
+        <v>67</v>
+      </c>
+      <c r="W16" t="s">
+        <v>62</v>
+      </c>
+      <c r="X16">
+        <f t="shared" ca="1" si="1"/>
+        <v>45563</v>
+      </c>
+      <c r="Y16">
+        <f t="shared" ca="1" si="2"/>
+        <v>45614</v>
+      </c>
+      <c r="Z16" t="s">
+        <v>68</v>
+      </c>
+      <c r="AA16" t="s">
+        <v>69</v>
+      </c>
+      <c r="AB16" t="s">
         <v>70</v>
       </c>
-      <c r="AG2" s="26">
+      <c r="AC16" t="s">
+        <v>71</v>
+      </c>
+      <c r="AD16" t="s">
+        <v>72</v>
+      </c>
+      <c r="AE16">
+        <v>121</v>
+      </c>
+      <c r="AF16" t="s">
+        <v>73</v>
+      </c>
+      <c r="AG16">
         <v>10</v>
       </c>
-      <c r="AH2" s="23" t="s">
-        <v>71</v>
-      </c>
-      <c r="AI2" s="23" t="s">
-        <v>72</v>
-      </c>
-      <c r="AJ2" s="20" t="s">
+      <c r="AH16" t="s">
+        <v>74</v>
+      </c>
+      <c r="AI16" t="s">
+        <v>75</v>
+      </c>
+      <c r="AJ16" t="s">
+        <v>76</v>
+      </c>
+      <c r="AK16" t="s">
+        <v>77</v>
+      </c>
+      <c r="AL16" t="s">
+        <v>78</v>
+      </c>
+      <c r="AM16" t="s">
+        <v>79</v>
+      </c>
+      <c r="AN16" t="s">
+        <v>80</v>
+      </c>
+      <c r="AO16" t="s">
+        <v>76</v>
+      </c>
+      <c r="AP16" t="s">
+        <v>56</v>
+      </c>
+      <c r="AQ16" t="s">
+        <v>81</v>
+      </c>
+      <c r="AR16">
+        <f ca="1"/>
+        <v>610067726.7278229</v>
+      </c>
+      <c r="AS16" t="s">
+        <v>82</v>
+      </c>
+      <c r="AT16">
+        <v>35591</v>
+      </c>
+      <c r="AU16" t="s">
+        <v>56</v>
+      </c>
+      <c r="AV16" t="s">
+        <v>83</v>
+      </c>
+      <c r="AW16" t="s">
+        <v>56</v>
+      </c>
+      <c r="AX16" t="s">
+        <v>84</v>
+      </c>
+      <c r="AY16">
+        <v>54057</v>
+      </c>
+      <c r="AZ16" t="s">
+        <v>63</v>
+      </c>
+      <c r="BA16" t="s">
+        <v>85</v>
+      </c>
+      <c r="BB16" t="s">
+        <v>86</v>
+      </c>
+      <c r="BC16" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="17" spans="1:55" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A17" t="s">
+        <v>174</v>
+      </c>
+      <c r="B17" t="s">
+        <v>175</v>
+      </c>
+      <c r="C17" s="7" t="s">
+        <v>54</v>
+      </c>
+      <c r="D17" t="s">
+        <v>90</v>
+      </c>
+      <c r="E17" t="s">
+        <v>56</v>
+      </c>
+      <c r="F17" t="s">
+        <v>57</v>
+      </c>
+      <c r="G17" t="s">
+        <v>176</v>
+      </c>
+      <c r="H17" t="s">
+        <v>177</v>
+      </c>
+      <c r="I17" t="s">
+        <v>60</v>
+      </c>
+      <c r="J17" t="s">
+        <v>61</v>
+      </c>
+      <c r="K17" t="s">
+        <v>62</v>
+      </c>
+      <c r="L17">
+        <f t="shared" ca="1" si="0"/>
+        <v>45563</v>
+      </c>
+      <c r="M17" t="s">
+        <v>56</v>
+      </c>
+      <c r="N17" t="s">
+        <v>63</v>
+      </c>
+      <c r="O17" t="s">
+        <v>64</v>
+      </c>
+      <c r="P17" t="s">
+        <v>63</v>
+      </c>
+      <c r="Q17">
+        <v>21201</v>
+      </c>
+      <c r="R17" t="s">
+        <v>65</v>
+      </c>
+      <c r="S17" t="s">
+        <v>65</v>
+      </c>
+      <c r="T17" t="s">
+        <v>62</v>
+      </c>
+      <c r="U17" t="s">
+        <v>66</v>
+      </c>
+      <c r="V17" t="s">
+        <v>67</v>
+      </c>
+      <c r="W17" t="s">
+        <v>62</v>
+      </c>
+      <c r="X17">
+        <f t="shared" ca="1" si="1"/>
+        <v>45563</v>
+      </c>
+      <c r="Y17">
+        <f t="shared" ca="1" si="2"/>
+        <v>45614</v>
+      </c>
+      <c r="Z17" t="s">
+        <v>68</v>
+      </c>
+      <c r="AA17" t="s">
+        <v>69</v>
+      </c>
+      <c r="AB17" t="s">
+        <v>70</v>
+      </c>
+      <c r="AC17" t="s">
+        <v>168</v>
+      </c>
+      <c r="AD17" t="s">
+        <v>94</v>
+      </c>
+      <c r="AE17">
+        <v>121</v>
+      </c>
+      <c r="AF17" t="s">
         <v>73</v>
       </c>
-      <c r="AK2" s="14" t="s">
+      <c r="AG17">
+        <v>37.5</v>
+      </c>
+      <c r="AH17" t="s">
         <v>74</v>
       </c>
-      <c r="AL2" s="14" t="s">
+      <c r="AI17" t="s">
         <v>75</v>
       </c>
-      <c r="AM2" s="23" t="s">
+      <c r="AJ17" t="s">
         <v>76</v>
       </c>
-      <c r="AN2" s="10" t="s">
+      <c r="AK17" t="s">
         <v>77</v>
       </c>
-      <c r="AO2" s="10" t="s">
-        <v>73</v>
-      </c>
-      <c r="AP2" s="10" t="s">
-        <v>53</v>
-      </c>
-      <c r="AQ2" s="27" t="s">
+      <c r="AL17" t="s">
         <v>78</v>
       </c>
-      <c r="AR2" s="28">
-        <f t="array" aca="1" ref="AR2" ca="1">_xlfn.RANDARRAY(1,1,123456789,999999999,FALSE)</f>
-        <v>469057824.76021934</v>
-      </c>
-      <c r="AS2" s="23" t="s">
-        <v>79</v>
-      </c>
-      <c r="AT2" s="29">
-        <v>35226</v>
-      </c>
-      <c r="AU2" s="10" t="s">
-        <v>53</v>
-      </c>
-      <c r="AV2" s="10" t="s">
+      <c r="AM17" t="s">
+        <v>169</v>
+      </c>
+      <c r="AN17" t="s">
         <v>80</v>
       </c>
-      <c r="AW2" s="10" t="s">
-        <v>53</v>
-      </c>
-      <c r="AX2" s="10" t="s">
+      <c r="AO17" t="s">
+        <v>76</v>
+      </c>
+      <c r="AP17" t="s">
+        <v>56</v>
+      </c>
+      <c r="AQ17" t="s">
         <v>81</v>
       </c>
-      <c r="AY2" s="10" t="s">
+      <c r="AR17">
+        <f ca="1"/>
+        <v>523158718.836573</v>
+      </c>
+      <c r="AS17" t="s">
         <v>82</v>
       </c>
-      <c r="AZ2" s="27" t="s">
+      <c r="AT17">
+        <v>35591</v>
+      </c>
+      <c r="AU17" t="s">
+        <v>56</v>
+      </c>
+      <c r="AV17" t="s">
         <v>83</v>
       </c>
-      <c r="BA2" s="30" t="s">
+      <c r="AW17" t="s">
+        <v>56</v>
+      </c>
+      <c r="AX17" t="s">
         <v>84</v>
       </c>
+      <c r="AY17">
+        <v>54057</v>
+      </c>
+      <c r="AZ17" t="s">
+        <v>63</v>
+      </c>
+      <c r="BA17" t="s">
+        <v>85</v>
+      </c>
+      <c r="BB17" t="s">
+        <v>86</v>
+      </c>
+      <c r="BC17" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="18" spans="1:55" ht="14.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AR18" s="9"/>
     </row>
   </sheetData>
-  <dataValidations count="1">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="K2 Z2 W2 T2" xr:uid="{00000000-0002-0000-0000-000000000000}">
+  <dataValidations count="3">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="K10:K17 Z10:Z17 W10:W17 T10:T17" xr:uid="{00000000-0002-0000-0000-000000000000}">
+      <formula1>INDIRECT($E3)</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="K2 Z2 W2 T2" xr:uid="{00000000-0002-0000-0000-000001000000}">
       <formula1>INDIRECT($G2)</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="K3:K17 Z3:Z17 W3:W17 T3:T17" xr:uid="{00000000-0002-0000-0000-000002000000}">
+      <formula1>INDIRECT($E3)</formula1>
     </dataValidation>
   </dataValidations>
   <hyperlinks>
     <hyperlink ref="V2" r:id="rId1" xr:uid="{00000000-0004-0000-0000-000000000000}"/>
+    <hyperlink ref="V3" r:id="rId2" xr:uid="{00000000-0004-0000-0000-000001000000}"/>
+    <hyperlink ref="V4" r:id="rId3" xr:uid="{00000000-0004-0000-0000-000002000000}"/>
+    <hyperlink ref="V5" r:id="rId4" xr:uid="{00000000-0004-0000-0000-000003000000}"/>
+    <hyperlink ref="V6" r:id="rId5" xr:uid="{00000000-0004-0000-0000-000004000000}"/>
+    <hyperlink ref="V7" r:id="rId6" xr:uid="{00000000-0004-0000-0000-000005000000}"/>
+    <hyperlink ref="V8" r:id="rId7" xr:uid="{00000000-0004-0000-0000-000006000000}"/>
+    <hyperlink ref="V9" r:id="rId8" xr:uid="{00000000-0004-0000-0000-000007000000}"/>
+    <hyperlink ref="V10" r:id="rId9" xr:uid="{00000000-0004-0000-0000-000008000000}"/>
+    <hyperlink ref="V11" r:id="rId10" xr:uid="{00000000-0004-0000-0000-000009000000}"/>
+    <hyperlink ref="V12" r:id="rId11" xr:uid="{00000000-0004-0000-0000-00000A000000}"/>
+    <hyperlink ref="V13" r:id="rId12" xr:uid="{00000000-0004-0000-0000-00000B000000}"/>
+    <hyperlink ref="V14" r:id="rId13" xr:uid="{00000000-0004-0000-0000-00000C000000}"/>
+    <hyperlink ref="V15" r:id="rId14" xr:uid="{00000000-0004-0000-0000-00000D000000}"/>
+    <hyperlink ref="V16" r:id="rId15" xr:uid="{00000000-0004-0000-0000-00000E000000}"/>
+    <hyperlink ref="V17" r:id="rId16" xr:uid="{00000000-0004-0000-0000-00000F000000}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" r:id="rId2"/>
+  <pageSetup orientation="portrait" useFirstPageNumber="1" horizontalDpi="4294967295" verticalDpi="4294967295"/>
 </worksheet>
 </file>
--- a/Data/Hires/testDataUS.xlsx
+++ b/Data/Hires/testDataUS.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="794" uniqueCount="182">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="799" uniqueCount="185">
   <si>
     <t>TestCaseID</t>
   </si>
@@ -178,7 +178,7 @@
     <t>Test_1</t>
   </si>
   <si>
-    <t>10652155</t>
+    <t>10652344</t>
   </si>
   <si>
     <t>Passed</t>
@@ -193,10 +193,10 @@
     <t>Mr</t>
   </si>
   <si>
-    <t>USATwoA</t>
-  </si>
-  <si>
-    <t>GlobelRegFourOCT</t>
+    <t>Bailey</t>
+  </si>
+  <si>
+    <t>Cormier</t>
   </si>
   <si>
     <t>(202) 555-0147</t>
@@ -226,7 +226,7 @@
     <t>New Hire</t>
   </si>
   <si>
-    <t>Auto 18704125</t>
+    <t>Auto 52580233</t>
   </si>
   <si>
     <t>Regular</t>
@@ -283,16 +283,19 @@
     <t>Test_2</t>
   </si>
   <si>
+    <t>10652345</t>
+  </si>
+  <si>
     <t>124 Department Manager (Cyvad Rogaga (10589000))</t>
   </si>
   <si>
-    <t>Shanel</t>
-  </si>
-  <si>
-    <t>Koss</t>
-  </si>
-  <si>
-    <t>Auto 19162479</t>
+    <t>Carlo</t>
+  </si>
+  <si>
+    <t>Smitham</t>
+  </si>
+  <si>
+    <t>Auto 87237801</t>
   </si>
   <si>
     <t>Store Manager_NEW</t>
@@ -301,16 +304,16 @@
     <t>Test_3</t>
   </si>
   <si>
-    <t>10652160</t>
-  </si>
-  <si>
-    <t>Marilyne</t>
-  </si>
-  <si>
-    <t>Dooley</t>
-  </si>
-  <si>
-    <t>Auto 62280832</t>
+    <t>10652347</t>
+  </si>
+  <si>
+    <t>Claudia</t>
+  </si>
+  <si>
+    <t>Larkin</t>
+  </si>
+  <si>
+    <t>Auto 17008980</t>
   </si>
   <si>
     <t>In-Store P&amp;C Manager_NEW</t>
@@ -319,13 +322,16 @@
     <t>Test_4</t>
   </si>
   <si>
+    <t>10652349</t>
+  </si>
+  <si>
     <t>114 Store Management (Typiv Cipopa (10147210))</t>
   </si>
   <si>
-    <t>Carmel</t>
-  </si>
-  <si>
-    <t>Nitzsche</t>
+    <t>Allie</t>
+  </si>
+  <si>
+    <t>Emmerich</t>
   </si>
   <si>
     <t>Pennsylvania</t>
@@ -334,37 +340,43 @@
     <t>Harrisburg</t>
   </si>
   <si>
-    <t>Auto 73062160</t>
+    <t>Auto 2959192</t>
   </si>
   <si>
     <t>Test_5</t>
   </si>
   <si>
-    <t>Abraham</t>
-  </si>
-  <si>
-    <t>Grant</t>
-  </si>
-  <si>
-    <t>Auto 25998588</t>
+    <t>10652350</t>
+  </si>
+  <si>
+    <t>Fletcher</t>
+  </si>
+  <si>
+    <t>Monahan</t>
+  </si>
+  <si>
+    <t>Auto 93925701</t>
   </si>
   <si>
     <t>Test_6</t>
   </si>
   <si>
-    <t>Eldon</t>
-  </si>
-  <si>
-    <t>Buckridge</t>
-  </si>
-  <si>
-    <t>Auto 17324343</t>
+    <t>10652352</t>
+  </si>
+  <si>
+    <t>Tara</t>
+  </si>
+  <si>
+    <t>Huel</t>
+  </si>
+  <si>
+    <t>Auto 84504559</t>
   </si>
   <si>
     <t>Test_7</t>
   </si>
   <si>
-    <t>Test failed for 'Brenda Franecki' Employee: Errors and AlertsAlertAdd/Edit ID (Row 1 Column 6)This national identifier you entered is already in use. Verify that the information is accurate. &amp; find failed Screenshot Path:-&gt;H:\WorkDaySuite_Playwright/WorkdayFailedScreenshot/2024-11-08T13-11-40-113Z.png</t>
+    <t>Test failed for 'Martine O'Connell' Employee: undefined&amp; find failed Screenshot Path:-&gt;H:\WorkDaySuite_Playwright/WorkdayFailedScreenshot/2024-11-11T17-35-40-890Z.png</t>
   </si>
   <si>
     <t>Failed</t>
@@ -373,10 +385,10 @@
     <t>103 Store Management (Pyzad Zolyte (1586520))</t>
   </si>
   <si>
-    <t>Brenda</t>
-  </si>
-  <si>
-    <t>Franecki</t>
+    <t>Martine</t>
+  </si>
+  <si>
+    <t>O'Connell</t>
   </si>
   <si>
     <t>Philadelphia</t>
@@ -388,534 +400,159 @@
     <t>Test_8</t>
   </si>
   <si>
-    <t>10652172</t>
-  </si>
-  <si>
-    <t>Dora</t>
-  </si>
-  <si>
-    <t>Kuphal</t>
-  </si>
-  <si>
-    <t>Auto 81543767</t>
+    <t>10652354</t>
+  </si>
+  <si>
+    <t>Missouri</t>
+  </si>
+  <si>
+    <t>Mayert</t>
+  </si>
+  <si>
+    <t>Auto 63167551</t>
   </si>
   <si>
     <t>Test_9</t>
   </si>
   <si>
-    <t>10652173</t>
-  </si>
-  <si>
-    <t>Jennie</t>
-  </si>
-  <si>
-    <t>Spencer</t>
-  </si>
-  <si>
-    <t>Auto 99884711</t>
+    <t>10652355</t>
+  </si>
+  <si>
+    <t>Julius</t>
+  </si>
+  <si>
+    <t>Marks</t>
+  </si>
+  <si>
+    <t>Auto 88719357</t>
   </si>
   <si>
     <t>Test_10</t>
   </si>
   <si>
-    <t>10652174</t>
+    <t>10652356</t>
   </si>
   <si>
     <t>108 Store Management (Deloh Rizyle (10104528))</t>
   </si>
   <si>
-    <t>Frieda</t>
-  </si>
-  <si>
-    <t>Rosenbaum</t>
-  </si>
-  <si>
-    <t>Auto 63374999</t>
+    <t>Nico</t>
+  </si>
+  <si>
+    <t>Heathcote</t>
+  </si>
+  <si>
+    <t>Auto 10542183</t>
   </si>
   <si>
     <t>Test_11</t>
   </si>
   <si>
-    <t>Test failed for 'Bo Cassin' Employee: Errors and AlertsAlertAdd/Edit ID (Row 1 Column 6)This national identifier you entered is already in use. Verify that the information is accurate. &amp; find failed Screenshot Path:-&gt;H:\WorkDaySuite_Playwright/WorkdayFailedScreenshot/2024-11-08T13-53-01-347Z.png</t>
-  </si>
-  <si>
-    <t>Bo</t>
-  </si>
-  <si>
-    <t>Cassin</t>
-  </si>
-  <si>
-    <t>Auto 17438617</t>
+    <t>10652357</t>
+  </si>
+  <si>
+    <t>Lucio</t>
+  </si>
+  <si>
+    <t>Glover</t>
+  </si>
+  <si>
+    <t>Auto 73608867</t>
   </si>
   <si>
     <t>Test_12</t>
   </si>
   <si>
-    <t>Test failed for 'Alexander Runolfsson' Employee: Errors and AlertsAlertAdd/Edit ID (Row 1 Column 6)This national identifier you entered is already in use. Verify that the information is accurate. &amp; find failed Screenshot Path:-&gt;H:\WorkDaySuite_Playwright/WorkdayFailedScreenshot/2024-11-08T13-59-27-812Z.png</t>
-  </si>
-  <si>
-    <t>Alexander</t>
-  </si>
-  <si>
-    <t>Runolfsson</t>
-  </si>
-  <si>
-    <t>Auto 9784745</t>
+    <t>10652358</t>
+  </si>
+  <si>
+    <t>Danny</t>
+  </si>
+  <si>
+    <t>Quitzon</t>
+  </si>
+  <si>
+    <t>Auto 9952567</t>
   </si>
   <si>
     <t>Test_13</t>
   </si>
   <si>
-    <t>10652263</t>
-  </si>
-  <si>
-    <t>134 Store Management (Zizez Cofyze (8702319))</t>
-  </si>
-  <si>
-    <t>Jules</t>
-  </si>
-  <si>
-    <t>Kilback</t>
-  </si>
-  <si>
-    <t>Potomac Mills,Virginia</t>
-  </si>
-  <si>
-    <t>Virginia</t>
-  </si>
-  <si>
-    <t>Auto 20746150</t>
-  </si>
-  <si>
-    <t>USA - Tier 1</t>
-  </si>
-  <si>
-    <t>Test_14</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Test failed for 'Vita Abernathy' Employee:{10652291}Error: [2mexpect([22m[31mreceived[39m[2m).[22mtoEqual[2m([22m[32mexpected[39m[2m) // deep equality[22m
+    <t xml:space="preserve">Test failed for 'Mark Ondricka' Employee:{10652378}Error: [2mexpect([22m[31mreceived[39m[2m).[22mtoEqual[2m([22m[32mexpected[39m[2m) // deep equality[22m
 Expected: [32m"USA Pay Group"[39m
 Received: [31m"[7mPlease select a [27mUSA Pay Group"[39m</t>
   </si>
   <si>
-    <t>Vita</t>
-  </si>
-  <si>
-    <t>Abernathy</t>
-  </si>
-  <si>
-    <t>Auto 2408459</t>
+    <t>134 Store Management (Zizez Cofyze (8702319))</t>
+  </si>
+  <si>
+    <t>Mark</t>
+  </si>
+  <si>
+    <t>Ondricka</t>
+  </si>
+  <si>
+    <t>Potomac Mills,Virginia</t>
+  </si>
+  <si>
+    <t>Virginia</t>
+  </si>
+  <si>
+    <t>Auto 85520936</t>
   </si>
   <si>
     <t>USA - Tier 3</t>
   </si>
   <si>
+    <t>Test_14</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Test failed for 'Madelynn Yost' Employee:{10652380}Error: [2mexpect([22m[31mreceived[39m[2m).[22mtoEqual[2m([22m[32mexpected[39m[2m) // deep equality[22m
+Expected: [32m"USA Pay Group"[39m
+Received: [31m"[7mPlease select a [27mUSA Pay Group"[39m</t>
+  </si>
+  <si>
+    <t>Madelynn</t>
+  </si>
+  <si>
+    <t>Yost</t>
+  </si>
+  <si>
+    <t>Auto 65006340</t>
+  </si>
+  <si>
     <t>Test_15</t>
   </si>
   <si>
-    <t xml:space="preserve">Test failed for 'Dante Lowe' Employee:{undefined}TimeoutError: locator.focus: Timeout 30000ms exceeded.
-Call log:
-  [2m- waiting for locator('//label[contains(.,\'Hire Date\')]/parent::div/following-sibling::div/descendant::input[@data-automation-id=\'dateSectionDay-input\']')[22m
-</t>
-  </si>
-  <si>
-    <t>Dante</t>
-  </si>
-  <si>
-    <t>Lowe</t>
-  </si>
-  <si>
-    <t>Auto 84946926</t>
+    <t xml:space="preserve">Test failed for 'Katelynn Rohan' Employee:{10652385}Error: [2mexpect([22m[31mreceived[39m[2m).[22mtoEqual[2m([22m[32mexpected[39m[2m) // deep equality[22m
+Expected: [32m"USA Pay Group"[39m
+Received: [31m"[7mPlease select a [27mUSA Pay Group"[39m</t>
+  </si>
+  <si>
+    <t>Katelynn</t>
+  </si>
+  <si>
+    <t>Rohan</t>
+  </si>
+  <si>
+    <t>Auto 79007249</t>
   </si>
   <si>
     <t>Test_16</t>
   </si>
   <si>
-    <t xml:space="preserve">Test failed for 'Dayana Harris' Employee:{undefined}TimeoutError: locator.click: Timeout 30000ms exceeded.
-Call log:
-  [2m- waiting for locator('//label[contains(.,\'Step\')]/parent::div/following-sibling::div//input[@placeholder=\'Search\']')[22m
-[2m  -   locator resolved to &lt;input value="" dir="ltr" width="280" tabindex="0" auto…/&gt;[22m
-[2m  - attempting click action[22m
-[2m  -   waiting for element to be visible, enabled and stable[22m
-[2m  -   element is visible, enabled and stable[22m
-[2m  -   scrolling into view if needed[22m
-[2m  -   done scrolling[22m
-[2m  -   &lt;p data-automation-id="promptOption" class="css-w0y…&gt;Initial Step - PAS - 16.25 USD&lt;/p&gt; from &lt;div tabindex="-1" class="css-3r73al-PillListContaine…&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
-[2m  - retrying click action, attempt #1[22m
-[2m  -   waiting for element to be visible, enabled and stable[22m
-[2m  -   element is visible, enabled and stable[22m
-[2m  -   scrolling into view if needed[22m
-[2m  -   done scrolling[22m
-[2m  -   &lt;p data-automation-id="promptOption" class="css-w0y…&gt;Initial Step - PAS - 16.25 USD&lt;/p&gt; from &lt;div tabindex="-1" class="css-3r73al-PillListContaine…&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
-[2m  - retrying click action, attempt #2[22m
-[2m  -   waiting 20ms[22m
-[2m  -   waiting for element to be visible, enabled and stable[22m
-[2m  -   element is visible, enabled and stable[22m
-[2m  -   scrolling into view if needed[22m
-[2m  -   done scrolling[22m
-[2m  -   &lt;p data-automation-id="promptOption" class="css-w0y…&gt;Initial Step - PAS - 16.25 USD&lt;/p&gt; from &lt;div tabindex="-1" class="css-3r73al-PillListContaine…&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
-[2m  - retrying click action, attempt #3[22m
-[2m  -   waiting 100ms[22m
-[2m  -   waiting for element to be visible, enabled and stable[22m
-[2m  -   element is visible, enabled and stable[22m
-[2m  -   scrolling into view if needed[22m
-[2m  -   done scrolling[22m
-[2m  -   &lt;p data-automation-id="promptOption" class="css-w0y…&gt;Initial Step - PAS - 16.25 USD&lt;/p&gt; from &lt;div tabindex="-1" class="css-3r73al-PillListContaine…&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
-[2m  - retrying click action, attempt #4[22m
-[2m  -   waiting 100ms[22m
-[2m  -   waiting for element to be visible, enabled and stable[22m
-[2m  -   element is visible, enabled and stable[22m
-[2m  -   scrolling into view if needed[22m
-[2m  -   done scrolling[22m
-[2m  -   &lt;p data-automation-id="promptOption" class="css-w0y…&gt;Initial Step - PAS - 16.25 USD&lt;/p&gt; from &lt;div tabindex="-1" class="css-3r73al-PillListContaine…&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
-[2m  - retrying click action, attempt #5[22m
-[2m  -   waiting 500ms[22m
-[2m  -   waiting for element to be visible, enabled and stable[22m
-[2m  -   element is visible, enabled and stable[22m
-[2m  -   scrolling into view if needed[22m
-[2m  -   done scrolling[22m
-[2m  -   &lt;p data-automation-id="promptOption" class="css-w0y…&gt;Initial Step - PAS - 16.25 USD&lt;/p&gt; from &lt;div tabindex="-1" class="css-3r73al-PillListContaine…&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
-[2m  - retrying click action, attempt #6[22m
-[2m  -   waiting 500ms[22m
-[2m  -   waiting for element to be visible, enabled and stable[22m
-[2m  -   element is visible, enabled and stable[22m
-[2m  -   scrolling into view if needed[22m
-[2m  -   done scrolling[22m
-[2m  -   &lt;p data-automation-id="promptOption" class="css-w0y…&gt;Initial Step - PAS - 16.25 USD&lt;/p&gt; from &lt;div tabindex="-1" class="css-3r73al-PillListContaine…&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
-[2m  - retrying click action, attempt #7[22m
-[2m  -   waiting 500ms[22m
-[2m  -   waiting for element to be visible, enabled and stable[22m
-[2m  -   element is visible, enabled and stable[22m
-[2m  -   scrolling into view if needed[22m
-[2m  -   done scrolling[22m
-[2m  -   &lt;p data-automation-id="promptOption" class="css-w0y…&gt;Initial Step - PAS - 16.25 USD&lt;/p&gt; from &lt;div tabindex="-1" class="css-3r73al-PillListContaine…&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
-[2m  - retrying click action, attempt #8[22m
-[2m  -   waiting 500ms[22m
-[2m  -   waiting for element to be visible, enabled and stable[22m
-[2m  -   element is visible, enabled and stable[22m
-[2m  -   scrolling into view if needed[22m
-[2m  -   done scrolling[22m
-[2m  -   &lt;p data-automation-id="promptOption" class="css-w0y…&gt;Initial Step - PAS - 16.25 USD&lt;/p&gt; from &lt;div tabindex="-1" class="css-3r73al-PillListContaine…&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
-[2m  - retrying click action, attempt #9[22m
-[2m  -   waiting 500ms[22m
-[2m  -   waiting for element to be visible, enabled and stable[22m
-[2m  -   element is visible, enabled and stable[22m
-[2m  -   scrolling into view if needed[22m
-[2m  -   done scrolling[22m
-[2m  -   &lt;p data-automation-id="promptOption" class="css-w0y…&gt;Initial Step - PAS - 16.25 USD&lt;/p&gt; from &lt;div tabindex="-1" class="css-3r73al-PillListContaine…&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
-[2m  - retrying click action, attempt #10[22m
-[2m  -   waiting 500ms[22m
-[2m  -   waiting for element to be visible, enabled and stable[22m
-[2m  -   element is visible, enabled and stable[22m
-[2m  -   scrolling into view if needed[22m
-[2m  -   done scrolling[22m
-[2m  -   &lt;p data-automation-id="promptOption" class="css-w0y…&gt;Initial Step - PAS - 16.25 USD&lt;/p&gt; from &lt;div tabindex="-1" class="css-3r73al-PillListContaine…&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
-[2m  - retrying click action, attempt #11[22m
-[2m  -   waiting 500ms[22m
-[2m  -   waiting for element to be visible, enabled and stable[22m
-[2m  -   element is visible, enabled and stable[22m
-[2m  -   scrolling into view if needed[22m
-[2m  -   done scrolling[22m
-[2m  -   &lt;p data-automation-id="promptOption" class="css-w0y…&gt;Initial Step - PAS - 16.25 USD&lt;/p&gt; from &lt;div tabindex="-1" class="css-3r73al-PillListContaine…&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
-[2m  - retrying click action, attempt #12[22m
-[2m  -   waiting 500ms[22m
-[2m  -   waiting for element to be visible, enabled and stable[22m
-[2m  -   element is visible, enabled and stable[22m
-[2m  -   scrolling into view if needed[22m
-[2m  -   done scrolling[22m
-[2m  -   &lt;p data-automation-id="promptOption" class="css-w0y…&gt;Initial Step - PAS - 16.25 USD&lt;/p&gt; from &lt;div tabindex="-1" class="css-3r73al-PillListContaine…&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
-[2m  - retrying click action, attempt #13[22m
-[2m  -   waiting 500ms[22m
-[2m  -   waiting for element to be visible, enabled and stable[22m
-[2m  -   element is visible, enabled and stable[22m
-[2m  -   scrolling into view if needed[22m
-[2m  -   done scrolling[22m
-[2m  -   &lt;p data-automation-id="promptOption" class="css-w0y…&gt;Initial Step - PAS - 16.25 USD&lt;/p&gt; from &lt;div tabindex="-1" class="css-3r73al-PillListContaine…&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
-[2m  - retrying click action, attempt #14[22m
-[2m  -   waiting 500ms[22m
-[2m  -   waiting for element to be visible, enabled and stable[22m
-[2m  -   element is visible, enabled and stable[22m
-[2m  -   scrolling into view if needed[22m
-[2m  -   done scrolling[22m
-[2m  -   &lt;p data-automation-id="promptOption" class="css-w0y…&gt;Initial Step - PAS - 16.25 USD&lt;/p&gt; from &lt;div tabindex="-1" class="css-3r73al-PillListContaine…&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
-[2m  - retrying click action, attempt #15[22m
-[2m  -   waiting 500ms[22m
-[2m  -   waiting for element to be visible, enabled and stable[22m
-[2m  -   element is visible, enabled and stable[22m
-[2m  -   scrolling into view if needed[22m
-[2m  -   done scrolling[22m
-[2m  -   &lt;p data-automation-id="promptOption" class="css-w0y…&gt;Initial Step - PAS - 16.25 USD&lt;/p&gt; from &lt;div tabindex="-1" class="css-3r73al-PillListContaine…&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
-[2m  - retrying click action, attempt #16[22m
-[2m  -   waiting 500ms[22m
-[2m  -   waiting for element to be visible, enabled and stable[22m
-[2m  -   element is visible, enabled and stable[22m
-[2m  -   scrolling into view if needed[22m
-[2m  -   done scrolling[22m
-[2m  -   &lt;p data-automation-id="promptOption" class="css-w0y…&gt;Initial Step - PAS - 16.25 USD&lt;/p&gt; from &lt;div tabindex="-1" class="css-3r73al-PillListContaine…&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
-[2m  - retrying click action, attempt #17[22m
-[2m  -   waiting 500ms[22m
-[2m  -   waiting for element to be visible, enabled and stable[22m
-[2m  -   element is visible, enabled and stable[22m
-[2m  -   scrolling into view if needed[22m
-[2m  -   done scrolling[22m
-[2m  -   &lt;p data-automation-id="promptOption" class="css-w0y…&gt;Initial Step - PAS - 16.25 USD&lt;/p&gt; from &lt;div tabindex="-1" class="css-3r73al-PillListContaine…&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
-[2m  - retrying click action, attempt #18[22m
-[2m  -   waiting 500ms[22m
-[2m  -   waiting for element to be visible, enabled and stable[22m
-[2m  -   element is visible, enabled and stable[22m
-[2m  -   scrolling into view if needed[22m
-[2m  -   done scrolling[22m
-[2m  -   &lt;p data-automation-id="promptOption" class="css-w0y…&gt;Initial Step - PAS - 16.25 USD&lt;/p&gt; from &lt;div tabindex="-1" class="css-3r73al-PillListContaine…&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
-[2m  - retrying click action, attempt #19[22m
-[2m  -   waiting 500ms[22m
-[2m  -   waiting for element to be visible, enabled and stable[22m
-[2m  -   element is visible, enabled and stable[22m
-[2m  -   scrolling into view if needed[22m
-[2m  -   done scrolling[22m
-[2m  -   &lt;p data-automation-id="promptOption" class="css-w0y…&gt;Initial Step - PAS - 16.25 USD&lt;/p&gt; from &lt;div tabindex="-1" class="css-3r73al-PillListContaine…&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
-[2m  - retrying click action, attempt #20[22m
-[2m  -   waiting 500ms[22m
-[2m  -   waiting for element to be visible, enabled and stable[22m
-[2m  -   element is visible, enabled and stable[22m
-[2m  -   scrolling into view if needed[22m
-[2m  -   done scrolling[22m
-[2m  -   &lt;p data-automation-id="promptOption" class="css-w0y…&gt;Initial Step - PAS - 16.25 USD&lt;/p&gt; from &lt;div tabindex="-1" class="css-3r73al-PillListContaine…&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
-[2m  - retrying click action, attempt #21[22m
-[2m  -   waiting 500ms[22m
-[2m  -   waiting for element to be visible, enabled and stable[22m
-[2m  -   element is visible, enabled and stable[22m
-[2m  -   scrolling into view if needed[22m
-[2m  -   done scrolling[22m
-[2m  -   &lt;p data-automation-id="promptOption" class="css-w0y…&gt;Initial Step - PAS - 16.25 USD&lt;/p&gt; from &lt;div tabindex="-1" class="css-3r73al-PillListContaine…&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
-[2m  - retrying click action, attempt #22[22m
-[2m  -   waiting 500ms[22m
-[2m  -   waiting for element to be visible, enabled and stable[22m
-[2m  -   element is visible, enabled and stable[22m
-[2m  -   scrolling into view if needed[22m
-[2m  -   done scrolling[22m
-[2m  -   &lt;p data-automation-id="promptOption" class="css-w0y…&gt;Initial Step - PAS - 16.25 USD&lt;/p&gt; from &lt;div tabindex="-1" class="css-3r73al-PillListContaine…&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
-[2m  - retrying click action, attempt #23[22m
-[2m  -   waiting 500ms[22m
-[2m  -   waiting for element to be visible, enabled and stable[22m
-[2m  -   element is visible, enabled and stable[22m
-[2m  -   scrolling into view if needed[22m
-[2m  -   done scrolling[22m
-[2m  -   &lt;p data-automation-id="promptOption" class="css-w0y…&gt;Initial Step - PAS - 16.25 USD&lt;/p&gt; from &lt;div tabindex="-1" class="css-3r73al-PillListContaine…&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
-[2m  - retrying click action, attempt #24[22m
-[2m  -   waiting 500ms[22m
-[2m  -   waiting for element to be visible, enabled and stable[22m
-[2m  -   element is visible, enabled and stable[22m
-[2m  -   scrolling into view if needed[22m
-[2m  -   done scrolling[22m
-[2m  -   &lt;p data-automation-id="promptOption" class="css-w0y…&gt;Initial Step - PAS - 16.25 USD&lt;/p&gt; from &lt;div tabindex="-1" class="css-3r73al-PillListContaine…&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
-[2m  - retrying click action, attempt #25[22m
-[2m  -   waiting 500ms[22m
-[2m  -   waiting for element to be visible, enabled and stable[22m
-[2m  -   element is visible, enabled and stable[22m
-[2m  -   scrolling into view if needed[22m
-[2m  -   done scrolling[22m
-[2m  -   &lt;p data-automation-id="promptOption" class="css-w0y…&gt;Initial Step - PAS - 16.25 USD&lt;/p&gt; from &lt;div tabindex="-1" class="css-3r73al-PillListContaine…&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
-[2m  - retrying click action, attempt #26[22m
-[2m  -   waiting 500ms[22m
-[2m  -   waiting for element to be visible, enabled and stable[22m
-[2m  -   element is visible, enabled and stable[22m
-[2m  -   scrolling into view if needed[22m
-[2m  -   done scrolling[22m
-[2m  -   &lt;p data-automation-id="promptOption" class="css-w0y…&gt;Initial Step - PAS - 16.25 USD&lt;/p&gt; from &lt;div tabindex="-1" class="css-3r73al-PillListContaine…&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
-[2m  - retrying click action, attempt #27[22m
-[2m  -   waiting 500ms[22m
-[2m  -   waiting for element to be visible, enabled and stable[22m
-[2m  -   element is visible, enabled and stable[22m
-[2m  -   scrolling into view if needed[22m
-[2m  -   done scrolling[22m
-[2m  -   &lt;p data-automation-id="promptOption" class="css-w0y…&gt;Initial Step - PAS - 16.25 USD&lt;/p&gt; from &lt;div tabindex="-1" class="css-3r73al-PillListContaine…&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
-[2m  - retrying click action, attempt #28[22m
-[2m  -   waiting 500ms[22m
-[2m  -   waiting for element to be visible, enabled and stable[22m
-[2m  -   element is visible, enabled and stable[22m
-[2m  -   scrolling into view if needed[22m
-[2m  -   done scrolling[22m
-[2m  -   &lt;p data-automation-id="promptOption" class="css-w0y…&gt;Initial Step - PAS - 16.25 USD&lt;/p&gt; from &lt;div tabindex="-1" class="css-3r73al-PillListContaine…&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
-[2m  - retrying click action, attempt #29[22m
-[2m  -   waiting 500ms[22m
-[2m  -   waiting for element to be visible, enabled and stable[22m
-[2m  -   element is visible, enabled and stable[22m
-[2m  -   scrolling into view if needed[22m
-[2m  -   done scrolling[22m
-[2m  -   &lt;p data-automation-id="promptOption" class="css-w0y…&gt;Initial Step - PAS - 16.25 USD&lt;/p&gt; from &lt;div tabindex="-1" class="css-3r73al-PillListContaine…&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
-[2m  - retrying click action, attempt #30[22m
-[2m  -   waiting 500ms[22m
-[2m  -   waiting for element to be visible, enabled and stable[22m
-[2m  -   element is visible, enabled and stable[22m
-[2m  -   scrolling into view if needed[22m
-[2m  -   done scrolling[22m
-[2m  -   &lt;p data-automation-id="promptOption" class="css-w0y…&gt;Initial Step - PAS - 16.25 USD&lt;/p&gt; from &lt;div tabindex="-1" class="css-3r73al-PillListContaine…&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
-[2m  - retrying click action, attempt #31[22m
-[2m  -   waiting 500ms[22m
-[2m  -   waiting for element to be visible, enabled and stable[22m
-[2m  -   element is visible, enabled and stable[22m
-[2m  -   scrolling into view if needed[22m
-[2m  -   done scrolling[22m
-[2m  -   &lt;p data-automation-id="promptOption" class="css-w0y…&gt;Initial Step - PAS - 16.25 USD&lt;/p&gt; from &lt;div tabindex="-1" class="css-3r73al-PillListContaine…&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
-[2m  - retrying click action, attempt #32[22m
-[2m  -   waiting 500ms[22m
-[2m  -   waiting for element to be visible, enabled and stable[22m
-[2m  -   element is visible, enabled and stable[22m
-[2m  -   scrolling into view if needed[22m
-[2m  -   done scrolling[22m
-[2m  -   &lt;p data-automation-id="promptOption" class="css-w0y…&gt;Initial Step - PAS - 16.25 USD&lt;/p&gt; from &lt;div tabindex="-1" class="css-3r73al-PillListContaine…&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
-[2m  - retrying click action, attempt #33[22m
-[2m  -   waiting 500ms[22m
-[2m  -   waiting for element to be visible, enabled and stable[22m
-[2m  -   element is visible, enabled and stable[22m
-[2m  -   scrolling into view if needed[22m
-[2m  -   done scrolling[22m
-[2m  -   &lt;p data-automation-id="promptOption" class="css-w0y…&gt;Initial Step - PAS - 16.25 USD&lt;/p&gt; from &lt;div tabindex="-1" class="css-3r73al-PillListContaine…&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
-[2m  - retrying click action, attempt #34[22m
-[2m  -   waiting 500ms[22m
-[2m  -   waiting for element to be visible, enabled and stable[22m
-[2m  -   element is visible, enabled and stable[22m
-[2m  -   scrolling into view if needed[22m
-[2m  -   done scrolling[22m
-[2m  -   &lt;p data-automation-id="promptOption" class="css-w0y…&gt;Initial Step - PAS - 16.25 USD&lt;/p&gt; from &lt;div tabindex="-1" class="css-3r73al-PillListContaine…&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
-[2m  - retrying click action, attempt #35[22m
-[2m  -   waiting 500ms[22m
-[2m  -   waiting for element to be visible, enabled and stable[22m
-[2m  -   element is visible, enabled and stable[22m
-[2m  -   scrolling into view if needed[22m
-[2m  -   done scrolling[22m
-[2m  -   &lt;p data-automation-id="promptOption" class="css-w0y…&gt;Initial Step - PAS - 16.25 USD&lt;/p&gt; from &lt;div tabindex="-1" class="css-3r73al-PillListContaine…&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
-[2m  - retrying click action, attempt #36[22m
-[2m  -   waiting 500ms[22m
-[2m  -   waiting for element to be visible, enabled and stable[22m
-[2m  -   element is visible, enabled and stable[22m
-[2m  -   scrolling into view if needed[22m
-[2m  -   done scrolling[22m
-[2m  -   &lt;p data-automation-id="promptOption" class="css-w0y…&gt;Initial Step - PAS - 16.25 USD&lt;/p&gt; from &lt;div tabindex="-1" class="css-3r73al-PillListContaine…&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
-[2m  - retrying click action, attempt #37[22m
-[2m  -   waiting 500ms[22m
-[2m  -   waiting for element to be visible, enabled and stable[22m
-[2m  -   element is visible, enabled and stable[22m
-[2m  -   scrolling into view if needed[22m
-[2m  -   done scrolling[22m
-[2m  -   &lt;p data-automation-id="promptOption" class="css-w0y…&gt;Initial Step - PAS - 16.25 USD&lt;/p&gt; from &lt;div tabindex="-1" class="css-3r73al-PillListContaine…&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
-[2m  - retrying click action, attempt #38[22m
-[2m  -   waiting 500ms[22m
-[2m  -   waiting for element to be visible, enabled and stable[22m
-[2m  -   element is visible, enabled and stable[22m
-[2m  -   scrolling into view if needed[22m
-[2m  -   done scrolling[22m
-[2m  -   &lt;p data-automation-id="promptOption" class="css-w0y…&gt;Initial Step - PAS - 16.25 USD&lt;/p&gt; from &lt;div tabindex="-1" class="css-3r73al-PillListContaine…&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
-[2m  - retrying click action, attempt #39[22m
-[2m  -   waiting 500ms[22m
-[2m  -   waiting for element to be visible, enabled and stable[22m
-[2m  -   element is visible, enabled and stable[22m
-[2m  -   scrolling into view if needed[22m
-[2m  -   done scrolling[22m
-[2m  -   &lt;p data-automation-id="promptOption" class="css-w0y…&gt;Initial Step - PAS - 16.25 USD&lt;/p&gt; from &lt;div tabindex="-1" class="css-3r73al-PillListContaine…&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
-[2m  - retrying click action, attempt #40[22m
-[2m  -   waiting 500ms[22m
-[2m  -   waiting for element to be visible, enabled and stable[22m
-[2m  -   element is visible, enabled and stable[22m
-[2m  -   scrolling into view if needed[22m
-[2m  -   done scrolling[22m
-[2m  -   &lt;p data-automation-id="promptOption" class="css-w0y…&gt;Initial Step - PAS - 16.25 USD&lt;/p&gt; from &lt;div tabindex="-1" class="css-3r73al-PillListContaine…&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
-[2m  - retrying click action, attempt #41[22m
-[2m  -   waiting 500ms[22m
-[2m  -   waiting for element to be visible, enabled and stable[22m
-[2m  -   element is visible, enabled and stable[22m
-[2m  -   scrolling into view if needed[22m
-[2m  -   done scrolling[22m
-[2m  -   &lt;p data-automation-id="promptOption" class="css-w0y…&gt;Initial Step - PAS - 16.25 USD&lt;/p&gt; from &lt;div tabindex="-1" class="css-3r73al-PillListContaine…&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
-[2m  - retrying click action, attempt #42[22m
-[2m  -   waiting 500ms[22m
-[2m  -   waiting for element to be visible, enabled and stable[22m
-[2m  -   element is visible, enabled and stable[22m
-[2m  -   scrolling into view if needed[22m
-[2m  -   done scrolling[22m
-[2m  -   &lt;p data-automation-id="promptOption" class="css-w0y…&gt;Initial Step - PAS - 16.25 USD&lt;/p&gt; from &lt;div tabindex="-1" class="css-3r73al-PillListContaine…&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
-[2m  - retrying click action, attempt #43[22m
-[2m  -   waiting 500ms[22m
-[2m  -   waiting for element to be visible, enabled and stable[22m
-[2m  -   element is visible, enabled and stable[22m
-[2m  -   scrolling into view if needed[22m
-[2m  -   done scrolling[22m
-[2m  -   &lt;p data-automation-id="promptOption" class="css-w0y…&gt;Initial Step - PAS - 16.25 USD&lt;/p&gt; from &lt;div tabindex="-1" class="css-3r73al-PillListContaine…&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
-[2m  - retrying click action, attempt #44[22m
-[2m  -   waiting 500ms[22m
-[2m  -   waiting for element to be visible, enabled and stable[22m
-[2m  -   element is visible, enabled and stable[22m
-[2m  -   scrolling into view if needed[22m
-[2m  -   done scrolling[22m
-[2m  -   &lt;p data-automation-id="promptOption" class="css-w0y…&gt;Initial Step - PAS - 16.25 USD&lt;/p&gt; from &lt;div tabindex="-1" class="css-3r73al-PillListContaine…&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
-[2m  - retrying click action, attempt #45[22m
-[2m  -   waiting 500ms[22m
-[2m  -   waiting for element to be visible, enabled and stable[22m
-[2m  -   element is visible, enabled and stable[22m
-[2m  -   scrolling into view if needed[22m
-[2m  -   done scrolling[22m
-[2m  -   &lt;p data-automation-id="promptOption" class="css-w0y…&gt;Initial Step - PAS - 16.25 USD&lt;/p&gt; from &lt;div tabindex="-1" class="css-3r73al-PillListContaine…&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
-[2m  - retrying click action, attempt #46[22m
-[2m  -   waiting 500ms[22m
-[2m  -   waiting for element to be visible, enabled and stable[22m
-[2m  -   element is visible, enabled and stable[22m
-[2m  -   scrolling into view if needed[22m
-[2m  -   done scrolling[22m
-[2m  -   &lt;p data-automation-id="promptOption" class="css-w0y…&gt;Initial Step - PAS - 16.25 USD&lt;/p&gt; from &lt;div tabindex="-1" class="css-3r73al-PillListContaine…&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
-[2m  - retrying click action, attempt #47[22m
-[2m  -   waiting 500ms[22m
-[2m  -   waiting for element to be visible, enabled and stable[22m
-[2m  -   element is visible, enabled and stable[22m
-[2m  -   scrolling into view if needed[22m
-[2m  -   done scrolling[22m
-[2m  -   &lt;p data-automation-id="promptOption" class="css-w0y…&gt;Initial Step - PAS - 16.25 USD&lt;/p&gt; from &lt;div tabindex="-1" class="css-3r73al-PillListContaine…&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
-[2m  - retrying click action, attempt #48[22m
-[2m  -   waiting 500ms[22m
-[2m  -   waiting for element to be visible, enabled and stable[22m
-[2m  -   element is visible, enabled and stable[22m
-[2m  -   scrolling into view if needed[22m
-[2m  -   done scrolling[22m
-[2m  -   &lt;p data-automation-id="promptOption" class="css-w0y…&gt;Initial Step - PAS - 16.25 USD&lt;/p&gt; from &lt;div tabindex="-1" class="css-3r73al-PillListContaine…&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
-[2m  - retrying click action, attempt #49[22m
-[2m  -   waiting 500ms[22m
-[2m  -   waiting for element to be visible, enabled and stable[22m
-[2m  -   element is visible, enabled and stable[22m
-[2m  -   scrolling into view if needed[22m
-[2m  -   done scrolling[22m
-[2m  -   &lt;p data-automation-id="promptOption" class="css-w0y…&gt;Initial Step - PAS - 16.25 USD&lt;/p&gt; from &lt;div tabindex="-1" class="css-3r73al-PillListContaine…&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
-[2m  - retrying click action, attempt #50[22m
-[2m  -   waiting 500ms[22m
-[2m  -   waiting for element to be visible, enabled and stable[22m
-[2m  -   element is visible, enabled and stable[22m
-[2m  -   scrolling into view if needed[22m
-[2m  -   done scrolling[22m
-[2m  -   &lt;p data-automation-id="promptOption" class="css-w0y…&gt;Initial Step - PAS - 16.25 USD&lt;/p&gt; from &lt;div tabindex="-1" class="css-3r73al-PillListContaine…&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
-[2m  - retrying click action, attempt #51[22m
-[2m  -   waiting 500ms[22m
-[2m  -   waiting for element to be visible, enabled and stable[22m
-[2m  -   element is visible, enabled and stable[22m
-[2m  -   scrolling into view if needed[22m
-[2m  -   done scrolling[22m
-[2m  -   &lt;p data-automation-id="promptOption" class="css-w0y…&gt;Initial Step - PAS - 16.25 USD&lt;/p&gt; from &lt;div tabindex="-1" class="css-3r73al-PillListContaine…&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
-[2m  - retrying click action, attempt #52[22m
-[2m  -   waiting 500ms[22m
-[2m  -   waiting for element to be visible, enabled and stable[22m
-[2m  -   element is visible, enabled and stable[22m
-[2m  -   scrolling into view if needed[22m
-[2m  -   done scrolling[22m
-[2m  -   &lt;p data-automation-id="promptOption" class="css-w0y…&gt;Initial Step - PAS - 16.25 USD&lt;/p&gt; from &lt;div tabindex="-1" class="css-3r73al-PillListContaine…&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
-[2m  - retrying click action, attempt #53[22m
-[2m  -   waiting 500ms[22m
-</t>
+    <t xml:space="preserve">Test failed for 'Glen Wolf' Employee:{10652395}Error: [2mexpect([22m[31mreceived[39m[2m).[22mtoEqual[2m([22m[32mexpected[39m[2m) // deep equality[22m
+Expected: [32m"USA Pay Group"[39m
+Received: [31m"[7mPlease select a [27mUSA Pay Group"[39m</t>
   </si>
   <si>
     <t>108 Recruitment (Pepog Bizyse (10240565))</t>
   </si>
   <si>
-    <t>Dayana</t>
-  </si>
-  <si>
-    <t>Harris</t>
+    <t>Glen</t>
+  </si>
+  <si>
+    <t>Wolf</t>
   </si>
   <si>
     <t>No</t>
@@ -1048,12 +685,6 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFFF00"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="FFF2DCDB"/>
         <bgColor rgb="FF000000"/>
       </patternFill>
@@ -1062,6 +693,12 @@
       <patternFill patternType="solid">
         <fgColor rgb="FFFFFF00"/>
         <bgColor rgb="FF000000"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
       </patternFill>
     </fill>
   </fills>
@@ -1135,7 +772,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="53">
+  <cellXfs count="54">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1209,17 +846,15 @@
       <alignment horizontal="left"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="164" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left"/>
       <protection locked="0"/>
     </xf>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="9" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="8" fillId="6" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="9" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="8" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="14" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
@@ -1228,14 +863,14 @@
     <xf numFmtId="0" fontId="8" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="6" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -1253,16 +888,19 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="7" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="7" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="6" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1596,7 +1234,7 @@
     <col min="42" max="42" width="4.90625" customWidth="1"/>
     <col min="43" max="43" width="8.7265625" customWidth="1"/>
     <col min="44" max="44" width="15.6328125" customWidth="1"/>
-    <col min="45" max="45" width="15.26953125" customWidth="1"/>
+    <col min="45" max="45" width="17.36328125" customWidth="1"/>
     <col min="46" max="46" width="7.26953125" customWidth="1"/>
     <col min="47" max="47" width="14.1796875" customWidth="1"/>
     <col min="48" max="48" width="13.90625" customWidth="1"/>
@@ -1817,7 +1455,7 @@
       </c>
       <c r="L2" s="14">
         <f>TODAY()-31</f>
-        <v>45576</v>
+        <v>45577</v>
       </c>
       <c r="M2" s="9" t="s">
         <v>57</v>
@@ -1854,11 +1492,11 @@
       </c>
       <c r="X2" s="19">
         <f>L2</f>
-        <v>45576</v>
+        <v>45577</v>
       </c>
       <c r="Y2" s="14">
         <f>TODAY()+20</f>
-        <v>45627</v>
+        <v>45628</v>
       </c>
       <c r="Z2" s="20" t="s">
         <v>69</v>
@@ -1918,7 +1556,8 @@
         <v>82</v>
       </c>
       <c r="AS2" s="28">
-        <v>985891654</v>
+        <f t="array" ref="AS2:AS17">_xlfn.RANDARRAY(16,1,123456789,999999999,FALSE)</f>
+        <v>382384988.3993381</v>
       </c>
       <c r="AT2" s="22" t="s">
         <v>83</v>
@@ -1958,14 +1597,14 @@
       <c r="A3" t="s">
         <v>88</v>
       </c>
-      <c r="B3">
-        <v>10652157</v>
+      <c r="B3" t="s">
+        <v>89</v>
       </c>
       <c r="C3" s="7" t="s">
         <v>55</v>
       </c>
       <c r="D3" s="8" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="E3" s="26" t="s">
         <v>57</v>
@@ -1974,10 +1613,10 @@
         <v>58</v>
       </c>
       <c r="G3" s="32" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="H3" s="33" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="I3" s="26" t="s">
         <v>61</v>
@@ -2034,13 +1673,13 @@
         <v>69</v>
       </c>
       <c r="AA3" s="38" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="AB3" s="39" t="s">
         <v>71</v>
       </c>
       <c r="AC3" s="40" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="AD3" s="39" t="s">
         <v>73</v>
@@ -2087,8 +1726,8 @@
       <c r="AR3" s="26" t="s">
         <v>82</v>
       </c>
-      <c r="AS3" s="41">
-        <v>984533287</v>
+      <c r="AS3" s="28">
+        <v>520899656.7887391</v>
       </c>
       <c r="AT3" s="39" t="s">
         <v>83</v>
@@ -2126,10 +1765,10 @@
     </row>
     <row r="4" ht="14.5" customHeight="1" spans="1:56" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="B4" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="C4" s="7" t="s">
         <v>55</v>
@@ -2144,10 +1783,10 @@
         <v>58</v>
       </c>
       <c r="G4" s="11" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="H4" s="12" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="I4" s="13" t="s">
         <v>61</v>
@@ -2160,7 +1799,7 @@
       </c>
       <c r="L4" s="14">
         <f>TODAY()-31</f>
-        <v>45576</v>
+        <v>45577</v>
       </c>
       <c r="M4" s="9" t="s">
         <v>57</v>
@@ -2197,23 +1836,23 @@
       </c>
       <c r="X4" s="19">
         <f>L4</f>
-        <v>45576</v>
+        <v>45577</v>
       </c>
       <c r="Y4" s="14">
         <f>TODAY()+20</f>
-        <v>45627</v>
+        <v>45628</v>
       </c>
       <c r="Z4" s="20" t="s">
         <v>69</v>
       </c>
       <c r="AA4" s="38" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="AB4" s="22" t="s">
         <v>71</v>
       </c>
       <c r="AC4" s="46" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="AD4" s="22" t="s">
         <v>73</v>
@@ -2261,7 +1900,7 @@
         <v>82</v>
       </c>
       <c r="AS4" s="28">
-        <v>909874389</v>
+        <v>557812545.4056697</v>
       </c>
       <c r="AT4" s="22" t="s">
         <v>83</v>
@@ -2299,16 +1938,16 @@
     </row>
     <row r="5" ht="14.5" customHeight="1" spans="1:56" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>100</v>
-      </c>
-      <c r="B5">
-        <v>10652162</v>
+        <v>101</v>
+      </c>
+      <c r="B5" t="s">
+        <v>102</v>
       </c>
       <c r="C5" s="7" t="s">
         <v>55</v>
       </c>
       <c r="D5" s="47" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="E5" s="9" t="s">
         <v>57</v>
@@ -2317,10 +1956,10 @@
         <v>58</v>
       </c>
       <c r="G5" s="11" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="H5" s="12" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="I5" s="13" t="s">
         <v>61</v>
@@ -2333,7 +1972,7 @@
       </c>
       <c r="L5" s="14">
         <f>TODAY()-31</f>
-        <v>45576</v>
+        <v>45577</v>
       </c>
       <c r="M5" s="9" t="s">
         <v>57</v>
@@ -2345,16 +1984,16 @@
         <v>64</v>
       </c>
       <c r="P5" s="15" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="Q5" s="16">
         <v>19102</v>
       </c>
       <c r="R5" s="13" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="S5" s="13" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="T5" s="13" t="s">
         <v>63</v>
@@ -2370,17 +2009,17 @@
       </c>
       <c r="X5" s="19">
         <f>L5</f>
-        <v>45576</v>
+        <v>45577</v>
       </c>
       <c r="Y5" s="14">
         <f>TODAY()+20</f>
-        <v>45627</v>
+        <v>45628</v>
       </c>
       <c r="Z5" s="20" t="s">
         <v>69</v>
       </c>
       <c r="AA5" s="38" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="AB5" s="22" t="s">
         <v>71</v>
@@ -2391,7 +2030,7 @@
       <c r="AD5" s="22" t="s">
         <v>73</v>
       </c>
-      <c r="AE5" s="28">
+      <c r="AE5" s="48">
         <v>114</v>
       </c>
       <c r="AF5" s="24" t="s">
@@ -2421,7 +2060,7 @@
       <c r="AN5" s="22" t="s">
         <v>79</v>
       </c>
-      <c r="AO5" s="48" t="s">
+      <c r="AO5" s="49" t="s">
         <v>80</v>
       </c>
       <c r="AP5" s="9" t="s">
@@ -2434,7 +2073,7 @@
         <v>82</v>
       </c>
       <c r="AS5" s="28">
-        <v>876529008</v>
+        <v>989456017.6990048</v>
       </c>
       <c r="AT5" s="22" t="s">
         <v>83</v>
@@ -2472,16 +2111,16 @@
     </row>
     <row r="6" ht="14.5" customHeight="1" spans="1:56" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>107</v>
-      </c>
-      <c r="B6">
-        <v>10652165</v>
+        <v>109</v>
+      </c>
+      <c r="B6" t="s">
+        <v>110</v>
       </c>
       <c r="C6" s="7" t="s">
         <v>55</v>
       </c>
       <c r="D6" s="47" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="E6" s="9" t="s">
         <v>57</v>
@@ -2490,10 +2129,10 @@
         <v>58</v>
       </c>
       <c r="G6" s="11" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c r="H6" s="12" t="s">
-        <v>109</v>
+        <v>112</v>
       </c>
       <c r="I6" s="13" t="s">
         <v>61</v>
@@ -2506,7 +2145,7 @@
       </c>
       <c r="L6" s="14">
         <f>TODAY()-31</f>
-        <v>45576</v>
+        <v>45577</v>
       </c>
       <c r="M6" s="9" t="s">
         <v>57</v>
@@ -2518,16 +2157,16 @@
         <v>64</v>
       </c>
       <c r="P6" s="15" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="Q6" s="16">
         <v>19102</v>
       </c>
       <c r="R6" s="13" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="S6" s="13" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="T6" s="13" t="s">
         <v>63</v>
@@ -2543,23 +2182,23 @@
       </c>
       <c r="X6" s="19">
         <f>L6</f>
-        <v>45576</v>
+        <v>45577</v>
       </c>
       <c r="Y6" s="14">
         <f>TODAY()+20</f>
-        <v>45627</v>
+        <v>45628</v>
       </c>
       <c r="Z6" s="20" t="s">
         <v>69</v>
       </c>
       <c r="AA6" s="38" t="s">
-        <v>110</v>
+        <v>113</v>
       </c>
       <c r="AB6" s="22" t="s">
         <v>71</v>
       </c>
       <c r="AC6" s="46" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="AD6" s="22" t="s">
         <v>73</v>
@@ -2607,7 +2246,7 @@
         <v>82</v>
       </c>
       <c r="AS6" s="28">
-        <v>983121853</v>
+        <v>785876381.062165</v>
       </c>
       <c r="AT6" s="22" t="s">
         <v>83</v>
@@ -2645,16 +2284,16 @@
     </row>
     <row r="7" ht="14.5" customHeight="1" spans="1:56" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>111</v>
-      </c>
-      <c r="B7">
-        <v>10652168</v>
+        <v>114</v>
+      </c>
+      <c r="B7" t="s">
+        <v>115</v>
       </c>
       <c r="C7" s="7" t="s">
         <v>55</v>
       </c>
       <c r="D7" s="47" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="E7" s="9" t="s">
         <v>57</v>
@@ -2663,10 +2302,10 @@
         <v>58</v>
       </c>
       <c r="G7" s="11" t="s">
-        <v>112</v>
+        <v>116</v>
       </c>
       <c r="H7" s="12" t="s">
-        <v>113</v>
+        <v>117</v>
       </c>
       <c r="I7" s="13" t="s">
         <v>61</v>
@@ -2679,7 +2318,7 @@
       </c>
       <c r="L7" s="14">
         <f>TODAY()-31</f>
-        <v>45576</v>
+        <v>45577</v>
       </c>
       <c r="M7" s="9" t="s">
         <v>57</v>
@@ -2691,16 +2330,16 @@
         <v>64</v>
       </c>
       <c r="P7" s="15" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="Q7" s="16">
         <v>19102</v>
       </c>
       <c r="R7" s="13" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="S7" s="13" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="T7" s="13" t="s">
         <v>63</v>
@@ -2716,23 +2355,23 @@
       </c>
       <c r="X7" s="19">
         <f>L7</f>
-        <v>45576</v>
+        <v>45577</v>
       </c>
       <c r="Y7" s="14">
         <f>TODAY()+20</f>
-        <v>45627</v>
+        <v>45628</v>
       </c>
       <c r="Z7" s="20" t="s">
         <v>69</v>
       </c>
       <c r="AA7" s="38" t="s">
-        <v>114</v>
+        <v>118</v>
       </c>
       <c r="AB7" s="22" t="s">
         <v>71</v>
       </c>
       <c r="AC7" s="46" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="AD7" s="22" t="s">
         <v>73</v>
@@ -2780,7 +2419,7 @@
         <v>82</v>
       </c>
       <c r="AS7" s="28">
-        <v>981121855</v>
+        <v>804058163.7429827</v>
       </c>
       <c r="AT7" s="22" t="s">
         <v>83</v>
@@ -2818,16 +2457,16 @@
     </row>
     <row r="8" ht="14.5" customHeight="1" spans="1:56" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>115</v>
+        <v>119</v>
       </c>
       <c r="B8" t="s">
-        <v>116</v>
+        <v>120</v>
       </c>
       <c r="C8" s="7" t="s">
-        <v>117</v>
+        <v>121</v>
       </c>
       <c r="D8" s="8" t="s">
-        <v>118</v>
+        <v>122</v>
       </c>
       <c r="E8" s="26" t="s">
         <v>57</v>
@@ -2836,10 +2475,10 @@
         <v>58</v>
       </c>
       <c r="G8" s="32" t="s">
-        <v>119</v>
+        <v>123</v>
       </c>
       <c r="H8" s="33" t="s">
-        <v>120</v>
+        <v>124</v>
       </c>
       <c r="I8" s="26" t="s">
         <v>61</v>
@@ -2863,16 +2502,16 @@
         <v>64</v>
       </c>
       <c r="P8" s="35" t="s">
-        <v>121</v>
+        <v>125</v>
       </c>
       <c r="Q8" s="16">
         <v>19406</v>
       </c>
       <c r="R8" s="26" t="s">
-        <v>121</v>
+        <v>125</v>
       </c>
       <c r="S8" s="26" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="T8" s="26" t="s">
         <v>63</v>
@@ -2896,7 +2535,7 @@
         <v>69</v>
       </c>
       <c r="AA8" s="38" t="s">
-        <v>122</v>
+        <v>126</v>
       </c>
       <c r="AB8" s="39" t="s">
         <v>71</v>
@@ -2949,8 +2588,8 @@
       <c r="AR8" s="26" t="s">
         <v>82</v>
       </c>
-      <c r="AS8" s="41">
-        <v>789634888</v>
+      <c r="AS8" s="28">
+        <v>632508201.5898451</v>
       </c>
       <c r="AT8" s="39" t="s">
         <v>83</v>
@@ -2988,16 +2627,16 @@
     </row>
     <row r="9" ht="14.5" customHeight="1" spans="1:56" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>123</v>
+        <v>127</v>
       </c>
       <c r="B9" t="s">
-        <v>124</v>
+        <v>128</v>
       </c>
       <c r="C9" s="7" t="s">
         <v>55</v>
       </c>
       <c r="D9" s="8" t="s">
-        <v>118</v>
+        <v>122</v>
       </c>
       <c r="E9" s="9" t="s">
         <v>57</v>
@@ -3006,10 +2645,10 @@
         <v>58</v>
       </c>
       <c r="G9" s="11" t="s">
-        <v>125</v>
+        <v>129</v>
       </c>
       <c r="H9" s="12" t="s">
-        <v>126</v>
+        <v>130</v>
       </c>
       <c r="I9" s="13" t="s">
         <v>61</v>
@@ -3022,7 +2661,7 @@
       </c>
       <c r="L9" s="14">
         <f>TODAY()-31</f>
-        <v>45576</v>
+        <v>45577</v>
       </c>
       <c r="M9" s="9" t="s">
         <v>57</v>
@@ -3034,16 +2673,16 @@
         <v>64</v>
       </c>
       <c r="P9" s="35" t="s">
-        <v>121</v>
+        <v>125</v>
       </c>
       <c r="Q9" s="16">
         <v>19406</v>
       </c>
       <c r="R9" s="26" t="s">
-        <v>121</v>
+        <v>125</v>
       </c>
       <c r="S9" s="26" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="T9" s="13" t="s">
         <v>63</v>
@@ -3059,23 +2698,23 @@
       </c>
       <c r="X9" s="19">
         <f>L9</f>
-        <v>45576</v>
+        <v>45577</v>
       </c>
       <c r="Y9" s="14">
         <f>TODAY()+20</f>
-        <v>45627</v>
+        <v>45628</v>
       </c>
       <c r="Z9" s="20" t="s">
         <v>69</v>
       </c>
       <c r="AA9" s="38" t="s">
-        <v>127</v>
+        <v>131</v>
       </c>
       <c r="AB9" s="22" t="s">
         <v>71</v>
       </c>
       <c r="AC9" s="46" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="AD9" s="22" t="s">
         <v>73</v>
@@ -3123,7 +2762,7 @@
         <v>82</v>
       </c>
       <c r="AS9" s="28">
-        <v>9098237787</v>
+        <v>784364524.2209965</v>
       </c>
       <c r="AT9" s="22" t="s">
         <v>83</v>
@@ -3161,16 +2800,16 @@
     </row>
     <row r="10" ht="14.5" customHeight="1" spans="1:56" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>128</v>
+        <v>132</v>
       </c>
       <c r="B10" t="s">
-        <v>129</v>
+        <v>133</v>
       </c>
       <c r="C10" s="7" t="s">
         <v>55</v>
       </c>
       <c r="D10" s="8" t="s">
-        <v>118</v>
+        <v>122</v>
       </c>
       <c r="E10" s="9" t="s">
         <v>57</v>
@@ -3179,10 +2818,10 @@
         <v>58</v>
       </c>
       <c r="G10" s="11" t="s">
-        <v>130</v>
+        <v>134</v>
       </c>
       <c r="H10" s="12" t="s">
-        <v>131</v>
+        <v>135</v>
       </c>
       <c r="I10" s="13" t="s">
         <v>61</v>
@@ -3195,7 +2834,7 @@
       </c>
       <c r="L10" s="14">
         <f>TODAY()-31</f>
-        <v>45576</v>
+        <v>45577</v>
       </c>
       <c r="M10" s="9" t="s">
         <v>57</v>
@@ -3207,16 +2846,16 @@
         <v>64</v>
       </c>
       <c r="P10" s="35" t="s">
-        <v>121</v>
+        <v>125</v>
       </c>
       <c r="Q10" s="16">
         <v>19406</v>
       </c>
       <c r="R10" s="26" t="s">
-        <v>121</v>
+        <v>125</v>
       </c>
       <c r="S10" s="26" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="T10" s="13" t="s">
         <v>63</v>
@@ -3232,23 +2871,23 @@
       </c>
       <c r="X10" s="19">
         <f>L10</f>
-        <v>45576</v>
+        <v>45577</v>
       </c>
       <c r="Y10" s="14">
         <f>TODAY()+20</f>
-        <v>45627</v>
+        <v>45628</v>
       </c>
       <c r="Z10" s="20" t="s">
         <v>69</v>
       </c>
       <c r="AA10" s="38" t="s">
-        <v>132</v>
+        <v>136</v>
       </c>
       <c r="AB10" s="22" t="s">
         <v>71</v>
       </c>
       <c r="AC10" s="46" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="AD10" s="22" t="s">
         <v>73</v>
@@ -3296,7 +2935,7 @@
         <v>82</v>
       </c>
       <c r="AS10" s="28">
-        <v>909120009</v>
+        <v>690276280.6384156</v>
       </c>
       <c r="AT10" s="22" t="s">
         <v>83</v>
@@ -3334,16 +2973,16 @@
     </row>
     <row r="11" ht="14.5" customHeight="1" spans="1:56" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>133</v>
+        <v>137</v>
       </c>
       <c r="B11" t="s">
-        <v>134</v>
+        <v>138</v>
       </c>
       <c r="C11" s="7" t="s">
         <v>55</v>
       </c>
-      <c r="D11" s="49" t="s">
-        <v>135</v>
+      <c r="D11" s="50" t="s">
+        <v>139</v>
       </c>
       <c r="E11" s="26" t="s">
         <v>57</v>
@@ -3352,10 +2991,10 @@
         <v>58</v>
       </c>
       <c r="G11" s="32" t="s">
-        <v>136</v>
+        <v>140</v>
       </c>
       <c r="H11" s="33" t="s">
-        <v>137</v>
+        <v>141</v>
       </c>
       <c r="I11" s="26" t="s">
         <v>61</v>
@@ -3379,16 +3018,16 @@
         <v>64</v>
       </c>
       <c r="P11" s="35" t="s">
-        <v>121</v>
+        <v>125</v>
       </c>
       <c r="Q11" s="16">
         <v>19090</v>
       </c>
       <c r="R11" s="35" t="s">
-        <v>121</v>
+        <v>125</v>
       </c>
       <c r="S11" s="26" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="T11" s="26" t="s">
         <v>63</v>
@@ -3412,7 +3051,7 @@
         <v>69</v>
       </c>
       <c r="AA11" s="38" t="s">
-        <v>138</v>
+        <v>142</v>
       </c>
       <c r="AB11" s="39" t="s">
         <v>71</v>
@@ -3453,7 +3092,7 @@
       <c r="AN11" s="39" t="s">
         <v>79</v>
       </c>
-      <c r="AO11" s="50" t="s">
+      <c r="AO11" s="51" t="s">
         <v>80</v>
       </c>
       <c r="AP11" s="26" t="s">
@@ -3465,8 +3104,8 @@
       <c r="AR11" s="26" t="s">
         <v>82</v>
       </c>
-      <c r="AS11" s="41">
-        <v>879234673</v>
+      <c r="AS11" s="28">
+        <v>501541083.3148836</v>
       </c>
       <c r="AT11" s="39" t="s">
         <v>83</v>
@@ -3504,16 +3143,16 @@
     </row>
     <row r="12" ht="14.5" customHeight="1" spans="1:56" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
+        <v>143</v>
+      </c>
+      <c r="B12" t="s">
+        <v>144</v>
+      </c>
+      <c r="C12" s="7" t="s">
+        <v>55</v>
+      </c>
+      <c r="D12" s="50" t="s">
         <v>139</v>
-      </c>
-      <c r="B12" t="s">
-        <v>140</v>
-      </c>
-      <c r="C12" s="7" t="s">
-        <v>117</v>
-      </c>
-      <c r="D12" s="49" t="s">
-        <v>135</v>
       </c>
       <c r="E12" s="9" t="s">
         <v>57</v>
@@ -3522,10 +3161,10 @@
         <v>58</v>
       </c>
       <c r="G12" s="11" t="s">
-        <v>141</v>
+        <v>145</v>
       </c>
       <c r="H12" s="12" t="s">
-        <v>142</v>
+        <v>146</v>
       </c>
       <c r="I12" s="13" t="s">
         <v>61</v>
@@ -3538,7 +3177,7 @@
       </c>
       <c r="L12" s="14">
         <f>TODAY()-31</f>
-        <v>45576</v>
+        <v>45577</v>
       </c>
       <c r="M12" s="9" t="s">
         <v>57</v>
@@ -3550,16 +3189,16 @@
         <v>64</v>
       </c>
       <c r="P12" s="35" t="s">
-        <v>121</v>
+        <v>125</v>
       </c>
       <c r="Q12" s="16">
         <v>19090</v>
       </c>
       <c r="R12" s="35" t="s">
-        <v>121</v>
+        <v>125</v>
       </c>
       <c r="S12" s="26" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="T12" s="13" t="s">
         <v>63</v>
@@ -3575,23 +3214,23 @@
       </c>
       <c r="X12" s="19">
         <f>L12</f>
-        <v>45576</v>
+        <v>45577</v>
       </c>
       <c r="Y12" s="14">
         <f>TODAY()+20</f>
-        <v>45627</v>
+        <v>45628</v>
       </c>
       <c r="Z12" s="20" t="s">
         <v>69</v>
       </c>
       <c r="AA12" s="38" t="s">
-        <v>143</v>
+        <v>147</v>
       </c>
       <c r="AB12" s="22" t="s">
         <v>71</v>
       </c>
       <c r="AC12" s="46" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="AD12" s="22" t="s">
         <v>73</v>
@@ -3626,7 +3265,7 @@
       <c r="AN12" s="22" t="s">
         <v>79</v>
       </c>
-      <c r="AO12" s="50" t="s">
+      <c r="AO12" s="51" t="s">
         <v>80</v>
       </c>
       <c r="AP12" s="9" t="s">
@@ -3639,7 +3278,7 @@
         <v>82</v>
       </c>
       <c r="AS12" s="28">
-        <v>983121853</v>
+        <v>660781998.1587614</v>
       </c>
       <c r="AT12" s="22" t="s">
         <v>83</v>
@@ -3677,16 +3316,16 @@
     </row>
     <row r="13" ht="14.5" customHeight="1" spans="1:56" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>144</v>
+        <v>148</v>
       </c>
       <c r="B13" t="s">
-        <v>145</v>
+        <v>149</v>
       </c>
       <c r="C13" s="7" t="s">
-        <v>117</v>
-      </c>
-      <c r="D13" s="49" t="s">
-        <v>135</v>
+        <v>55</v>
+      </c>
+      <c r="D13" s="50" t="s">
+        <v>139</v>
       </c>
       <c r="E13" s="9" t="s">
         <v>57</v>
@@ -3695,10 +3334,10 @@
         <v>58</v>
       </c>
       <c r="G13" s="11" t="s">
-        <v>146</v>
+        <v>150</v>
       </c>
       <c r="H13" s="12" t="s">
-        <v>147</v>
+        <v>151</v>
       </c>
       <c r="I13" s="13" t="s">
         <v>61</v>
@@ -3711,7 +3350,7 @@
       </c>
       <c r="L13" s="14">
         <f>TODAY()-31</f>
-        <v>45576</v>
+        <v>45577</v>
       </c>
       <c r="M13" s="9" t="s">
         <v>57</v>
@@ -3723,16 +3362,16 @@
         <v>64</v>
       </c>
       <c r="P13" s="35" t="s">
-        <v>121</v>
+        <v>125</v>
       </c>
       <c r="Q13" s="16">
         <v>19090</v>
       </c>
       <c r="R13" s="35" t="s">
-        <v>121</v>
+        <v>125</v>
       </c>
       <c r="S13" s="26" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="T13" s="13" t="s">
         <v>63</v>
@@ -3748,23 +3387,23 @@
       </c>
       <c r="X13" s="19">
         <f>L13</f>
-        <v>45576</v>
+        <v>45577</v>
       </c>
       <c r="Y13" s="14">
         <f>TODAY()+20</f>
-        <v>45627</v>
+        <v>45628</v>
       </c>
       <c r="Z13" s="20" t="s">
         <v>69</v>
       </c>
       <c r="AA13" s="38" t="s">
-        <v>148</v>
+        <v>152</v>
       </c>
       <c r="AB13" s="22" t="s">
         <v>71</v>
       </c>
       <c r="AC13" s="46" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="AD13" s="22" t="s">
         <v>73</v>
@@ -3799,7 +3438,7 @@
       <c r="AN13" s="22" t="s">
         <v>79</v>
       </c>
-      <c r="AO13" s="50" t="s">
+      <c r="AO13" s="51" t="s">
         <v>80</v>
       </c>
       <c r="AP13" s="9" t="s">
@@ -3812,7 +3451,7 @@
         <v>82</v>
       </c>
       <c r="AS13" s="28">
-        <v>981121855</v>
+        <v>369519756.158321</v>
       </c>
       <c r="AT13" s="22" t="s">
         <v>83</v>
@@ -3850,16 +3489,16 @@
     </row>
     <row r="14" ht="14.5" customHeight="1" spans="1:56" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>149</v>
+        <v>153</v>
       </c>
       <c r="B14" t="s">
-        <v>150</v>
+        <v>154</v>
       </c>
       <c r="C14" s="7" t="s">
-        <v>55</v>
-      </c>
-      <c r="D14" s="49" t="s">
-        <v>151</v>
+        <v>121</v>
+      </c>
+      <c r="D14" s="50" t="s">
+        <v>155</v>
       </c>
       <c r="E14" s="26" t="s">
         <v>57</v>
@@ -3868,10 +3507,10 @@
         <v>58</v>
       </c>
       <c r="G14" s="32" t="s">
-        <v>152</v>
+        <v>156</v>
       </c>
       <c r="H14" s="33" t="s">
-        <v>153</v>
+        <v>157</v>
       </c>
       <c r="I14" s="26" t="s">
         <v>61</v>
@@ -3895,16 +3534,16 @@
         <v>64</v>
       </c>
       <c r="P14" s="35" t="s">
-        <v>154</v>
+        <v>158</v>
       </c>
       <c r="Q14" s="16">
         <v>22192</v>
       </c>
       <c r="R14" s="35" t="s">
-        <v>155</v>
-      </c>
-      <c r="S14" s="35" t="s">
-        <v>155</v>
+        <v>159</v>
+      </c>
+      <c r="S14" s="26" t="s">
+        <v>159</v>
       </c>
       <c r="T14" s="26" t="s">
         <v>63</v>
@@ -3928,7 +3567,7 @@
         <v>69</v>
       </c>
       <c r="AA14" s="38" t="s">
-        <v>156</v>
+        <v>160</v>
       </c>
       <c r="AB14" s="39" t="s">
         <v>71</v>
@@ -3969,8 +3608,8 @@
       <c r="AN14" s="39" t="s">
         <v>79</v>
       </c>
-      <c r="AO14" s="50" t="s">
-        <v>157</v>
+      <c r="AO14" s="51" t="s">
+        <v>161</v>
       </c>
       <c r="AP14" s="26" t="s">
         <v>81</v>
@@ -3981,8 +3620,8 @@
       <c r="AR14" s="26" t="s">
         <v>82</v>
       </c>
-      <c r="AS14" s="41">
-        <v>657899922</v>
+      <c r="AS14" s="28">
+        <v>584522102.083316</v>
       </c>
       <c r="AT14" s="39" t="s">
         <v>83</v>
@@ -4020,16 +3659,16 @@
     </row>
     <row r="15" ht="14.5" customHeight="1" spans="1:56" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>158</v>
+        <v>162</v>
       </c>
       <c r="B15" t="s">
-        <v>159</v>
+        <v>163</v>
       </c>
       <c r="C15" s="7" t="s">
-        <v>117</v>
-      </c>
-      <c r="D15" s="49" t="s">
-        <v>151</v>
+        <v>121</v>
+      </c>
+      <c r="D15" s="50" t="s">
+        <v>155</v>
       </c>
       <c r="E15" s="9" t="s">
         <v>57</v>
@@ -4038,10 +3677,10 @@
         <v>58</v>
       </c>
       <c r="G15" s="11" t="s">
-        <v>160</v>
+        <v>164</v>
       </c>
       <c r="H15" s="12" t="s">
-        <v>161</v>
+        <v>165</v>
       </c>
       <c r="I15" s="13" t="s">
         <v>61</v>
@@ -4054,7 +3693,7 @@
       </c>
       <c r="L15" s="14">
         <f>TODAY()-31</f>
-        <v>45576</v>
+        <v>45577</v>
       </c>
       <c r="M15" s="9" t="s">
         <v>57</v>
@@ -4066,16 +3705,16 @@
         <v>64</v>
       </c>
       <c r="P15" s="35" t="s">
-        <v>154</v>
+        <v>158</v>
       </c>
       <c r="Q15" s="16">
         <v>22192</v>
       </c>
       <c r="R15" s="35" t="s">
-        <v>155</v>
+        <v>159</v>
       </c>
       <c r="S15" s="35" t="s">
-        <v>155</v>
+        <v>159</v>
       </c>
       <c r="T15" s="13" t="s">
         <v>63</v>
@@ -4091,23 +3730,23 @@
       </c>
       <c r="X15" s="19">
         <f>L15</f>
-        <v>45576</v>
+        <v>45577</v>
       </c>
       <c r="Y15" s="14">
         <f>TODAY()+20</f>
-        <v>45627</v>
+        <v>45628</v>
       </c>
       <c r="Z15" s="20" t="s">
         <v>69</v>
       </c>
       <c r="AA15" s="38" t="s">
-        <v>162</v>
+        <v>166</v>
       </c>
       <c r="AB15" s="22" t="s">
         <v>71</v>
       </c>
       <c r="AC15" s="46" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="AD15" s="22" t="s">
         <v>73</v>
@@ -4142,8 +3781,8 @@
       <c r="AN15" s="22" t="s">
         <v>79</v>
       </c>
-      <c r="AO15" s="50" t="s">
-        <v>163</v>
+      <c r="AO15" s="51" t="s">
+        <v>161</v>
       </c>
       <c r="AP15" s="9" t="s">
         <v>81</v>
@@ -4155,7 +3794,7 @@
         <v>82</v>
       </c>
       <c r="AS15" s="28">
-        <v>973409873</v>
+        <v>407198291.49721277</v>
       </c>
       <c r="AT15" s="22" t="s">
         <v>83</v>
@@ -4193,16 +3832,16 @@
     </row>
     <row r="16" ht="14.5" customHeight="1" spans="1:56" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>164</v>
+        <v>167</v>
       </c>
       <c r="B16" t="s">
-        <v>165</v>
+        <v>168</v>
       </c>
       <c r="C16" s="7" t="s">
-        <v>117</v>
-      </c>
-      <c r="D16" s="49" t="s">
-        <v>151</v>
+        <v>121</v>
+      </c>
+      <c r="D16" s="50" t="s">
+        <v>155</v>
       </c>
       <c r="E16" s="9" t="s">
         <v>57</v>
@@ -4211,10 +3850,10 @@
         <v>58</v>
       </c>
       <c r="G16" s="11" t="s">
-        <v>166</v>
+        <v>169</v>
       </c>
       <c r="H16" s="12" t="s">
-        <v>167</v>
+        <v>170</v>
       </c>
       <c r="I16" s="13" t="s">
         <v>61</v>
@@ -4227,7 +3866,7 @@
       </c>
       <c r="L16" s="14">
         <f>TODAY()-31</f>
-        <v>45576</v>
+        <v>45577</v>
       </c>
       <c r="M16" s="9" t="s">
         <v>57</v>
@@ -4239,16 +3878,16 @@
         <v>64</v>
       </c>
       <c r="P16" s="35" t="s">
-        <v>154</v>
+        <v>158</v>
       </c>
       <c r="Q16" s="16">
         <v>22192</v>
       </c>
       <c r="R16" s="35" t="s">
-        <v>155</v>
+        <v>159</v>
       </c>
       <c r="S16" s="35" t="s">
-        <v>155</v>
+        <v>159</v>
       </c>
       <c r="T16" s="13" t="s">
         <v>63</v>
@@ -4264,23 +3903,23 @@
       </c>
       <c r="X16" s="19">
         <f>L16</f>
-        <v>45576</v>
+        <v>45577</v>
       </c>
       <c r="Y16" s="14">
         <f>TODAY()+20</f>
-        <v>45627</v>
+        <v>45628</v>
       </c>
       <c r="Z16" s="20" t="s">
         <v>69</v>
       </c>
       <c r="AA16" s="38" t="s">
-        <v>168</v>
+        <v>171</v>
       </c>
       <c r="AB16" s="22" t="s">
         <v>71</v>
       </c>
       <c r="AC16" s="46" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="AD16" s="22" t="s">
         <v>73</v>
@@ -4315,8 +3954,8 @@
       <c r="AN16" s="22" t="s">
         <v>79</v>
       </c>
-      <c r="AO16" s="50" t="s">
-        <v>163</v>
+      <c r="AO16" s="51" t="s">
+        <v>161</v>
       </c>
       <c r="AP16" s="9" t="s">
         <v>81</v>
@@ -4328,7 +3967,7 @@
         <v>82</v>
       </c>
       <c r="AS16" s="28">
-        <v>984129567</v>
+        <v>419288037.28788507</v>
       </c>
       <c r="AT16" s="22" t="s">
         <v>83</v>
@@ -4366,16 +4005,16 @@
     </row>
     <row r="17" ht="14.5" customHeight="1" spans="1:56" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>169</v>
+        <v>172</v>
       </c>
       <c r="B17" t="s">
-        <v>170</v>
+        <v>173</v>
       </c>
       <c r="C17" s="7" t="s">
-        <v>117</v>
-      </c>
-      <c r="D17" s="49" t="s">
-        <v>171</v>
+        <v>121</v>
+      </c>
+      <c r="D17" s="50" t="s">
+        <v>174</v>
       </c>
       <c r="E17" s="26" t="s">
         <v>57</v>
@@ -4384,10 +4023,10 @@
         <v>58</v>
       </c>
       <c r="G17" s="32" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="H17" s="33" t="s">
-        <v>173</v>
+        <v>176</v>
       </c>
       <c r="I17" s="26" t="s">
         <v>61</v>
@@ -4411,16 +4050,16 @@
         <v>64</v>
       </c>
       <c r="P17" s="35" t="s">
-        <v>121</v>
+        <v>125</v>
       </c>
       <c r="Q17" s="16">
         <v>19141</v>
       </c>
       <c r="R17" s="35" t="s">
-        <v>121</v>
+        <v>125</v>
       </c>
       <c r="S17" s="26" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="T17" s="26" t="s">
         <v>63</v>
@@ -4444,25 +4083,25 @@
         <v>69</v>
       </c>
       <c r="AA17" s="38" t="s">
-        <v>174</v>
+        <v>177</v>
       </c>
       <c r="AB17" s="39" t="s">
         <v>71</v>
       </c>
       <c r="AC17" s="23" t="s">
-        <v>175</v>
+        <v>178</v>
       </c>
       <c r="AD17" s="39" t="s">
-        <v>176</v>
+        <v>179</v>
       </c>
       <c r="AE17" s="41">
         <v>108</v>
       </c>
       <c r="AF17" s="42" t="s">
-        <v>177</v>
-      </c>
-      <c r="AG17" s="25">
-        <v>40</v>
+        <v>180</v>
+      </c>
+      <c r="AG17" s="24" t="s">
+        <v>74</v>
       </c>
       <c r="AH17" s="43">
         <v>25</v>
@@ -4480,16 +4119,16 @@
         <v>77</v>
       </c>
       <c r="AM17" s="26" t="s">
-        <v>178</v>
+        <v>181</v>
       </c>
       <c r="AN17" s="39" t="s">
-        <v>179</v>
-      </c>
-      <c r="AO17" s="50" t="s">
-        <v>104</v>
+        <v>182</v>
+      </c>
+      <c r="AO17" s="51" t="s">
+        <v>106</v>
       </c>
       <c r="AP17" s="26" t="s">
-        <v>180</v>
+        <v>183</v>
       </c>
       <c r="AQ17" s="26" t="s">
         <v>57</v>
@@ -4497,14 +4136,14 @@
       <c r="AR17" s="26" t="s">
         <v>82</v>
       </c>
-      <c r="AS17" s="41">
-        <v>8976652307</v>
+      <c r="AS17" s="28">
+        <v>696712179.0472647</v>
       </c>
       <c r="AT17" s="39" t="s">
         <v>83</v>
       </c>
-      <c r="AU17" s="51" t="s">
-        <v>181</v>
+      <c r="AU17" s="52" t="s">
+        <v>184</v>
       </c>
       <c r="AV17" s="26" t="s">
         <v>57</v>
@@ -4535,7 +4174,7 @@
       </c>
     </row>
     <row r="18" ht="14.5" customHeight="1" spans="45:45" x14ac:dyDescent="0.25">
-      <c r="AS18" s="52"/>
+      <c r="AS18" s="53"/>
     </row>
   </sheetData>
   <dataValidations count="24">

--- a/Data/Hires/testDataUS.xlsx
+++ b/Data/Hires/testDataUS.xlsx
@@ -507,52 +507,46 @@
     <t>Test_14</t>
   </si>
   <si>
-    <t xml:space="preserve">Test failed for 'Madelynn Yost' Employee:{10652380}Error: [2mexpect([22m[31mreceived[39m[2m).[22mtoEqual[2m([22m[32mexpected[39m[2m) // deep equality[22m
-Expected: [32m"USA Pay Group"[39m
-Received: [31m"[7mPlease select a [27mUSA Pay Group"[39m</t>
-  </si>
-  <si>
-    <t>Madelynn</t>
-  </si>
-  <si>
-    <t>Yost</t>
-  </si>
-  <si>
-    <t>Auto 65006340</t>
+    <t>10652410</t>
+  </si>
+  <si>
+    <t>Karli</t>
+  </si>
+  <si>
+    <t>Kris</t>
+  </si>
+  <si>
+    <t>Auto 39710683</t>
   </si>
   <si>
     <t>Test_15</t>
   </si>
   <si>
-    <t xml:space="preserve">Test failed for 'Katelynn Rohan' Employee:{10652385}Error: [2mexpect([22m[31mreceived[39m[2m).[22mtoEqual[2m([22m[32mexpected[39m[2m) // deep equality[22m
-Expected: [32m"USA Pay Group"[39m
-Received: [31m"[7mPlease select a [27mUSA Pay Group"[39m</t>
-  </si>
-  <si>
-    <t>Katelynn</t>
-  </si>
-  <si>
-    <t>Rohan</t>
-  </si>
-  <si>
-    <t>Auto 79007249</t>
+    <t>10652407</t>
+  </si>
+  <si>
+    <t>Philip</t>
+  </si>
+  <si>
+    <t>Crooks</t>
+  </si>
+  <si>
+    <t>Auto 6318502</t>
   </si>
   <si>
     <t>Test_16</t>
   </si>
   <si>
-    <t xml:space="preserve">Test failed for 'Glen Wolf' Employee:{10652395}Error: [2mexpect([22m[31mreceived[39m[2m).[22mtoEqual[2m([22m[32mexpected[39m[2m) // deep equality[22m
-Expected: [32m"USA Pay Group"[39m
-Received: [31m"[7mPlease select a [27mUSA Pay Group"[39m</t>
+    <t>10652405</t>
   </si>
   <si>
     <t>108 Recruitment (Pepog Bizyse (10240565))</t>
   </si>
   <si>
-    <t>Glen</t>
-  </si>
-  <si>
-    <t>Wolf</t>
+    <t>Kyler</t>
+  </si>
+  <si>
+    <t>Schaefer</t>
   </si>
   <si>
     <t>No</t>
@@ -674,7 +668,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFF0000"/>
+        <fgColor rgb="FF00FF00"/>
       </patternFill>
     </fill>
     <fill>
@@ -772,7 +766,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="54">
+  <cellXfs count="55">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -902,6 +896,9 @@
     </xf>
     <xf numFmtId="0" fontId="8" fillId="6" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -1557,7 +1554,7 @@
       </c>
       <c r="AS2" s="28">
         <f t="array" ref="AS2:AS17">_xlfn.RANDARRAY(16,1,123456789,999999999,FALSE)</f>
-        <v>382384988.3993381</v>
+        <v>460815640.7913228</v>
       </c>
       <c r="AT2" s="22" t="s">
         <v>83</v>
@@ -1727,7 +1724,7 @@
         <v>82</v>
       </c>
       <c r="AS3" s="28">
-        <v>520899656.7887391</v>
+        <v>472982800.79699147</v>
       </c>
       <c r="AT3" s="39" t="s">
         <v>83</v>
@@ -1900,7 +1897,7 @@
         <v>82</v>
       </c>
       <c r="AS4" s="28">
-        <v>557812545.4056697</v>
+        <v>318166387.0177647</v>
       </c>
       <c r="AT4" s="22" t="s">
         <v>83</v>
@@ -2073,7 +2070,7 @@
         <v>82</v>
       </c>
       <c r="AS5" s="28">
-        <v>989456017.6990048</v>
+        <v>467531187.97844076</v>
       </c>
       <c r="AT5" s="22" t="s">
         <v>83</v>
@@ -2246,7 +2243,7 @@
         <v>82</v>
       </c>
       <c r="AS6" s="28">
-        <v>785876381.062165</v>
+        <v>517755556.7426585</v>
       </c>
       <c r="AT6" s="22" t="s">
         <v>83</v>
@@ -2419,7 +2416,7 @@
         <v>82</v>
       </c>
       <c r="AS7" s="28">
-        <v>804058163.7429827</v>
+        <v>555811152.5144323</v>
       </c>
       <c r="AT7" s="22" t="s">
         <v>83</v>
@@ -2589,7 +2586,7 @@
         <v>82</v>
       </c>
       <c r="AS8" s="28">
-        <v>632508201.5898451</v>
+        <v>825511269.0782044</v>
       </c>
       <c r="AT8" s="39" t="s">
         <v>83</v>
@@ -2762,7 +2759,7 @@
         <v>82</v>
       </c>
       <c r="AS9" s="28">
-        <v>784364524.2209965</v>
+        <v>747492505.429115</v>
       </c>
       <c r="AT9" s="22" t="s">
         <v>83</v>
@@ -2935,7 +2932,7 @@
         <v>82</v>
       </c>
       <c r="AS10" s="28">
-        <v>690276280.6384156</v>
+        <v>927618183.0344183</v>
       </c>
       <c r="AT10" s="22" t="s">
         <v>83</v>
@@ -3105,7 +3102,7 @@
         <v>82</v>
       </c>
       <c r="AS11" s="28">
-        <v>501541083.3148836</v>
+        <v>687838782.7348971</v>
       </c>
       <c r="AT11" s="39" t="s">
         <v>83</v>
@@ -3278,7 +3275,7 @@
         <v>82</v>
       </c>
       <c r="AS12" s="28">
-        <v>660781998.1587614</v>
+        <v>830591566.4173034</v>
       </c>
       <c r="AT12" s="22" t="s">
         <v>83</v>
@@ -3451,7 +3448,7 @@
         <v>82</v>
       </c>
       <c r="AS13" s="28">
-        <v>369519756.158321</v>
+        <v>892760956.1489455</v>
       </c>
       <c r="AT13" s="22" t="s">
         <v>83</v>
@@ -3491,7 +3488,7 @@
       <c r="A14" t="s">
         <v>153</v>
       </c>
-      <c r="B14" t="s">
+      <c r="B14" s="52" t="s">
         <v>154</v>
       </c>
       <c r="C14" s="7" t="s">
@@ -3621,7 +3618,7 @@
         <v>82</v>
       </c>
       <c r="AS14" s="28">
-        <v>584522102.083316</v>
+        <v>788948433.5635042</v>
       </c>
       <c r="AT14" s="39" t="s">
         <v>83</v>
@@ -3665,7 +3662,7 @@
         <v>163</v>
       </c>
       <c r="C15" s="7" t="s">
-        <v>121</v>
+        <v>55</v>
       </c>
       <c r="D15" s="50" t="s">
         <v>155</v>
@@ -3794,7 +3791,7 @@
         <v>82</v>
       </c>
       <c r="AS15" s="28">
-        <v>407198291.49721277</v>
+        <v>584250515.7309579</v>
       </c>
       <c r="AT15" s="22" t="s">
         <v>83</v>
@@ -3838,7 +3835,7 @@
         <v>168</v>
       </c>
       <c r="C16" s="7" t="s">
-        <v>121</v>
+        <v>55</v>
       </c>
       <c r="D16" s="50" t="s">
         <v>155</v>
@@ -3967,7 +3964,7 @@
         <v>82</v>
       </c>
       <c r="AS16" s="28">
-        <v>419288037.28788507</v>
+        <v>227977938.30577552</v>
       </c>
       <c r="AT16" s="22" t="s">
         <v>83</v>
@@ -4007,11 +4004,11 @@
       <c r="A17" t="s">
         <v>172</v>
       </c>
-      <c r="B17" t="s">
+      <c r="B17" s="52" t="s">
         <v>173</v>
       </c>
       <c r="C17" s="7" t="s">
-        <v>121</v>
+        <v>55</v>
       </c>
       <c r="D17" s="50" t="s">
         <v>174</v>
@@ -4137,12 +4134,12 @@
         <v>82</v>
       </c>
       <c r="AS17" s="28">
-        <v>696712179.0472647</v>
+        <v>153729041.11979425</v>
       </c>
       <c r="AT17" s="39" t="s">
         <v>83</v>
       </c>
-      <c r="AU17" s="52" t="s">
+      <c r="AU17" s="53" t="s">
         <v>184</v>
       </c>
       <c r="AV17" s="26" t="s">
@@ -4174,7 +4171,7 @@
       </c>
     </row>
     <row r="18" ht="14.5" customHeight="1" spans="45:45" x14ac:dyDescent="0.25">
-      <c r="AS18" s="53"/>
+      <c r="AS18" s="54"/>
     </row>
   </sheetData>
   <dataValidations count="24">

--- a/Data/Hires/testDataUS.xlsx
+++ b/Data/Hires/testDataUS.xlsx
@@ -1,29 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="27328"/>
-  <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9634BB6E-AEA9-49C1-877D-82B7626DAA38}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9303"/>
+  <workbookPr defaultThemeVersion="164011" filterPrivacy="1"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet sheetId="1" name="Sheet1" state="visible" r:id="rId4"/>
   </sheets>
-  <calcPr calcId="191029"/>
-  <extLst>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
-  </extLst>
+  <calcPr calcId="171027"/>
 </workbook>
 </file>
 
@@ -189,396 +175,7 @@
     <t>Test_1</t>
   </si>
   <si>
-    <t xml:space="preserve">Test failed for 'Conor Rippin' Employee:{undefined}TimeoutError: locator.click: Timeout 30000ms exceeded.
-Call log:
-  [2m- waiting for getByLabel('My Tasks Items')[22m
-[2m  -   locator resolved to &lt;button class="wdappchrome-w" data-automation-id="inbox_…&gt;…&lt;/button&gt;[22m
-[2m  - attempting click action[22m
-[2m  -   waiting for element to be visible, enabled and stable[22m
-[2m  -   element is visible, enabled and stable[22m
-[2m  -   scrolling into view if needed[22m
-[2m  -   done scrolling[22m
-[2m  -   &lt;div class="WDKP" data-automation-id="modalOverlay"&gt;…&lt;/div&gt; from &lt;div id="content-container"&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
-[2m  - retrying click action, attempt #1[22m
-[2m  -   waiting for element to be visible, enabled and stable[22m
-[2m  -   element is visible, enabled and stable[22m
-[2m  -   scrolling into view if needed[22m
-[2m  -   done scrolling[22m
-[2m  -   &lt;div class="WDKP" data-automation-id="modalOverlay"&gt;…&lt;/div&gt; from &lt;div id="content-container"&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
-[2m  - retrying click action, attempt #2[22m
-[2m  -   waiting 20ms[22m
-[2m  -   waiting for element to be visible, enabled and stable[22m
-[2m  -   element is visible, enabled and stable[22m
-[2m  -   scrolling into view if needed[22m
-[2m  -   done scrolling[22m
-[2m  -   &lt;div class="WDKP" data-automation-id="modalOverlay"&gt;…&lt;/div&gt; from &lt;div id="content-container"&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
-[2m  - retrying click action, attempt #3[22m
-[2m  -   waiting 100ms[22m
-[2m  -   waiting for element to be visible, enabled and stable[22m
-[2m  -   element is visible, enabled and stable[22m
-[2m  -   scrolling into view if needed[22m
-[2m  -   done scrolling[22m
-[2m  -   &lt;div class="WDKP" data-automation-id="modalOverlay"&gt;…&lt;/div&gt; from &lt;div id="content-container"&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
-[2m  - retrying click action, attempt #4[22m
-[2m  -   waiting 100ms[22m
-[2m  -   waiting for element to be visible, enabled and stable[22m
-[2m  -   element is visible, enabled and stable[22m
-[2m  -   scrolling into view if needed[22m
-[2m  -   done scrolling[22m
-[2m  -   &lt;div class="WDKP" data-automation-id="modalOverlay"&gt;…&lt;/div&gt; from &lt;div id="content-container"&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
-[2m  - retrying click action, attempt #5[22m
-[2m  -   waiting 500ms[22m
-[2m  -   waiting for element to be visible, enabled and stable[22m
-[2m  -   element is visible, enabled and stable[22m
-[2m  -   scrolling into view if needed[22m
-[2m  -   done scrolling[22m
-[2m  -   &lt;div class="WDKP" data-automation-id="modalOverlay"&gt;…&lt;/div&gt; from &lt;div id="content-container"&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
-[2m  - retrying click action, attempt #6[22m
-[2m  -   waiting 500ms[22m
-[2m  -   waiting for element to be visible, enabled and stable[22m
-[2m  -   element is visible, enabled and stable[22m
-[2m  -   scrolling into view if needed[22m
-[2m  -   done scrolling[22m
-[2m  -   &lt;div class="WDKP" data-automation-id="modalOverlay"&gt;…&lt;/div&gt; from &lt;div id="content-container"&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
-[2m  - retrying click action, attempt #7[22m
-[2m  -   waiting 500ms[22m
-[2m  -   waiting for element to be visible, enabled and stable[22m
-[2m  -   element is visible, enabled and stable[22m
-[2m  -   scrolling into view if needed[22m
-[2m  -   done scrolling[22m
-[2m  -   &lt;div class="WDKP" data-automation-id="modalOverlay"&gt;…&lt;/div&gt; from &lt;div id="content-container"&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
-[2m  - retrying click action, attempt #8[22m
-[2m  -   waiting 500ms[22m
-[2m  -   waiting for element to be visible, enabled and stable[22m
-[2m  -   element is visible, enabled and stable[22m
-[2m  -   scrolling into view if needed[22m
-[2m  -   done scrolling[22m
-[2m  -   &lt;div class="WDKP" data-automation-id="modalOverlay"&gt;…&lt;/div&gt; from &lt;div id="content-container"&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
-[2m  - retrying click action, attempt #9[22m
-[2m  -   waiting 500ms[22m
-[2m  -   waiting for element to be visible, enabled and stable[22m
-[2m  -   element is visible, enabled and stable[22m
-[2m  -   scrolling into view if needed[22m
-[2m  -   done scrolling[22m
-[2m  -   &lt;div class="WDKP" data-automation-id="modalOverlay"&gt;…&lt;/div&gt; from &lt;div id="content-container"&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
-[2m  - retrying click action, attempt #10[22m
-[2m  -   waiting 500ms[22m
-[2m  -   waiting for element to be visible, enabled and stable[22m
-[2m  -   element is visible, enabled and stable[22m
-[2m  -   scrolling into view if needed[22m
-[2m  -   done scrolling[22m
-[2m  -   &lt;div class="WDKP" data-automation-id="modalOverlay"&gt;…&lt;/div&gt; from &lt;div id="content-container"&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
-[2m  - retrying click action, attempt #11[22m
-[2m  -   waiting 500ms[22m
-[2m  -   waiting for element to be visible, enabled and stable[22m
-[2m  -   element is visible, enabled and stable[22m
-[2m  -   scrolling into view if needed[22m
-[2m  -   done scrolling[22m
-[2m  -   &lt;div class="WDKP" data-automation-id="modalOverlay"&gt;…&lt;/div&gt; from &lt;div id="content-container"&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
-[2m  - retrying click action, attempt #12[22m
-[2m  -   waiting 500ms[22m
-[2m  -   waiting for element to be visible, enabled and stable[22m
-[2m  -   element is visible, enabled and stable[22m
-[2m  -   scrolling into view if needed[22m
-[2m  -   done scrolling[22m
-[2m  -   &lt;div class="WDKP" data-automation-id="modalOverlay"&gt;…&lt;/div&gt; from &lt;div id="content-container"&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
-[2m  - retrying click action, attempt #13[22m
-[2m  -   waiting 500ms[22m
-[2m  -   waiting for element to be visible, enabled and stable[22m
-[2m  -   element is visible, enabled and stable[22m
-[2m  -   scrolling into view if needed[22m
-[2m  -   done scrolling[22m
-[2m  -   &lt;div class="WDKP" data-automation-id="modalOverlay"&gt;…&lt;/div&gt; from &lt;div id="content-container"&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
-[2m  - retrying click action, attempt #14[22m
-[2m  -   waiting 500ms[22m
-[2m  -   waiting for element to be visible, enabled and stable[22m
-[2m  -   element is visible, enabled and stable[22m
-[2m  -   scrolling into view if needed[22m
-[2m  -   done scrolling[22m
-[2m  -   &lt;div class="WDKP" data-automation-id="modalOverlay"&gt;…&lt;/div&gt; from &lt;div id="content-container"&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
-[2m  - retrying click action, attempt #15[22m
-[2m  -   waiting 500ms[22m
-[2m  -   waiting for element to be visible, enabled and stable[22m
-[2m  -   element is visible, enabled and stable[22m
-[2m  -   scrolling into view if needed[22m
-[2m  -   done scrolling[22m
-[2m  -   &lt;div class="WDKP" data-automation-id="modalOverlay"&gt;…&lt;/div&gt; from &lt;div id="content-container"&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
-[2m  - retrying click action, attempt #16[22m
-[2m  -   waiting 500ms[22m
-[2m  -   waiting for element to be visible, enabled and stable[22m
-[2m  -   element is visible, enabled and stable[22m
-[2m  -   scrolling into view if needed[22m
-[2m  -   done scrolling[22m
-[2m  -   &lt;div class="WDKP" data-automation-id="modalOverlay"&gt;…&lt;/div&gt; from &lt;div id="content-container"&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
-[2m  - retrying click action, attempt #17[22m
-[2m  -   waiting 500ms[22m
-[2m  -   waiting for element to be visible, enabled and stable[22m
-[2m  -   element is visible, enabled and stable[22m
-[2m  -   scrolling into view if needed[22m
-[2m  -   done scrolling[22m
-[2m  -   &lt;div class="WDKP" data-automation-id="modalOverlay"&gt;…&lt;/div&gt; from &lt;div id="content-container"&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
-[2m  - retrying click action, attempt #18[22m
-[2m  -   waiting 500ms[22m
-[2m  -   waiting for element to be visible, enabled and stable[22m
-[2m  -   element is visible, enabled and stable[22m
-[2m  -   scrolling into view if needed[22m
-[2m  -   done scrolling[22m
-[2m  -   &lt;div class="WDKP" data-automation-id="modalOverlay"&gt;…&lt;/div&gt; from &lt;div id="content-container"&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
-[2m  - retrying click action, attempt #19[22m
-[2m  -   waiting 500ms[22m
-[2m  -   waiting for element to be visible, enabled and stable[22m
-[2m  -   element is visible, enabled and stable[22m
-[2m  -   scrolling into view if needed[22m
-[2m  -   done scrolling[22m
-[2m  -   &lt;div class="WDKP" data-automation-id="modalOverlay"&gt;…&lt;/div&gt; from &lt;div id="content-container"&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
-[2m  - retrying click action, attempt #20[22m
-[2m  -   waiting 500ms[22m
-[2m  -   waiting for element to be visible, enabled and stable[22m
-[2m  -   element is visible, enabled and stable[22m
-[2m  -   scrolling into view if needed[22m
-[2m  -   done scrolling[22m
-[2m  -   &lt;div class="WDKP" data-automation-id="modalOverlay"&gt;…&lt;/div&gt; from &lt;div id="content-container"&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
-[2m  - retrying click action, attempt #21[22m
-[2m  -   waiting 500ms[22m
-[2m  -   waiting for element to be visible, enabled and stable[22m
-[2m  -   element is visible, enabled and stable[22m
-[2m  -   scrolling into view if needed[22m
-[2m  -   done scrolling[22m
-[2m  -   &lt;div class="WDKP" data-automation-id="modalOverlay"&gt;…&lt;/div&gt; from &lt;div id="content-container"&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
-[2m  - retrying click action, attempt #22[22m
-[2m  -   waiting 500ms[22m
-[2m  -   waiting for element to be visible, enabled and stable[22m
-[2m  -   element is visible, enabled and stable[22m
-[2m  -   scrolling into view if needed[22m
-[2m  -   done scrolling[22m
-[2m  -   &lt;div class="WDKP" data-automation-id="modalOverlay"&gt;…&lt;/div&gt; from &lt;div id="content-container"&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
-[2m  - retrying click action, attempt #23[22m
-[2m  -   waiting 500ms[22m
-[2m  -   waiting for element to be visible, enabled and stable[22m
-[2m  -   element is visible, enabled and stable[22m
-[2m  -   scrolling into view if needed[22m
-[2m  -   done scrolling[22m
-[2m  -   &lt;div class="WDKP" data-automation-id="modalOverlay"&gt;…&lt;/div&gt; from &lt;div id="content-container"&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
-[2m  - retrying click action, attempt #24[22m
-[2m  -   waiting 500ms[22m
-[2m  -   waiting for element to be visible, enabled and stable[22m
-[2m  -   element is visible, enabled and stable[22m
-[2m  -   scrolling into view if needed[22m
-[2m  -   done scrolling[22m
-[2m  -   &lt;div class="WDKP" data-automation-id="modalOverlay"&gt;…&lt;/div&gt; from &lt;div id="content-container"&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
-[2m  - retrying click action, attempt #25[22m
-[2m  -   waiting 500ms[22m
-[2m  -   waiting for element to be visible, enabled and stable[22m
-[2m  -   element is visible, enabled and stable[22m
-[2m  -   scrolling into view if needed[22m
-[2m  -   done scrolling[22m
-[2m  -   &lt;div class="WDKP" data-automation-id="modalOverlay"&gt;…&lt;/div&gt; from &lt;div id="content-container"&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
-[2m  - retrying click action, attempt #26[22m
-[2m  -   waiting 500ms[22m
-[2m  -   waiting for element to be visible, enabled and stable[22m
-[2m  -   element is visible, enabled and stable[22m
-[2m  -   scrolling into view if needed[22m
-[2m  -   done scrolling[22m
-[2m  -   &lt;div class="WDKP" data-automation-id="modalOverlay"&gt;…&lt;/div&gt; from &lt;div id="content-container"&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
-[2m  - retrying click action, attempt #27[22m
-[2m  -   waiting 500ms[22m
-[2m  -   waiting for element to be visible, enabled and stable[22m
-[2m  -   element is visible, enabled and stable[22m
-[2m  -   scrolling into view if needed[22m
-[2m  -   done scrolling[22m
-[2m  -   &lt;div class="WDKP" data-automation-id="modalOverlay"&gt;…&lt;/div&gt; from &lt;div id="content-container"&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
-[2m  - retrying click action, attempt #28[22m
-[2m  -   waiting 500ms[22m
-[2m  -   waiting for element to be visible, enabled and stable[22m
-[2m  -   element is visible, enabled and stable[22m
-[2m  -   scrolling into view if needed[22m
-[2m  -   done scrolling[22m
-[2m  -   &lt;div class="WDKP" data-automation-id="modalOverlay"&gt;…&lt;/div&gt; from &lt;div id="content-container"&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
-[2m  - retrying click action, attempt #29[22m
-[2m  -   waiting 500ms[22m
-[2m  -   waiting for element to be visible, enabled and stable[22m
-[2m  -   element is visible, enabled and stable[22m
-[2m  -   scrolling into view if needed[22m
-[2m  -   done scrolling[22m
-[2m  -   &lt;div class="WDKP" data-automation-id="modalOverlay"&gt;…&lt;/div&gt; from &lt;div id="content-container"&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
-[2m  - retrying click action, attempt #30[22m
-[2m  -   waiting 500ms[22m
-[2m  -   waiting for element to be visible, enabled and stable[22m
-[2m  -   element is visible, enabled and stable[22m
-[2m  -   scrolling into view if needed[22m
-[2m  -   done scrolling[22m
-[2m  -   &lt;div class="WDKP" data-automation-id="modalOverlay"&gt;…&lt;/div&gt; from &lt;div id="content-container"&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
-[2m  - retrying click action, attempt #31[22m
-[2m  -   waiting 500ms[22m
-[2m  -   waiting for element to be visible, enabled and stable[22m
-[2m  -   element is visible, enabled and stable[22m
-[2m  -   scrolling into view if needed[22m
-[2m  -   done scrolling[22m
-[2m  -   &lt;div class="WDKP" data-automation-id="modalOverlay"&gt;…&lt;/div&gt; from &lt;div id="content-container"&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
-[2m  - retrying click action, attempt #32[22m
-[2m  -   waiting 500ms[22m
-[2m  -   waiting for element to be visible, enabled and stable[22m
-[2m  -   element is visible, enabled and stable[22m
-[2m  -   scrolling into view if needed[22m
-[2m  -   done scrolling[22m
-[2m  -   &lt;div class="WDKP" data-automation-id="modalOverlay"&gt;…&lt;/div&gt; from &lt;div id="content-container"&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
-[2m  - retrying click action, attempt #33[22m
-[2m  -   waiting 500ms[22m
-[2m  -   waiting for element to be visible, enabled and stable[22m
-[2m  -   element is visible, enabled and stable[22m
-[2m  -   scrolling into view if needed[22m
-[2m  -   done scrolling[22m
-[2m  -   &lt;div class="WDKP" data-automation-id="modalOverlay"&gt;…&lt;/div&gt; from &lt;div id="content-container"&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
-[2m  - retrying click action, attempt #34[22m
-[2m  -   waiting 500ms[22m
-[2m  -   waiting for element to be visible, enabled and stable[22m
-[2m  -   element is visible, enabled and stable[22m
-[2m  -   scrolling into view if needed[22m
-[2m  -   done scrolling[22m
-[2m  -   &lt;div class="WDKP" data-automation-id="modalOverlay"&gt;…&lt;/div&gt; from &lt;div id="content-container"&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
-[2m  - retrying click action, attempt #35[22m
-[2m  -   waiting 500ms[22m
-[2m  -   waiting for element to be visible, enabled and stable[22m
-[2m  -   element is visible, enabled and stable[22m
-[2m  -   scrolling into view if needed[22m
-[2m  -   done scrolling[22m
-[2m  -   &lt;div class="WDKP" data-automation-id="modalOverlay"&gt;…&lt;/div&gt; from &lt;div id="content-container"&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
-[2m  - retrying click action, attempt #36[22m
-[2m  -   waiting 500ms[22m
-[2m  -   waiting for element to be visible, enabled and stable[22m
-[2m  -   element is visible, enabled and stable[22m
-[2m  -   scrolling into view if needed[22m
-[2m  -   done scrolling[22m
-[2m  -   &lt;div class="WDKP" data-automation-id="modalOverlay"&gt;…&lt;/div&gt; from &lt;div id="content-container"&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
-[2m  - retrying click action, attempt #37[22m
-[2m  -   waiting 500ms[22m
-[2m  -   waiting for element to be visible, enabled and stable[22m
-[2m  -   element is visible, enabled and stable[22m
-[2m  -   scrolling into view if needed[22m
-[2m  -   done scrolling[22m
-[2m  -   &lt;div class="WDKP" data-automation-id="modalOverlay"&gt;…&lt;/div&gt; from &lt;div id="content-container"&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
-[2m  - retrying click action, attempt #38[22m
-[2m  -   waiting 500ms[22m
-[2m  -   waiting for element to be visible, enabled and stable[22m
-[2m  -   element is visible, enabled and stable[22m
-[2m  -   scrolling into view if needed[22m
-[2m  -   done scrolling[22m
-[2m  -   &lt;div class="WDKP" data-automation-id="modalOverlay"&gt;…&lt;/div&gt; from &lt;div id="content-container"&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
-[2m  - retrying click action, attempt #39[22m
-[2m  -   waiting 500ms[22m
-[2m  -   waiting for element to be visible, enabled and stable[22m
-[2m  -   element is visible, enabled and stable[22m
-[2m  -   scrolling into view if needed[22m
-[2m  -   done scrolling[22m
-[2m  -   &lt;div class="WDKP" data-automation-id="modalOverlay"&gt;…&lt;/div&gt; from &lt;div id="content-container"&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
-[2m  - retrying click action, attempt #40[22m
-[2m  -   waiting 500ms[22m
-[2m  -   waiting for element to be visible, enabled and stable[22m
-[2m  -   element is visible, enabled and stable[22m
-[2m  -   scrolling into view if needed[22m
-[2m  -   done scrolling[22m
-[2m  -   &lt;div class="WDKP" data-automation-id="modalOverlay"&gt;…&lt;/div&gt; from &lt;div id="content-container"&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
-[2m  - retrying click action, attempt #41[22m
-[2m  -   waiting 500ms[22m
-[2m  -   waiting for element to be visible, enabled and stable[22m
-[2m  -   element is visible, enabled and stable[22m
-[2m  -   scrolling into view if needed[22m
-[2m  -   done scrolling[22m
-[2m  -   &lt;div class="WDKP" data-automation-id="modalOverlay"&gt;…&lt;/div&gt; from &lt;div id="content-container"&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
-[2m  - retrying click action, attempt #42[22m
-[2m  -   waiting 500ms[22m
-[2m  -   waiting for element to be visible, enabled and stable[22m
-[2m  -   element is visible, enabled and stable[22m
-[2m  -   scrolling into view if needed[22m
-[2m  -   done scrolling[22m
-[2m  -   &lt;div class="WDKP" data-automation-id="modalOverlay"&gt;…&lt;/div&gt; from &lt;div id="content-container"&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
-[2m  - retrying click action, attempt #43[22m
-[2m  -   waiting 500ms[22m
-[2m  -   waiting for element to be visible, enabled and stable[22m
-[2m  -   element is visible, enabled and stable[22m
-[2m  -   scrolling into view if needed[22m
-[2m  -   done scrolling[22m
-[2m  -   &lt;div class="WDKP" data-automation-id="modalOverlay"&gt;…&lt;/div&gt; from &lt;div id="content-container"&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
-[2m  - retrying click action, attempt #44[22m
-[2m  -   waiting 500ms[22m
-[2m  -   waiting for element to be visible, enabled and stable[22m
-[2m  -   element is visible, enabled and stable[22m
-[2m  -   scrolling into view if needed[22m
-[2m  -   done scrolling[22m
-[2m  -   &lt;div class="WDKP" data-automation-id="modalOverlay"&gt;…&lt;/div&gt; from &lt;div id="content-container"&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
-[2m  - retrying click action, attempt #45[22m
-[2m  -   waiting 500ms[22m
-[2m  -   waiting for element to be visible, enabled and stable[22m
-[2m  -   element is visible, enabled and stable[22m
-[2m  -   scrolling into view if needed[22m
-[2m  -   done scrolling[22m
-[2m  -   &lt;div class="WDKP" data-automation-id="modalOverlay"&gt;…&lt;/div&gt; from &lt;div id="content-container"&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
-[2m  - retrying click action, attempt #46[22m
-[2m  -   waiting 500ms[22m
-[2m  -   waiting for element to be visible, enabled and stable[22m
-[2m  -   element is visible, enabled and stable[22m
-[2m  -   scrolling into view if needed[22m
-[2m  -   done scrolling[22m
-[2m  -   &lt;div class="WDKP" data-automation-id="modalOverlay"&gt;…&lt;/div&gt; from &lt;div id="content-container"&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
-[2m  - retrying click action, attempt #47[22m
-[2m  -   waiting 500ms[22m
-[2m  -   waiting for element to be visible, enabled and stable[22m
-[2m  -   element is visible, enabled and stable[22m
-[2m  -   scrolling into view if needed[22m
-[2m  -   done scrolling[22m
-[2m  -   &lt;div class="WDKP" data-automation-id="modalOverlay"&gt;…&lt;/div&gt; from &lt;div id="content-container"&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
-[2m  - retrying click action, attempt #48[22m
-[2m  -   waiting 500ms[22m
-[2m  -   waiting for element to be visible, enabled and stable[22m
-[2m  -   element is visible, enabled and stable[22m
-[2m  -   scrolling into view if needed[22m
-[2m  -   done scrolling[22m
-[2m  -   &lt;div class="WDKP" data-automation-id="modalOverlay"&gt;…&lt;/div&gt; from &lt;div id="content-container"&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
-[2m  - retrying click action, attempt #49[22m
-[2m  -   waiting 500ms[22m
-[2m  -   waiting for element to be visible, enabled and stable[22m
-[2m  -   element is visible, enabled and stable[22m
-[2m  -   scrolling into view if needed[22m
-[2m  -   done scrolling[22m
-[2m  -   &lt;div class="WDKP" data-automation-id="modalOverlay"&gt;…&lt;/div&gt; from &lt;div id="content-container"&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
-[2m  - retrying click action, attempt #50[22m
-[2m  -   waiting 500ms[22m
-[2m  -   waiting for element to be visible, enabled and stable[22m
-[2m  -   element is visible, enabled and stable[22m
-[2m  -   scrolling into view if needed[22m
-[2m  -   done scrolling[22m
-[2m  -   &lt;div class="WDKP" data-automation-id="modalOverlay"&gt;…&lt;/div&gt; from &lt;div id="content-container"&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
-[2m  - retrying click action, attempt #51[22m
-[2m  -   waiting 500ms[22m
-[2m  -   waiting for element to be visible, enabled and stable[22m
-[2m  -   element is visible, enabled and stable[22m
-[2m  -   scrolling into view if needed[22m
-[2m  -   done scrolling[22m
-[2m  -   &lt;div class="WDKP" data-automation-id="modalOverlay"&gt;…&lt;/div&gt; from &lt;div id="content-container"&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
-[2m  - retrying click action, attempt #52[22m
-[2m  -   waiting 500ms[22m
-[2m  -   waiting for element to be visible, enabled and stable[22m
-[2m  -   element is visible, enabled and stable[22m
-[2m  -   scrolling into view if needed[22m
-[2m  -   done scrolling[22m
-[2m  -   &lt;div class="WDKP" data-automation-id="modalOverlay"&gt;…&lt;/div&gt; from &lt;div id="content-container"&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
-[2m  - retrying click action, attempt #53[22m
-[2m  -   waiting 500ms[22m
-[2m  -   waiting for element to be visible, enabled and stable[22m
-[2m  -   element is visible, enabled and stable[22m
-[2m  -   scrolling into view if needed[22m
-[2m  -   done scrolling[22m
-[2m  -   &lt;div class="WDKP" data-automation-id="modalOverlay"&gt;…&lt;/div&gt; from &lt;div id="content-container"&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
-[2m  - retrying click action, attempt #54[22m
-[2m  -   waiting 500ms[22m
-[2m  -   waiting for element to be visible, enabled and stable[22m
-[2m  -   element is visible, enabled and stable[22m
-[2m  -   scrolling into view if needed[22m
-[2m  -   done scrolling[22m
-[2m  -   &lt;div class="WDKP" data-automation-id="modalOverlay"&gt;…&lt;/div&gt; from &lt;div id="content-container"&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
-[2m  - retrying click action, attempt #55[22m
-[2m  -   waiting 500ms[22m
-</t>
+    <t>Test failed for 'Marilie Leuschke' Employee:{10652046}Error: locator.isVisible: Target page, context or browser has been closed</t>
   </si>
   <si>
     <t>Failed</t>
@@ -593,10 +190,10 @@
     <t>Mr</t>
   </si>
   <si>
-    <t>Conor</t>
-  </si>
-  <si>
-    <t>Rippin</t>
+    <t>Marilie</t>
+  </si>
+  <si>
+    <t>Leuschke</t>
   </si>
   <si>
     <t>(202) 555-0147</t>
@@ -2826,26 +2423,26 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
   <fonts count="3" x14ac:knownFonts="1">
     <font>
-      <sz val="11"/>
       <color theme="1"/>
-      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
+      <sz val="11"/>
+      <name val="Calibri"/>
     </font>
     <font>
+      <color rgb="FFFF0000"/>
+      <family val="2"/>
       <sz val="11"/>
-      <color rgb="FFFF0000"/>
       <name val="Arial"/>
-      <family val="2"/>
     </font>
     <font>
+      <color theme="1"/>
+      <family val="2"/>
       <sz val="11"/>
-      <color theme="1"/>
       <name val="Arial"/>
-      <family val="2"/>
     </font>
   </fonts>
   <fills count="6">
@@ -2857,7 +2454,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.59999389629810485"/>
+        <fgColor theme="5" tint="0.5999938962981048"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -2873,7 +2470,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.79998168889431442"/>
+        <fgColor theme="5" tint="0.7999816888943144"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -2893,12 +2490,8 @@
       <right style="medium">
         <color indexed="64"/>
       </right>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
-      <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
+      <top style="thin"/>
+      <bottom style="thin"/>
       <diagonal/>
     </border>
     <border>
@@ -2908,25 +2501,15 @@
       <right style="medium">
         <color indexed="64"/>
       </right>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
+      <top style="thin"/>
       <bottom/>
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color auto="1"/>
-      </left>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
-      <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
       <diagonal/>
     </border>
     <border>
@@ -2937,9 +2520,7 @@
         <color indexed="64"/>
       </right>
       <top/>
-      <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
+      <bottom style="thin"/>
       <diagonal/>
     </border>
   </borders>
@@ -3248,9 +2829,9 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:BC18"/>
-  <sheetFormatPr defaultRowHeight="14.5" customHeight="1" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="14.5" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0.35" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="7.26953125" customWidth="1"/>
     <col min="2" max="2" width="10.81640625" customWidth="1"/>
@@ -3308,7 +2889,7 @@
     <col min="56" max="56" width="8.7265625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:55" s="1" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" ht="18" customHeight="1" spans="1:55" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -3475,7 +3056,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="2" spans="1:55" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="2" ht="14.5" customHeight="1" spans="1:55" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>52</v>
       </c>
@@ -3510,7 +3091,7 @@
         <v>62</v>
       </c>
       <c r="L2">
-        <f t="shared" ref="L2:L17" ca="1" si="0">TODAY()-31</f>
+        <f t="shared" ref="L2:L17" si="0">TODAY()-31</f>
         <v>45563</v>
       </c>
       <c r="M2" t="s">
@@ -3547,11 +3128,11 @@
         <v>62</v>
       </c>
       <c r="X2">
-        <f t="shared" ref="X2:X17" ca="1" si="1">L2</f>
+        <f t="shared" ref="X2:X17" si="1">L2</f>
         <v>45563</v>
       </c>
       <c r="Y2">
-        <f t="shared" ref="Y2:Y17" ca="1" si="2">TODAY()+20</f>
+        <f t="shared" ref="Y2:Y17" si="2">TODAY()+20</f>
         <v>45614</v>
       </c>
       <c r="Z2" t="s">
@@ -3609,8 +3190,8 @@
         <v>81</v>
       </c>
       <c r="AR2">
-        <f t="array" aca="1" ref="AR2:AR17" ca="1">_xlfn.RANDARRAY(16,1,123456789,999999999,FALSE)</f>
-        <v>844100754.75221956</v>
+        <f t="array" ref="AR2:AR17">_xlfn.RANDARRAY(16,1,123456789,999999999,FALSE)</f>
+        <v>844100754.7522196</v>
       </c>
       <c r="AS2" t="s">
         <v>82</v>
@@ -3646,7 +3227,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="3" spans="1:55" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="3" ht="14.5" customHeight="1" spans="1:55" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>88</v>
       </c>
@@ -3681,7 +3262,7 @@
         <v>62</v>
       </c>
       <c r="L3">
-        <f t="shared" ca="1" si="0"/>
+        <f t="shared" si="0"/>
         <v>45563</v>
       </c>
       <c r="M3" t="s">
@@ -3718,11 +3299,11 @@
         <v>62</v>
       </c>
       <c r="X3">
-        <f t="shared" ca="1" si="1"/>
+        <f t="shared" si="1"/>
         <v>45563</v>
       </c>
       <c r="Y3">
-        <f t="shared" ca="1" si="2"/>
+        <f t="shared" si="2"/>
         <v>45614</v>
       </c>
       <c r="Z3" t="s">
@@ -3780,8 +3361,7 @@
         <v>81</v>
       </c>
       <c r="AR3">
-        <f ca="1"/>
-        <v>978941583.73973286</v>
+        <v>978941583.7397329</v>
       </c>
       <c r="AS3" t="s">
         <v>82</v>
@@ -3817,7 +3397,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="4" spans="1:55" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="4" ht="14.5" customHeight="1" spans="1:55" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>96</v>
       </c>
@@ -3852,7 +3432,7 @@
         <v>62</v>
       </c>
       <c r="L4">
-        <f t="shared" ca="1" si="0"/>
+        <f t="shared" si="0"/>
         <v>45563</v>
       </c>
       <c r="M4" t="s">
@@ -3889,11 +3469,11 @@
         <v>62</v>
       </c>
       <c r="X4">
-        <f t="shared" ca="1" si="1"/>
+        <f t="shared" si="1"/>
         <v>45563</v>
       </c>
       <c r="Y4">
-        <f t="shared" ca="1" si="2"/>
+        <f t="shared" si="2"/>
         <v>45614</v>
       </c>
       <c r="Z4" t="s">
@@ -3951,8 +3531,7 @@
         <v>81</v>
       </c>
       <c r="AR4">
-        <f ca="1"/>
-        <v>617992452.72788286</v>
+        <v>617992452.7278829</v>
       </c>
       <c r="AS4" t="s">
         <v>82</v>
@@ -3988,7 +3567,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="5" spans="1:55" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="5" ht="14.5" customHeight="1" spans="1:55" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>105</v>
       </c>
@@ -4023,7 +3602,7 @@
         <v>62</v>
       </c>
       <c r="L5">
-        <f t="shared" ca="1" si="0"/>
+        <f t="shared" si="0"/>
         <v>45563</v>
       </c>
       <c r="M5" t="s">
@@ -4060,11 +3639,11 @@
         <v>62</v>
       </c>
       <c r="X5">
-        <f t="shared" ca="1" si="1"/>
+        <f t="shared" si="1"/>
         <v>45563</v>
       </c>
       <c r="Y5">
-        <f t="shared" ca="1" si="2"/>
+        <f t="shared" si="2"/>
         <v>45614</v>
       </c>
       <c r="Z5" t="s">
@@ -4122,7 +3701,6 @@
         <v>81</v>
       </c>
       <c r="AR5">
-        <f ca="1"/>
         <v>341904021.5753274</v>
       </c>
       <c r="AS5" t="s">
@@ -4159,7 +3737,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="6" spans="1:55" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="6" ht="14.5" customHeight="1" spans="1:55" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>110</v>
       </c>
@@ -4194,7 +3772,7 @@
         <v>62</v>
       </c>
       <c r="L6">
-        <f t="shared" ca="1" si="0"/>
+        <f t="shared" si="0"/>
         <v>45563</v>
       </c>
       <c r="M6" t="s">
@@ -4231,11 +3809,11 @@
         <v>62</v>
       </c>
       <c r="X6">
-        <f t="shared" ca="1" si="1"/>
+        <f t="shared" si="1"/>
         <v>45563</v>
       </c>
       <c r="Y6">
-        <f t="shared" ca="1" si="2"/>
+        <f t="shared" si="2"/>
         <v>45614</v>
       </c>
       <c r="Z6" t="s">
@@ -4293,8 +3871,7 @@
         <v>81</v>
       </c>
       <c r="AR6">
-        <f ca="1"/>
-        <v>549430002.93627071</v>
+        <v>549430002.9362707</v>
       </c>
       <c r="AS6" t="s">
         <v>82</v>
@@ -4330,7 +3907,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="7" spans="1:55" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="7" ht="14.5" customHeight="1" spans="1:55" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>116</v>
       </c>
@@ -4365,7 +3942,7 @@
         <v>62</v>
       </c>
       <c r="L7">
-        <f t="shared" ca="1" si="0"/>
+        <f t="shared" si="0"/>
         <v>45563</v>
       </c>
       <c r="M7" t="s">
@@ -4402,11 +3979,11 @@
         <v>62</v>
       </c>
       <c r="X7">
-        <f t="shared" ca="1" si="1"/>
+        <f t="shared" si="1"/>
         <v>45563</v>
       </c>
       <c r="Y7">
-        <f t="shared" ca="1" si="2"/>
+        <f t="shared" si="2"/>
         <v>45614</v>
       </c>
       <c r="Z7" t="s">
@@ -4464,8 +4041,7 @@
         <v>81</v>
       </c>
       <c r="AR7">
-        <f ca="1"/>
-        <v>729117931.47737575</v>
+        <v>729117931.4773757</v>
       </c>
       <c r="AS7" t="s">
         <v>82</v>
@@ -4501,7 +4077,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="8" spans="1:55" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="8" ht="14.5" customHeight="1" spans="1:55" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>122</v>
       </c>
@@ -4536,7 +4112,7 @@
         <v>62</v>
       </c>
       <c r="L8">
-        <f t="shared" ca="1" si="0"/>
+        <f t="shared" si="0"/>
         <v>45563</v>
       </c>
       <c r="M8" t="s">
@@ -4573,11 +4149,11 @@
         <v>62</v>
       </c>
       <c r="X8">
-        <f t="shared" ca="1" si="1"/>
+        <f t="shared" si="1"/>
         <v>45563</v>
       </c>
       <c r="Y8">
-        <f t="shared" ca="1" si="2"/>
+        <f t="shared" si="2"/>
         <v>45614</v>
       </c>
       <c r="Z8" t="s">
@@ -4635,7 +4211,6 @@
         <v>81</v>
       </c>
       <c r="AR8">
-        <f ca="1"/>
         <v>134367581.14492083</v>
       </c>
       <c r="AS8" t="s">
@@ -4672,7 +4247,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="9" spans="1:55" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="9" ht="14.5" customHeight="1" spans="1:55" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>128</v>
       </c>
@@ -4707,7 +4282,7 @@
         <v>62</v>
       </c>
       <c r="L9">
-        <f t="shared" ca="1" si="0"/>
+        <f t="shared" si="0"/>
         <v>45563</v>
       </c>
       <c r="M9" t="s">
@@ -4744,11 +4319,11 @@
         <v>62</v>
       </c>
       <c r="X9">
-        <f t="shared" ca="1" si="1"/>
+        <f t="shared" si="1"/>
         <v>45563</v>
       </c>
       <c r="Y9">
-        <f t="shared" ca="1" si="2"/>
+        <f t="shared" si="2"/>
         <v>45614</v>
       </c>
       <c r="Z9" t="s">
@@ -4806,8 +4381,7 @@
         <v>81</v>
       </c>
       <c r="AR9">
-        <f ca="1"/>
-        <v>605135441.84431624</v>
+        <v>605135441.8443162</v>
       </c>
       <c r="AS9" t="s">
         <v>82</v>
@@ -4843,7 +4417,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="10" spans="1:55" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="10" ht="14.5" customHeight="1" spans="1:55" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>134</v>
       </c>
@@ -4878,7 +4452,7 @@
         <v>62</v>
       </c>
       <c r="L10">
-        <f t="shared" ca="1" si="0"/>
+        <f t="shared" si="0"/>
         <v>45563</v>
       </c>
       <c r="M10" t="s">
@@ -4915,11 +4489,11 @@
         <v>62</v>
       </c>
       <c r="X10">
-        <f t="shared" ca="1" si="1"/>
+        <f t="shared" si="1"/>
         <v>45563</v>
       </c>
       <c r="Y10">
-        <f t="shared" ca="1" si="2"/>
+        <f t="shared" si="2"/>
         <v>45614</v>
       </c>
       <c r="Z10" t="s">
@@ -4977,8 +4551,7 @@
         <v>81</v>
       </c>
       <c r="AR10">
-        <f ca="1"/>
-        <v>511097241.76941502</v>
+        <v>511097241.769415</v>
       </c>
       <c r="AS10" t="s">
         <v>82</v>
@@ -5014,7 +4587,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="11" spans="1:55" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="11" ht="14.5" customHeight="1" spans="1:55" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>140</v>
       </c>
@@ -5049,7 +4622,7 @@
         <v>62</v>
       </c>
       <c r="L11">
-        <f t="shared" ca="1" si="0"/>
+        <f t="shared" si="0"/>
         <v>45563</v>
       </c>
       <c r="M11" t="s">
@@ -5086,11 +4659,11 @@
         <v>62</v>
       </c>
       <c r="X11">
-        <f t="shared" ca="1" si="1"/>
+        <f t="shared" si="1"/>
         <v>45563</v>
       </c>
       <c r="Y11">
-        <f t="shared" ca="1" si="2"/>
+        <f t="shared" si="2"/>
         <v>45614</v>
       </c>
       <c r="Z11" t="s">
@@ -5148,8 +4721,7 @@
         <v>81</v>
       </c>
       <c r="AR11">
-        <f ca="1"/>
-        <v>948406794.54615104</v>
+        <v>948406794.546151</v>
       </c>
       <c r="AS11" t="s">
         <v>82</v>
@@ -5185,7 +4757,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="12" spans="1:55" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="12" ht="14.5" customHeight="1" spans="1:55" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>147</v>
       </c>
@@ -5220,7 +4792,7 @@
         <v>62</v>
       </c>
       <c r="L12">
-        <f t="shared" ca="1" si="0"/>
+        <f t="shared" si="0"/>
         <v>45563</v>
       </c>
       <c r="M12" t="s">
@@ -5257,11 +4829,11 @@
         <v>62</v>
       </c>
       <c r="X12">
-        <f t="shared" ca="1" si="1"/>
+        <f t="shared" si="1"/>
         <v>45563</v>
       </c>
       <c r="Y12">
-        <f t="shared" ca="1" si="2"/>
+        <f t="shared" si="2"/>
         <v>45614</v>
       </c>
       <c r="Z12" t="s">
@@ -5319,7 +4891,6 @@
         <v>81</v>
       </c>
       <c r="AR12">
-        <f ca="1"/>
         <v>348597166.78207755</v>
       </c>
       <c r="AS12" t="s">
@@ -5356,7 +4927,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="13" spans="1:55" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="13" ht="14.5" customHeight="1" spans="1:55" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>153</v>
       </c>
@@ -5391,7 +4962,7 @@
         <v>62</v>
       </c>
       <c r="L13">
-        <f t="shared" ca="1" si="0"/>
+        <f t="shared" si="0"/>
         <v>45563</v>
       </c>
       <c r="M13" t="s">
@@ -5428,11 +4999,11 @@
         <v>62</v>
       </c>
       <c r="X13">
-        <f t="shared" ca="1" si="1"/>
+        <f t="shared" si="1"/>
         <v>45563</v>
       </c>
       <c r="Y13">
-        <f t="shared" ca="1" si="2"/>
+        <f t="shared" si="2"/>
         <v>45614</v>
       </c>
       <c r="Z13" t="s">
@@ -5490,8 +5061,7 @@
         <v>81</v>
       </c>
       <c r="AR13">
-        <f ca="1"/>
-        <v>996765621.22767663</v>
+        <v>996765621.2276766</v>
       </c>
       <c r="AS13" t="s">
         <v>82</v>
@@ -5527,7 +5097,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="14" spans="1:55" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="14" ht="14.5" customHeight="1" spans="1:55" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>159</v>
       </c>
@@ -5562,7 +5132,7 @@
         <v>62</v>
       </c>
       <c r="L14">
-        <f t="shared" ca="1" si="0"/>
+        <f t="shared" si="0"/>
         <v>45563</v>
       </c>
       <c r="M14" t="s">
@@ -5599,11 +5169,11 @@
         <v>62</v>
       </c>
       <c r="X14">
-        <f t="shared" ca="1" si="1"/>
+        <f t="shared" si="1"/>
         <v>45563</v>
       </c>
       <c r="Y14">
-        <f t="shared" ca="1" si="2"/>
+        <f t="shared" si="2"/>
         <v>45614</v>
       </c>
       <c r="Z14" t="s">
@@ -5661,7 +5231,6 @@
         <v>81</v>
       </c>
       <c r="AR14">
-        <f ca="1"/>
         <v>324906807.98325133</v>
       </c>
       <c r="AS14" t="s">
@@ -5698,7 +5267,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="15" spans="1:55" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="15" ht="14.5" customHeight="1" spans="1:55" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>164</v>
       </c>
@@ -5733,7 +5302,7 @@
         <v>62</v>
       </c>
       <c r="L15">
-        <f t="shared" ca="1" si="0"/>
+        <f t="shared" si="0"/>
         <v>45563</v>
       </c>
       <c r="M15" t="s">
@@ -5770,11 +5339,11 @@
         <v>62</v>
       </c>
       <c r="X15">
-        <f t="shared" ca="1" si="1"/>
+        <f t="shared" si="1"/>
         <v>45563</v>
       </c>
       <c r="Y15">
-        <f t="shared" ca="1" si="2"/>
+        <f t="shared" si="2"/>
         <v>45614</v>
       </c>
       <c r="Z15" t="s">
@@ -5832,7 +5401,6 @@
         <v>81</v>
       </c>
       <c r="AR15">
-        <f ca="1"/>
         <v>686344253.4275887</v>
       </c>
       <c r="AS15" t="s">
@@ -5869,7 +5437,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="16" spans="1:55" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="16" ht="14.5" customHeight="1" spans="1:55" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>170</v>
       </c>
@@ -5904,7 +5472,7 @@
         <v>62</v>
       </c>
       <c r="L16">
-        <f t="shared" ca="1" si="0"/>
+        <f t="shared" si="0"/>
         <v>45563</v>
       </c>
       <c r="M16" t="s">
@@ -5941,11 +5509,11 @@
         <v>62</v>
       </c>
       <c r="X16">
-        <f t="shared" ca="1" si="1"/>
+        <f t="shared" si="1"/>
         <v>45563</v>
       </c>
       <c r="Y16">
-        <f t="shared" ca="1" si="2"/>
+        <f t="shared" si="2"/>
         <v>45614</v>
       </c>
       <c r="Z16" t="s">
@@ -6003,7 +5571,6 @@
         <v>81</v>
       </c>
       <c r="AR16">
-        <f ca="1"/>
         <v>610067726.7278229</v>
       </c>
       <c r="AS16" t="s">
@@ -6040,7 +5607,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="17" spans="1:55" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="17" ht="14.5" customHeight="1" spans="1:55" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>174</v>
       </c>
@@ -6075,7 +5642,7 @@
         <v>62</v>
       </c>
       <c r="L17">
-        <f t="shared" ca="1" si="0"/>
+        <f t="shared" si="0"/>
         <v>45563</v>
       </c>
       <c r="M17" t="s">
@@ -6112,11 +5679,11 @@
         <v>62</v>
       </c>
       <c r="X17">
-        <f t="shared" ca="1" si="1"/>
+        <f t="shared" si="1"/>
         <v>45563</v>
       </c>
       <c r="Y17">
-        <f t="shared" ca="1" si="2"/>
+        <f t="shared" si="2"/>
         <v>45614</v>
       </c>
       <c r="Z17" t="s">
@@ -6174,7 +5741,6 @@
         <v>81</v>
       </c>
       <c r="AR17">
-        <f ca="1"/>
         <v>523158718.836573</v>
       </c>
       <c r="AS17" t="s">
@@ -6211,40 +5777,67 @@
         <v>87</v>
       </c>
     </row>
-    <row r="18" spans="1:55" ht="14.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="18" ht="14.5" customHeight="1" spans="44:44" x14ac:dyDescent="0.25">
       <c r="AR18" s="9"/>
     </row>
   </sheetData>
-  <dataValidations count="3">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="K10:K17 Z10:Z17 W10:W17 T10:T17" xr:uid="{00000000-0002-0000-0000-000000000000}">
+  <dataValidations count="12">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="K10:K17">
       <formula1>INDIRECT($E3)</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="K2 Z2 W2 T2" xr:uid="{00000000-0002-0000-0000-000001000000}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="K2">
       <formula1>INDIRECT($G2)</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="K3:K17 Z3:Z17 W3:W17 T3:T17" xr:uid="{00000000-0002-0000-0000-000002000000}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="K3:K17">
+      <formula1>INDIRECT($E3)</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="T10:T17">
+      <formula1>INDIRECT($E3)</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="T2">
+      <formula1>INDIRECT($G2)</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="T3:T17">
+      <formula1>INDIRECT($E3)</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="W10:W17">
+      <formula1>INDIRECT($E3)</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="W2">
+      <formula1>INDIRECT($G2)</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="W3:W17">
+      <formula1>INDIRECT($E3)</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="Z10:Z17">
+      <formula1>INDIRECT($E3)</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="Z2">
+      <formula1>INDIRECT($G2)</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="Z3:Z17">
       <formula1>INDIRECT($E3)</formula1>
     </dataValidation>
   </dataValidations>
   <hyperlinks>
-    <hyperlink ref="V2" r:id="rId1" xr:uid="{00000000-0004-0000-0000-000000000000}"/>
-    <hyperlink ref="V3" r:id="rId2" xr:uid="{00000000-0004-0000-0000-000001000000}"/>
-    <hyperlink ref="V4" r:id="rId3" xr:uid="{00000000-0004-0000-0000-000002000000}"/>
-    <hyperlink ref="V5" r:id="rId4" xr:uid="{00000000-0004-0000-0000-000003000000}"/>
-    <hyperlink ref="V6" r:id="rId5" xr:uid="{00000000-0004-0000-0000-000004000000}"/>
-    <hyperlink ref="V7" r:id="rId6" xr:uid="{00000000-0004-0000-0000-000005000000}"/>
-    <hyperlink ref="V8" r:id="rId7" xr:uid="{00000000-0004-0000-0000-000006000000}"/>
-    <hyperlink ref="V9" r:id="rId8" xr:uid="{00000000-0004-0000-0000-000007000000}"/>
-    <hyperlink ref="V10" r:id="rId9" xr:uid="{00000000-0004-0000-0000-000008000000}"/>
-    <hyperlink ref="V11" r:id="rId10" xr:uid="{00000000-0004-0000-0000-000009000000}"/>
-    <hyperlink ref="V12" r:id="rId11" xr:uid="{00000000-0004-0000-0000-00000A000000}"/>
-    <hyperlink ref="V13" r:id="rId12" xr:uid="{00000000-0004-0000-0000-00000B000000}"/>
-    <hyperlink ref="V14" r:id="rId13" xr:uid="{00000000-0004-0000-0000-00000C000000}"/>
-    <hyperlink ref="V15" r:id="rId14" xr:uid="{00000000-0004-0000-0000-00000D000000}"/>
-    <hyperlink ref="V16" r:id="rId15" xr:uid="{00000000-0004-0000-0000-00000E000000}"/>
-    <hyperlink ref="V17" r:id="rId16" xr:uid="{00000000-0004-0000-0000-00000F000000}"/>
+    <hyperlink ref="V2" r:id="rId1"/>
+    <hyperlink ref="V3" r:id="rId2"/>
+    <hyperlink ref="V4" r:id="rId3"/>
+    <hyperlink ref="V5" r:id="rId4"/>
+    <hyperlink ref="V6" r:id="rId5"/>
+    <hyperlink ref="V7" r:id="rId6"/>
+    <hyperlink ref="V8" r:id="rId7"/>
+    <hyperlink ref="V9" r:id="rId8"/>
+    <hyperlink ref="V10" r:id="rId9"/>
+    <hyperlink ref="V11" r:id="rId10"/>
+    <hyperlink ref="V12" r:id="rId11"/>
+    <hyperlink ref="V13" r:id="rId12"/>
+    <hyperlink ref="V14" r:id="rId13"/>
+    <hyperlink ref="V15" r:id="rId14"/>
+    <hyperlink ref="V16" r:id="rId15"/>
+    <hyperlink ref="V17" r:id="rId16"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" useFirstPageNumber="1" horizontalDpi="4294967295" verticalDpi="4294967295"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>
 </worksheet>
 </file>